--- a/Knowledge/Model Outputs/MNST/MNST_model.xlsx
+++ b/Knowledge/Model Outputs/MNST/MNST_model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rodin\Desktop\Brain\Knowledge\Model Outputs\MNST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4494808D-52CD-41C0-905D-FD3F44160813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A5A73C-4B0C-4130-BC1E-E73248AE8B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4810,83 +4810,83 @@
       </c>
       <c r="Z22" s="11">
         <f>'CF DRIVERS'!Z22</f>
-        <v>0</v>
+        <v>4815.9971645233672</v>
       </c>
       <c r="AA22" s="11">
         <f>'CF DRIVERS'!AA22</f>
-        <v>0</v>
+        <v>29114.825015548769</v>
       </c>
       <c r="AB22" s="11">
         <f>'CF DRIVERS'!AB22</f>
-        <v>0</v>
+        <v>9690.2162765632165</v>
       </c>
       <c r="AC22" s="11">
         <f>'CF DRIVERS'!AC22</f>
-        <v>0</v>
+        <v>-7485.8246022026797</v>
       </c>
       <c r="AD22" s="11">
         <f>'CF DRIVERS'!AD22</f>
-        <v>0</v>
+        <v>5663.8592644697201</v>
       </c>
       <c r="AE22" s="11">
         <f>'CF DRIVERS'!AE22</f>
-        <v>0</v>
+        <v>34240.525017844666</v>
       </c>
       <c r="AF22" s="11">
         <f>'CF DRIVERS'!AF22</f>
-        <v>0</v>
+        <v>11396.190520423574</v>
       </c>
       <c r="AG22" s="11">
         <f>'CF DRIVERS'!AG22</f>
-        <v>0</v>
+        <v>-8803.7130373969849</v>
       </c>
       <c r="AH22" s="11">
         <f>'CF DRIVERS'!AH22</f>
-        <v>0</v>
+        <v>6660.9885080558233</v>
       </c>
       <c r="AI22" s="11">
         <f>'CF DRIVERS'!AI22</f>
-        <v>0</v>
+        <v>40268.610677602192</v>
       </c>
       <c r="AJ22" s="11">
         <f>'CF DRIVERS'!AJ22</f>
-        <v>0</v>
+        <v>13402.503584146376</v>
       </c>
       <c r="AK22" s="11">
         <f>'CF DRIVERS'!AK22</f>
-        <v>0</v>
+        <v>-10353.617318528588</v>
       </c>
       <c r="AL22" s="11">
         <f>'CF DRIVERS'!AL22</f>
-        <v>0</v>
+        <v>7833.6635556578985</v>
       </c>
       <c r="AM22" s="11">
         <f>'CF DRIVERS'!AM22</f>
-        <v>0</v>
+        <v>47357.948076415589</v>
       </c>
       <c r="AN22" s="11">
         <f>'CF DRIVERS'!AN22</f>
-        <v>0</v>
+        <v>15762.030478618326</v>
       </c>
       <c r="AO22" s="11">
         <f>'CF DRIVERS'!AO22</f>
-        <v>0</v>
+        <v>-12176.384114654415</v>
       </c>
       <c r="AP22" s="11">
         <f>'CF DRIVERS'!AP22</f>
-        <v>0</v>
+        <v>9212.7894574545571</v>
       </c>
       <c r="AQ22" s="11">
         <f>'CF DRIVERS'!AQ22</f>
-        <v>0</v>
+        <v>55695.371860840714</v>
       </c>
       <c r="AR22" s="11">
         <f>'CF DRIVERS'!AR22</f>
-        <v>0</v>
+        <v>18536.954924061356</v>
       </c>
       <c r="AS22" s="11">
         <f>'CF DRIVERS'!AS22</f>
-        <v>0</v>
+        <v>-14320.051200103422</v>
       </c>
     </row>
     <row r="23" spans="1:45" x14ac:dyDescent="0.25">
@@ -5172,83 +5172,83 @@
       </c>
       <c r="Z24" s="7">
         <f t="shared" ref="Z24:AS24" si="0">SUM(Z2:Z23)</f>
-        <v>507366.04979337979</v>
+        <v>512182.04695790313</v>
       </c>
       <c r="AA24" s="7">
         <f t="shared" si="0"/>
-        <v>433233.00936874747</v>
+        <v>462347.83438429626</v>
       </c>
       <c r="AB24" s="7">
         <f t="shared" si="0"/>
-        <v>572854.57586070639</v>
+        <v>582544.79213726963</v>
       </c>
       <c r="AC24" s="7">
         <f t="shared" si="0"/>
-        <v>657177.62129324151</v>
+        <v>649691.79669103888</v>
       </c>
       <c r="AD24" s="7">
         <f t="shared" si="0"/>
-        <v>592457.61741658114</v>
+        <v>598121.47668105084</v>
       </c>
       <c r="AE24" s="7">
         <f t="shared" si="0"/>
-        <v>505273.36595867545</v>
+        <v>539513.89097652014</v>
       </c>
       <c r="AF24" s="7">
         <f t="shared" si="0"/>
-        <v>669475.47735537635</v>
+        <v>680871.66787579993</v>
       </c>
       <c r="AG24" s="7">
         <f t="shared" si="0"/>
-        <v>768643.69647301291</v>
+        <v>759839.9834356159</v>
       </c>
       <c r="AH24" s="7">
         <f t="shared" si="0"/>
-        <v>692529.65798195684</v>
+        <v>699190.64649001264</v>
       </c>
       <c r="AI24" s="7">
         <f t="shared" si="0"/>
-        <v>589996.51407289389</v>
+        <v>630265.12475049612</v>
       </c>
       <c r="AJ24" s="7">
         <f t="shared" si="0"/>
-        <v>783106.60490321869</v>
+        <v>796509.10848736507</v>
       </c>
       <c r="AK24" s="7">
         <f t="shared" si="0"/>
-        <v>899733.50840887695</v>
+        <v>889379.89109034836</v>
       </c>
       <c r="AL24" s="7">
         <f t="shared" si="0"/>
-        <v>810219.50178955751</v>
+        <v>818053.16534521547</v>
       </c>
       <c r="AM24" s="7">
         <f t="shared" si="0"/>
-        <v>689635.27443110279</v>
+        <v>736993.22250751837</v>
       </c>
       <c r="AN24" s="7">
         <f t="shared" si="0"/>
-        <v>916742.62928357895</v>
+        <v>932504.65976219729</v>
       </c>
       <c r="AO24" s="7">
         <f t="shared" si="0"/>
-        <v>1053901.8395864605</v>
+        <v>1041725.4554718061</v>
       </c>
       <c r="AP24" s="7">
         <f t="shared" si="0"/>
-        <v>948628.78431446548</v>
+        <v>957841.57377192006</v>
       </c>
       <c r="AQ24" s="7">
         <f t="shared" si="0"/>
-        <v>806815.55852933368</v>
+        <v>862510.93039017438</v>
       </c>
       <c r="AR24" s="7">
         <f t="shared" si="0"/>
-        <v>1073905.4366725073</v>
+        <v>1092442.3915965687</v>
       </c>
       <c r="AS24" s="7">
         <f t="shared" si="0"/>
-        <v>1235211.6911080228</v>
+        <v>1220891.6399079193</v>
       </c>
     </row>
     <row r="25" spans="1:45" x14ac:dyDescent="0.25">
@@ -8587,83 +8587,83 @@
       </c>
       <c r="Z43" s="7">
         <f t="shared" ref="Z43:AS43" si="3">Z24+Z33+Z41+Z42</f>
-        <v>492210.49508407683</v>
+        <v>497026.49224860017</v>
       </c>
       <c r="AA43" s="7">
         <f t="shared" si="3"/>
-        <v>356388.98789241223</v>
+        <v>385503.81290796102</v>
       </c>
       <c r="AB43" s="7">
         <f t="shared" si="3"/>
-        <v>540799.75702492963</v>
+        <v>550489.97330149286</v>
       </c>
       <c r="AC43" s="7">
         <f t="shared" si="3"/>
-        <v>666930.94479695905</v>
+        <v>659445.12019475643</v>
       </c>
       <c r="AD43" s="7">
         <f t="shared" si="3"/>
-        <v>570212.55911054707</v>
+        <v>575876.41837501677</v>
       </c>
       <c r="AE43" s="7">
         <f t="shared" si="3"/>
-        <v>410479.51202975848</v>
+        <v>444720.03704760317</v>
       </c>
       <c r="AF43" s="7">
         <f t="shared" si="3"/>
-        <v>627356.01912433258</v>
+        <v>638752.20964475628</v>
       </c>
       <c r="AG43" s="7">
         <f t="shared" si="3"/>
-        <v>775692.75438316399</v>
+        <v>766889.04134576698</v>
       </c>
       <c r="AH43" s="7">
         <f t="shared" si="3"/>
-        <v>661946.98043423635</v>
+        <v>668607.96894229215</v>
       </c>
       <c r="AI43" s="7">
         <f t="shared" si="3"/>
-        <v>474092.73807401728</v>
+        <v>514361.34875161952</v>
       </c>
       <c r="AJ43" s="7">
         <f t="shared" si="3"/>
-        <v>729150.61539214232</v>
+        <v>742553.11897628871</v>
       </c>
       <c r="AK43" s="7">
         <f t="shared" si="3"/>
-        <v>903602.21151140111</v>
+        <v>893248.59419287252</v>
       </c>
       <c r="AL43" s="7">
         <f t="shared" si="3"/>
-        <v>769831.3570929959</v>
+        <v>777665.02064865385</v>
       </c>
       <c r="AM43" s="7">
         <f t="shared" si="3"/>
-        <v>548905.14916256093</v>
+        <v>596263.09723897651</v>
       </c>
       <c r="AN43" s="7">
         <f t="shared" si="3"/>
-        <v>848866.27290778619</v>
+        <v>864628.30338640453</v>
       </c>
       <c r="AO43" s="7">
         <f t="shared" si="3"/>
-        <v>1054030.2825878845</v>
+        <v>1041853.8984732302</v>
       </c>
       <c r="AP43" s="7">
         <f t="shared" si="3"/>
-        <v>896708.90817035967</v>
+        <v>905921.69762781425</v>
       </c>
       <c r="AQ43" s="7">
         <f t="shared" si="3"/>
-        <v>636888.37530781608</v>
+        <v>692583.74716865667</v>
       </c>
       <c r="AR43" s="7">
         <f t="shared" si="3"/>
-        <v>989658.01608340244</v>
+        <v>1008194.9710074639</v>
       </c>
       <c r="AS43" s="7">
         <f t="shared" si="3"/>
-        <v>1230941.3967137532</v>
+        <v>1216621.3455136498</v>
       </c>
     </row>
   </sheetData>
@@ -10143,83 +10143,83 @@
       </c>
       <c r="W2" s="4">
         <f>V2+'QTR CF'!Z43</f>
-        <v>2580327.4950840767</v>
+        <v>2585143.4922486003</v>
       </c>
       <c r="X2" s="4">
         <f>W2+'QTR CF'!AA43</f>
-        <v>2936716.4829764888</v>
+        <v>2970647.3051565615</v>
       </c>
       <c r="Y2" s="4">
         <f>X2+'QTR CF'!AB43</f>
-        <v>3477516.2400014186</v>
+        <v>3521137.2784580542</v>
       </c>
       <c r="Z2" s="4">
         <f>Y2+'QTR CF'!AC43</f>
-        <v>4144447.1847983776</v>
+        <v>4180582.3986528106</v>
       </c>
       <c r="AA2" s="4">
         <f>Z2+'QTR CF'!AD43</f>
-        <v>4714659.743908925</v>
+        <v>4756458.8170278277</v>
       </c>
       <c r="AB2" s="4">
         <f>AA2+'QTR CF'!AE43</f>
-        <v>5125139.2559386836</v>
+        <v>5201178.8540754309</v>
       </c>
       <c r="AC2" s="4">
         <f>AB2+'QTR CF'!AF43</f>
-        <v>5752495.2750630165</v>
+        <v>5839931.0637201872</v>
       </c>
       <c r="AD2" s="4">
         <f>AC2+'QTR CF'!AG43</f>
-        <v>6528188.0294461809</v>
+        <v>6606820.1050659539</v>
       </c>
       <c r="AE2" s="4">
         <f>AD2+'QTR CF'!AH43</f>
-        <v>7190135.009880417</v>
+        <v>7275428.074008246</v>
       </c>
       <c r="AF2" s="4">
         <f>AE2+'QTR CF'!AI43</f>
-        <v>7664227.7479544347</v>
+        <v>7789789.4227598654</v>
       </c>
       <c r="AG2" s="4">
         <f>AF2+'QTR CF'!AJ43</f>
-        <v>8393378.3633465767</v>
+        <v>8532342.5417361539</v>
       </c>
       <c r="AH2" s="4">
         <f>AG2+'QTR CF'!AK43</f>
-        <v>9296980.5748579782</v>
+        <v>9425591.1359290257</v>
       </c>
       <c r="AI2" s="4">
         <f>AH2+'QTR CF'!AL43</f>
-        <v>10066811.931950973</v>
+        <v>10203256.15657768</v>
       </c>
       <c r="AJ2" s="4">
         <f>AI2+'QTR CF'!AM43</f>
-        <v>10615717.081113534</v>
+        <v>10799519.253816657</v>
       </c>
       <c r="AK2" s="4">
         <f>AJ2+'QTR CF'!AN43</f>
-        <v>11464583.35402132</v>
+        <v>11664147.557203062</v>
       </c>
       <c r="AL2" s="4">
         <f>AK2+'QTR CF'!AO43</f>
-        <v>12518613.636609204</v>
+        <v>12706001.455676291</v>
       </c>
       <c r="AM2" s="4">
         <f>AL2+'QTR CF'!AP43</f>
-        <v>13415322.544779563</v>
+        <v>13611923.153304106</v>
       </c>
       <c r="AN2" s="4">
         <f>AM2+'QTR CF'!AQ43</f>
-        <v>14052210.920087378</v>
+        <v>14304506.900472762</v>
       </c>
       <c r="AO2" s="4">
         <f>AN2+'QTR CF'!AR43</f>
-        <v>15041868.936170781</v>
+        <v>15312701.871480227</v>
       </c>
       <c r="AP2" s="4">
         <f>AO2+'QTR CF'!AS43</f>
-        <v>16272810.332884535</v>
+        <v>16529323.216993876</v>
       </c>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.25">
@@ -18327,65 +18327,85 @@
         <f>'QTR CF'!Y22</f>
         <v>-2858</v>
       </c>
-      <c r="Z22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AL22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AM22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AN22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AO22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AP22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AQ22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AR22" s="15">
-        <v>0</v>
-      </c>
-      <c r="AS22" s="15">
-        <v>0</v>
+      <c r="Z22" s="4">
+        <f>-('QTR BS'!W14-'QTR BS'!V14)+('QTR BS'!W19-'QTR BS'!V19)+('QTR BS'!W21-'QTR BS'!V21)+('QTR BS'!W23-'QTR BS'!V23)+('QTR BS'!W25-'QTR BS'!V25)-('QTR BS'!W3-'QTR BS'!V3)-('QTR BS'!W12-'QTR BS'!V12)-('QTR BS'!W13-'QTR BS'!V13)+('QTR BS'!W24-'QTR BS'!V24)+('QTR BS'!W26-'QTR BS'!V26)+('QTR BS'!W28-'QTR BS'!V28)+('QTR BS'!W32-'QTR BS'!V32)</f>
+        <v>4815.9971645233672</v>
+      </c>
+      <c r="AA22" s="4">
+        <f>-('QTR BS'!X14-'QTR BS'!W14)+('QTR BS'!X19-'QTR BS'!W19)+('QTR BS'!X21-'QTR BS'!W21)+('QTR BS'!X23-'QTR BS'!W23)+('QTR BS'!X25-'QTR BS'!W25)-('QTR BS'!X3-'QTR BS'!W3)-('QTR BS'!X12-'QTR BS'!W12)-('QTR BS'!X13-'QTR BS'!W13)+('QTR BS'!X24-'QTR BS'!W24)+('QTR BS'!X26-'QTR BS'!W26)+('QTR BS'!X28-'QTR BS'!W28)+('QTR BS'!X32-'QTR BS'!W32)</f>
+        <v>29114.825015548769</v>
+      </c>
+      <c r="AB22" s="4">
+        <f>-('QTR BS'!Y14-'QTR BS'!X14)+('QTR BS'!Y19-'QTR BS'!X19)+('QTR BS'!Y21-'QTR BS'!X21)+('QTR BS'!Y23-'QTR BS'!X23)+('QTR BS'!Y25-'QTR BS'!X25)-('QTR BS'!Y3-'QTR BS'!X3)-('QTR BS'!Y12-'QTR BS'!X12)-('QTR BS'!Y13-'QTR BS'!X13)+('QTR BS'!Y24-'QTR BS'!X24)+('QTR BS'!Y26-'QTR BS'!X26)+('QTR BS'!Y28-'QTR BS'!X28)+('QTR BS'!Y32-'QTR BS'!X32)</f>
+        <v>9690.2162765632165</v>
+      </c>
+      <c r="AC22" s="4">
+        <f>-('QTR BS'!Z14-'QTR BS'!Y14)+('QTR BS'!Z19-'QTR BS'!Y19)+('QTR BS'!Z21-'QTR BS'!Y21)+('QTR BS'!Z23-'QTR BS'!Y23)+('QTR BS'!Z25-'QTR BS'!Y25)-('QTR BS'!Z3-'QTR BS'!Y3)-('QTR BS'!Z12-'QTR BS'!Y12)-('QTR BS'!Z13-'QTR BS'!Y13)+('QTR BS'!Z24-'QTR BS'!Y24)+('QTR BS'!Z26-'QTR BS'!Y26)+('QTR BS'!Z28-'QTR BS'!Y28)+('QTR BS'!Z32-'QTR BS'!Y32)</f>
+        <v>-7485.8246022026797</v>
+      </c>
+      <c r="AD22" s="4">
+        <f>-('QTR BS'!AA14-'QTR BS'!Z14)+('QTR BS'!AA19-'QTR BS'!Z19)+('QTR BS'!AA21-'QTR BS'!Z21)+('QTR BS'!AA23-'QTR BS'!Z23)+('QTR BS'!AA25-'QTR BS'!Z25)-('QTR BS'!AA3-'QTR BS'!Z3)-('QTR BS'!AA12-'QTR BS'!Z12)-('QTR BS'!AA13-'QTR BS'!Z13)+('QTR BS'!AA24-'QTR BS'!Z24)+('QTR BS'!AA26-'QTR BS'!Z26)+('QTR BS'!AA28-'QTR BS'!Z28)+('QTR BS'!AA32-'QTR BS'!Z32)</f>
+        <v>5663.8592644697201</v>
+      </c>
+      <c r="AE22" s="4">
+        <f>-('QTR BS'!AB14-'QTR BS'!AA14)+('QTR BS'!AB19-'QTR BS'!AA19)+('QTR BS'!AB21-'QTR BS'!AA21)+('QTR BS'!AB23-'QTR BS'!AA23)+('QTR BS'!AB25-'QTR BS'!AA25)-('QTR BS'!AB3-'QTR BS'!AA3)-('QTR BS'!AB12-'QTR BS'!AA12)-('QTR BS'!AB13-'QTR BS'!AA13)+('QTR BS'!AB24-'QTR BS'!AA24)+('QTR BS'!AB26-'QTR BS'!AA26)+('QTR BS'!AB28-'QTR BS'!AA28)+('QTR BS'!AB32-'QTR BS'!AA32)</f>
+        <v>34240.525017844666</v>
+      </c>
+      <c r="AF22" s="4">
+        <f>-('QTR BS'!AC14-'QTR BS'!AB14)+('QTR BS'!AC19-'QTR BS'!AB19)+('QTR BS'!AC21-'QTR BS'!AB21)+('QTR BS'!AC23-'QTR BS'!AB23)+('QTR BS'!AC25-'QTR BS'!AB25)-('QTR BS'!AC3-'QTR BS'!AB3)-('QTR BS'!AC12-'QTR BS'!AB12)-('QTR BS'!AC13-'QTR BS'!AB13)+('QTR BS'!AC24-'QTR BS'!AB24)+('QTR BS'!AC26-'QTR BS'!AB26)+('QTR BS'!AC28-'QTR BS'!AB28)+('QTR BS'!AC32-'QTR BS'!AB32)</f>
+        <v>11396.190520423574</v>
+      </c>
+      <c r="AG22" s="4">
+        <f>-('QTR BS'!AD14-'QTR BS'!AC14)+('QTR BS'!AD19-'QTR BS'!AC19)+('QTR BS'!AD21-'QTR BS'!AC21)+('QTR BS'!AD23-'QTR BS'!AC23)+('QTR BS'!AD25-'QTR BS'!AC25)-('QTR BS'!AD3-'QTR BS'!AC3)-('QTR BS'!AD12-'QTR BS'!AC12)-('QTR BS'!AD13-'QTR BS'!AC13)+('QTR BS'!AD24-'QTR BS'!AC24)+('QTR BS'!AD26-'QTR BS'!AC26)+('QTR BS'!AD28-'QTR BS'!AC28)+('QTR BS'!AD32-'QTR BS'!AC32)</f>
+        <v>-8803.7130373969849</v>
+      </c>
+      <c r="AH22" s="4">
+        <f>-('QTR BS'!AE14-'QTR BS'!AD14)+('QTR BS'!AE19-'QTR BS'!AD19)+('QTR BS'!AE21-'QTR BS'!AD21)+('QTR BS'!AE23-'QTR BS'!AD23)+('QTR BS'!AE25-'QTR BS'!AD25)-('QTR BS'!AE3-'QTR BS'!AD3)-('QTR BS'!AE12-'QTR BS'!AD12)-('QTR BS'!AE13-'QTR BS'!AD13)+('QTR BS'!AE24-'QTR BS'!AD24)+('QTR BS'!AE26-'QTR BS'!AD26)+('QTR BS'!AE28-'QTR BS'!AD28)+('QTR BS'!AE32-'QTR BS'!AD32)</f>
+        <v>6660.9885080558233</v>
+      </c>
+      <c r="AI22" s="4">
+        <f>-('QTR BS'!AF14-'QTR BS'!AE14)+('QTR BS'!AF19-'QTR BS'!AE19)+('QTR BS'!AF21-'QTR BS'!AE21)+('QTR BS'!AF23-'QTR BS'!AE23)+('QTR BS'!AF25-'QTR BS'!AE25)-('QTR BS'!AF3-'QTR BS'!AE3)-('QTR BS'!AF12-'QTR BS'!AE12)-('QTR BS'!AF13-'QTR BS'!AE13)+('QTR BS'!AF24-'QTR BS'!AE24)+('QTR BS'!AF26-'QTR BS'!AE26)+('QTR BS'!AF28-'QTR BS'!AE28)+('QTR BS'!AF32-'QTR BS'!AE32)</f>
+        <v>40268.610677602192</v>
+      </c>
+      <c r="AJ22" s="4">
+        <f>-('QTR BS'!AG14-'QTR BS'!AF14)+('QTR BS'!AG19-'QTR BS'!AF19)+('QTR BS'!AG21-'QTR BS'!AF21)+('QTR BS'!AG23-'QTR BS'!AF23)+('QTR BS'!AG25-'QTR BS'!AF25)-('QTR BS'!AG3-'QTR BS'!AF3)-('QTR BS'!AG12-'QTR BS'!AF12)-('QTR BS'!AG13-'QTR BS'!AF13)+('QTR BS'!AG24-'QTR BS'!AF24)+('QTR BS'!AG26-'QTR BS'!AF26)+('QTR BS'!AG28-'QTR BS'!AF28)+('QTR BS'!AG32-'QTR BS'!AF32)</f>
+        <v>13402.503584146376</v>
+      </c>
+      <c r="AK22" s="4">
+        <f>-('QTR BS'!AH14-'QTR BS'!AG14)+('QTR BS'!AH19-'QTR BS'!AG19)+('QTR BS'!AH21-'QTR BS'!AG21)+('QTR BS'!AH23-'QTR BS'!AG23)+('QTR BS'!AH25-'QTR BS'!AG25)-('QTR BS'!AH3-'QTR BS'!AG3)-('QTR BS'!AH12-'QTR BS'!AG12)-('QTR BS'!AH13-'QTR BS'!AG13)+('QTR BS'!AH24-'QTR BS'!AG24)+('QTR BS'!AH26-'QTR BS'!AG26)+('QTR BS'!AH28-'QTR BS'!AG28)+('QTR BS'!AH32-'QTR BS'!AG32)</f>
+        <v>-10353.617318528588</v>
+      </c>
+      <c r="AL22" s="4">
+        <f>-('QTR BS'!AI14-'QTR BS'!AH14)+('QTR BS'!AI19-'QTR BS'!AH19)+('QTR BS'!AI21-'QTR BS'!AH21)+('QTR BS'!AI23-'QTR BS'!AH23)+('QTR BS'!AI25-'QTR BS'!AH25)-('QTR BS'!AI3-'QTR BS'!AH3)-('QTR BS'!AI12-'QTR BS'!AH12)-('QTR BS'!AI13-'QTR BS'!AH13)+('QTR BS'!AI24-'QTR BS'!AH24)+('QTR BS'!AI26-'QTR BS'!AH26)+('QTR BS'!AI28-'QTR BS'!AH28)+('QTR BS'!AI32-'QTR BS'!AH32)</f>
+        <v>7833.6635556578985</v>
+      </c>
+      <c r="AM22" s="4">
+        <f>-('QTR BS'!AJ14-'QTR BS'!AI14)+('QTR BS'!AJ19-'QTR BS'!AI19)+('QTR BS'!AJ21-'QTR BS'!AI21)+('QTR BS'!AJ23-'QTR BS'!AI23)+('QTR BS'!AJ25-'QTR BS'!AI25)-('QTR BS'!AJ3-'QTR BS'!AI3)-('QTR BS'!AJ12-'QTR BS'!AI12)-('QTR BS'!AJ13-'QTR BS'!AI13)+('QTR BS'!AJ24-'QTR BS'!AI24)+('QTR BS'!AJ26-'QTR BS'!AI26)+('QTR BS'!AJ28-'QTR BS'!AI28)+('QTR BS'!AJ32-'QTR BS'!AI32)</f>
+        <v>47357.948076415589</v>
+      </c>
+      <c r="AN22" s="4">
+        <f>-('QTR BS'!AK14-'QTR BS'!AJ14)+('QTR BS'!AK19-'QTR BS'!AJ19)+('QTR BS'!AK21-'QTR BS'!AJ21)+('QTR BS'!AK23-'QTR BS'!AJ23)+('QTR BS'!AK25-'QTR BS'!AJ25)-('QTR BS'!AK3-'QTR BS'!AJ3)-('QTR BS'!AK12-'QTR BS'!AJ12)-('QTR BS'!AK13-'QTR BS'!AJ13)+('QTR BS'!AK24-'QTR BS'!AJ24)+('QTR BS'!AK26-'QTR BS'!AJ26)+('QTR BS'!AK28-'QTR BS'!AJ28)+('QTR BS'!AK32-'QTR BS'!AJ32)</f>
+        <v>15762.030478618326</v>
+      </c>
+      <c r="AO22" s="4">
+        <f>-('QTR BS'!AL14-'QTR BS'!AK14)+('QTR BS'!AL19-'QTR BS'!AK19)+('QTR BS'!AL21-'QTR BS'!AK21)+('QTR BS'!AL23-'QTR BS'!AK23)+('QTR BS'!AL25-'QTR BS'!AK25)-('QTR BS'!AL3-'QTR BS'!AK3)-('QTR BS'!AL12-'QTR BS'!AK12)-('QTR BS'!AL13-'QTR BS'!AK13)+('QTR BS'!AL24-'QTR BS'!AK24)+('QTR BS'!AL26-'QTR BS'!AK26)+('QTR BS'!AL28-'QTR BS'!AK28)+('QTR BS'!AL32-'QTR BS'!AK32)</f>
+        <v>-12176.384114654415</v>
+      </c>
+      <c r="AP22" s="4">
+        <f>-('QTR BS'!AM14-'QTR BS'!AL14)+('QTR BS'!AM19-'QTR BS'!AL19)+('QTR BS'!AM21-'QTR BS'!AL21)+('QTR BS'!AM23-'QTR BS'!AL23)+('QTR BS'!AM25-'QTR BS'!AL25)-('QTR BS'!AM3-'QTR BS'!AL3)-('QTR BS'!AM12-'QTR BS'!AL12)-('QTR BS'!AM13-'QTR BS'!AL13)+('QTR BS'!AM24-'QTR BS'!AL24)+('QTR BS'!AM26-'QTR BS'!AL26)+('QTR BS'!AM28-'QTR BS'!AL28)+('QTR BS'!AM32-'QTR BS'!AL32)</f>
+        <v>9212.7894574545571</v>
+      </c>
+      <c r="AQ22" s="4">
+        <f>-('QTR BS'!AN14-'QTR BS'!AM14)+('QTR BS'!AN19-'QTR BS'!AM19)+('QTR BS'!AN21-'QTR BS'!AM21)+('QTR BS'!AN23-'QTR BS'!AM23)+('QTR BS'!AN25-'QTR BS'!AM25)-('QTR BS'!AN3-'QTR BS'!AM3)-('QTR BS'!AN12-'QTR BS'!AM12)-('QTR BS'!AN13-'QTR BS'!AM13)+('QTR BS'!AN24-'QTR BS'!AM24)+('QTR BS'!AN26-'QTR BS'!AM26)+('QTR BS'!AN28-'QTR BS'!AM28)+('QTR BS'!AN32-'QTR BS'!AM32)</f>
+        <v>55695.371860840714</v>
+      </c>
+      <c r="AR22" s="4">
+        <f>-('QTR BS'!AO14-'QTR BS'!AN14)+('QTR BS'!AO19-'QTR BS'!AN19)+('QTR BS'!AO21-'QTR BS'!AN21)+('QTR BS'!AO23-'QTR BS'!AN23)+('QTR BS'!AO25-'QTR BS'!AN25)-('QTR BS'!AO3-'QTR BS'!AN3)-('QTR BS'!AO12-'QTR BS'!AN12)-('QTR BS'!AO13-'QTR BS'!AN13)+('QTR BS'!AO24-'QTR BS'!AN24)+('QTR BS'!AO26-'QTR BS'!AN26)+('QTR BS'!AO28-'QTR BS'!AN28)+('QTR BS'!AO32-'QTR BS'!AN32)</f>
+        <v>18536.954924061356</v>
+      </c>
+      <c r="AS22" s="4">
+        <f>-('QTR BS'!AP14-'QTR BS'!AO14)+('QTR BS'!AP19-'QTR BS'!AO19)+('QTR BS'!AP21-'QTR BS'!AO21)+('QTR BS'!AP23-'QTR BS'!AO23)+('QTR BS'!AP25-'QTR BS'!AO25)-('QTR BS'!AP3-'QTR BS'!AO3)-('QTR BS'!AP12-'QTR BS'!AO12)-('QTR BS'!AP13-'QTR BS'!AO13)+('QTR BS'!AP24-'QTR BS'!AO24)+('QTR BS'!AP26-'QTR BS'!AO26)+('QTR BS'!AP28-'QTR BS'!AO28)+('QTR BS'!AP32-'QTR BS'!AO32)</f>
+        <v>-14320.051200103422</v>
       </c>
     </row>
     <row r="23" spans="1:45" x14ac:dyDescent="0.25">
@@ -22013,23 +22033,23 @@
       </c>
       <c r="H2" s="11">
         <f>'QTR BS'!Z2</f>
-        <v>4144447.1847983776</v>
+        <v>4180582.3986528106</v>
       </c>
       <c r="I2" s="11">
         <f>'QTR BS'!AD2</f>
-        <v>6528188.0294461809</v>
+        <v>6606820.1050659539</v>
       </c>
       <c r="J2" s="11">
         <f>'QTR BS'!AH2</f>
-        <v>9296980.5748579782</v>
+        <v>9425591.1359290257</v>
       </c>
       <c r="K2" s="11">
         <f>'QTR BS'!AL2</f>
-        <v>12518613.636609204</v>
+        <v>12706001.455676291</v>
       </c>
       <c r="L2" s="11">
         <f>'QTR BS'!AP2</f>
-        <v>16272810.332884535</v>
+        <v>16529323.216993876</v>
       </c>
       <c r="M2" s="5"/>
     </row>
@@ -22283,23 +22303,23 @@
       </c>
       <c r="H8" s="7">
         <f t="shared" si="0"/>
-        <v>7874422.5127534289</v>
+        <v>7910557.7266078629</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" si="0"/>
-        <v>10795628.551794514</v>
+        <v>10874260.627414286</v>
       </c>
       <c r="J8" s="7">
         <f t="shared" si="0"/>
-        <v>14196507.686255559</v>
+        <v>14325118.247326607</v>
       </c>
       <c r="K8" s="7">
         <f t="shared" si="0"/>
-        <v>18161506.942178532</v>
+        <v>18348894.76124562</v>
       </c>
       <c r="L8" s="7">
         <f t="shared" si="0"/>
-        <v>22789940.346226081</v>
+        <v>23046453.230335422</v>
       </c>
       <c r="M8" s="7">
         <f t="shared" si="0"/>
@@ -22600,23 +22620,23 @@
       </c>
       <c r="H15" s="7">
         <f t="shared" si="1"/>
-        <v>12581700.122867659</v>
+        <v>12617835.336722095</v>
       </c>
       <c r="I15" s="7">
         <f t="shared" si="1"/>
-        <v>15598948.450948428</v>
+        <v>15677580.5265682</v>
       </c>
       <c r="J15" s="7">
         <f t="shared" si="1"/>
-        <v>19115422.52416908</v>
+        <v>19244033.085240126</v>
       </c>
       <c r="K15" s="7">
         <f t="shared" si="1"/>
-        <v>23219011.636098877</v>
+        <v>23406399.455165967</v>
       </c>
       <c r="L15" s="7">
         <f t="shared" si="1"/>
-        <v>28013078.096270941</v>
+        <v>28269590.980380282</v>
       </c>
       <c r="M15" s="7">
         <f t="shared" si="1"/>
@@ -24380,23 +24400,23 @@
       </c>
       <c r="I20" s="11">
         <f>'QTR CF'!Z22+'QTR CF'!AA22+'QTR CF'!AB22+'QTR CF'!AC22</f>
-        <v>0</v>
+        <v>36135.213854432674</v>
       </c>
       <c r="J20" s="11">
         <f>'QTR CF'!AD22+'QTR CF'!AE22+'QTR CF'!AF22+'QTR CF'!AG22</f>
-        <v>0</v>
+        <v>42496.861765340975</v>
       </c>
       <c r="K20" s="11">
         <f>'QTR CF'!AH22+'QTR CF'!AI22+'QTR CF'!AJ22+'QTR CF'!AK22</f>
-        <v>0</v>
+        <v>49978.485451275803</v>
       </c>
       <c r="L20" s="11">
         <f>'QTR CF'!AL22+'QTR CF'!AM22+'QTR CF'!AN22+'QTR CF'!AO22</f>
-        <v>0</v>
+        <v>58777.257996037399</v>
       </c>
       <c r="M20" s="11">
         <f>'QTR CF'!AP22+'QTR CF'!AQ22+'QTR CF'!AR22+'QTR CF'!AS22</f>
-        <v>0</v>
+        <v>69125.065042253205</v>
       </c>
       <c r="N20" s="5"/>
     </row>
@@ -24481,23 +24501,23 @@
       </c>
       <c r="I22" s="7">
         <f t="shared" si="0"/>
-        <v>2170631.2563160751</v>
+        <v>2206766.4701705077</v>
       </c>
       <c r="J22" s="7">
         <f t="shared" si="0"/>
-        <v>2535850.1572036459</v>
+        <v>2578347.0189689868</v>
       </c>
       <c r="K22" s="7">
         <f t="shared" si="0"/>
-        <v>2965366.2853669473</v>
+        <v>3015344.7708182232</v>
       </c>
       <c r="L22" s="7">
         <f t="shared" si="0"/>
-        <v>3470499.2450907002</v>
+        <v>3529276.5030867378</v>
       </c>
       <c r="M22" s="7">
         <f t="shared" si="0"/>
-        <v>4064561.4706243305</v>
+        <v>4133686.5356665836</v>
       </c>
       <c r="N22" s="7">
         <f t="shared" si="0"/>
@@ -25357,23 +25377,23 @@
       </c>
       <c r="I40" s="7">
         <f t="shared" si="3"/>
-        <v>2056330.1847983776</v>
+        <v>2092465.3986528101</v>
       </c>
       <c r="J40" s="7">
         <f t="shared" si="3"/>
-        <v>2383740.8446478024</v>
+        <v>2426237.7064131433</v>
       </c>
       <c r="K40" s="7">
         <f t="shared" si="3"/>
-        <v>2768792.5454117982</v>
+        <v>2818771.0308630741</v>
       </c>
       <c r="L40" s="7">
         <f t="shared" si="3"/>
-        <v>3221633.0617512278</v>
+        <v>3280410.3197472654</v>
       </c>
       <c r="M40" s="7">
         <f t="shared" si="3"/>
-        <v>3754196.6962753325</v>
+        <v>3823321.7613175856</v>
       </c>
       <c r="N40" s="7">
         <f t="shared" si="3"/>
@@ -33799,83 +33819,83 @@
       </c>
       <c r="W2" s="11">
         <f>'BS DRIVERS'!W2</f>
-        <v>2580327.4950840767</v>
+        <v>2585143.4922486003</v>
       </c>
       <c r="X2" s="11">
         <f>'BS DRIVERS'!X2</f>
-        <v>2936716.4829764888</v>
+        <v>2970647.3051565615</v>
       </c>
       <c r="Y2" s="11">
         <f>'BS DRIVERS'!Y2</f>
-        <v>3477516.2400014186</v>
+        <v>3521137.2784580542</v>
       </c>
       <c r="Z2" s="11">
         <f>'BS DRIVERS'!Z2</f>
-        <v>4144447.1847983776</v>
+        <v>4180582.3986528106</v>
       </c>
       <c r="AA2" s="11">
         <f>'BS DRIVERS'!AA2</f>
-        <v>4714659.743908925</v>
+        <v>4756458.8170278277</v>
       </c>
       <c r="AB2" s="11">
         <f>'BS DRIVERS'!AB2</f>
-        <v>5125139.2559386836</v>
+        <v>5201178.8540754309</v>
       </c>
       <c r="AC2" s="11">
         <f>'BS DRIVERS'!AC2</f>
-        <v>5752495.2750630165</v>
+        <v>5839931.0637201872</v>
       </c>
       <c r="AD2" s="11">
         <f>'BS DRIVERS'!AD2</f>
-        <v>6528188.0294461809</v>
+        <v>6606820.1050659539</v>
       </c>
       <c r="AE2" s="11">
         <f>'BS DRIVERS'!AE2</f>
-        <v>7190135.009880417</v>
+        <v>7275428.074008246</v>
       </c>
       <c r="AF2" s="11">
         <f>'BS DRIVERS'!AF2</f>
-        <v>7664227.7479544347</v>
+        <v>7789789.4227598654</v>
       </c>
       <c r="AG2" s="11">
         <f>'BS DRIVERS'!AG2</f>
-        <v>8393378.3633465767</v>
+        <v>8532342.5417361539</v>
       </c>
       <c r="AH2" s="11">
         <f>'BS DRIVERS'!AH2</f>
-        <v>9296980.5748579782</v>
+        <v>9425591.1359290257</v>
       </c>
       <c r="AI2" s="11">
         <f>'BS DRIVERS'!AI2</f>
-        <v>10066811.931950973</v>
+        <v>10203256.15657768</v>
       </c>
       <c r="AJ2" s="11">
         <f>'BS DRIVERS'!AJ2</f>
-        <v>10615717.081113534</v>
+        <v>10799519.253816657</v>
       </c>
       <c r="AK2" s="11">
         <f>'BS DRIVERS'!AK2</f>
-        <v>11464583.35402132</v>
+        <v>11664147.557203062</v>
       </c>
       <c r="AL2" s="11">
         <f>'BS DRIVERS'!AL2</f>
-        <v>12518613.636609204</v>
+        <v>12706001.455676291</v>
       </c>
       <c r="AM2" s="11">
         <f>'BS DRIVERS'!AM2</f>
-        <v>13415322.544779563</v>
+        <v>13611923.153304106</v>
       </c>
       <c r="AN2" s="11">
         <f>'BS DRIVERS'!AN2</f>
-        <v>14052210.920087378</v>
+        <v>14304506.900472762</v>
       </c>
       <c r="AO2" s="11">
         <f>'BS DRIVERS'!AO2</f>
-        <v>15041868.936170781</v>
+        <v>15312701.871480227</v>
       </c>
       <c r="AP2" s="11">
         <f>'BS DRIVERS'!AP2</f>
-        <v>16272810.332884535</v>
+        <v>16529323.216993876</v>
       </c>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.25">
@@ -34813,83 +34833,83 @@
       </c>
       <c r="W8" s="7">
         <f t="shared" ref="W8:AP8" si="0">SUM(W2:W7)</f>
-        <v>5914203.2479826044</v>
+        <v>5919019.2451471277</v>
       </c>
       <c r="X8" s="7">
         <f t="shared" si="0"/>
-        <v>6638812.4864223273</v>
+        <v>6672743.3086024001</v>
       </c>
       <c r="Y8" s="7">
         <f t="shared" si="0"/>
-        <v>7302166.0923303673</v>
+        <v>7345787.1307870029</v>
       </c>
       <c r="Z8" s="7">
         <f t="shared" si="0"/>
-        <v>7874422.5127534289</v>
+        <v>7910557.7266078629</v>
       </c>
       <c r="AA8" s="7">
         <f t="shared" si="0"/>
-        <v>8516266.8840529192</v>
+        <v>8558065.957171822</v>
       </c>
       <c r="AB8" s="7">
         <f t="shared" si="0"/>
-        <v>9359792.2651273627</v>
+        <v>9435831.8632641099</v>
       </c>
       <c r="AC8" s="7">
         <f t="shared" si="0"/>
-        <v>10131277.885802597</v>
+        <v>10218713.674459768</v>
       </c>
       <c r="AD8" s="7">
         <f t="shared" si="0"/>
-        <v>10795628.551794514</v>
+        <v>10874260.627414286</v>
       </c>
       <c r="AE8" s="7">
         <f t="shared" si="0"/>
-        <v>11541818.211208247</v>
+        <v>11627111.275336076</v>
       </c>
       <c r="AF8" s="7">
         <f t="shared" si="0"/>
-        <v>12525195.065019868</v>
+        <v>12650756.739825297</v>
       </c>
       <c r="AG8" s="7">
         <f t="shared" si="0"/>
-        <v>13423849.471868083</v>
+        <v>13562813.65025766</v>
       </c>
       <c r="AH8" s="7">
         <f t="shared" si="0"/>
-        <v>14196507.686255559</v>
+        <v>14325118.247326607</v>
       </c>
       <c r="AI8" s="7">
         <f t="shared" si="0"/>
-        <v>15065412.74740232</v>
+        <v>15201856.972029027</v>
       </c>
       <c r="AJ8" s="7">
         <f t="shared" si="0"/>
-        <v>16213262.094127169</v>
+        <v>16397064.266830293</v>
       </c>
       <c r="AK8" s="7">
         <f t="shared" si="0"/>
-        <v>17261473.505083065</v>
+        <v>17461037.708264805</v>
       </c>
       <c r="AL8" s="7">
         <f t="shared" si="0"/>
-        <v>18161506.942178532</v>
+        <v>18348894.76124562</v>
       </c>
       <c r="AM8" s="7">
         <f t="shared" si="0"/>
-        <v>19174731.599299874</v>
+        <v>19371332.207824416</v>
       </c>
       <c r="AN8" s="7">
         <f t="shared" si="0"/>
-        <v>20516009.019363139</v>
+        <v>20768304.999748524</v>
       </c>
       <c r="AO8" s="7">
         <f t="shared" si="0"/>
-        <v>21740107.125087362</v>
+        <v>22010940.060396809</v>
       </c>
       <c r="AP8" s="7">
         <f t="shared" si="0"/>
-        <v>22789940.346226081</v>
+        <v>23046453.230335422</v>
       </c>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.25">
@@ -35996,83 +36016,83 @@
       </c>
       <c r="W15" s="7">
         <f t="shared" ref="W15:AP15" si="1">W8+SUM(W9:W14)</f>
-        <v>10549140.984553687</v>
+        <v>10553956.981718209</v>
       </c>
       <c r="X15" s="7">
         <f t="shared" si="1"/>
-        <v>11356791.114141569</v>
+        <v>11390721.936321642</v>
       </c>
       <c r="Y15" s="7">
         <f t="shared" si="1"/>
-        <v>12041777.866520908</v>
+        <v>12085398.904977543</v>
       </c>
       <c r="Z15" s="7">
         <f t="shared" si="1"/>
-        <v>12581700.122867659</v>
+        <v>12617835.336722095</v>
       </c>
       <c r="AA15" s="7">
         <f t="shared" si="1"/>
-        <v>13232528.171004493</v>
+        <v>13274327.244123396</v>
       </c>
       <c r="AB15" s="7">
         <f t="shared" si="1"/>
-        <v>14174374.964378081</v>
+        <v>14250414.562514829</v>
       </c>
       <c r="AC15" s="7">
         <f t="shared" si="1"/>
-        <v>14971963.345281754</v>
+        <v>15059399.133938927</v>
       </c>
       <c r="AD15" s="7">
         <f t="shared" si="1"/>
-        <v>15598948.450948428</v>
+        <v>15677580.5265682</v>
       </c>
       <c r="AE15" s="7">
         <f t="shared" si="1"/>
-        <v>16356364.446595863</v>
+        <v>16441657.510723691</v>
       </c>
       <c r="AF15" s="7">
         <f t="shared" si="1"/>
-        <v>17456033.388006125</v>
+        <v>17581595.062811553</v>
       </c>
       <c r="AG15" s="7">
         <f t="shared" si="1"/>
-        <v>18386047.049723901</v>
+        <v>18525011.22811348</v>
       </c>
       <c r="AH15" s="7">
         <f t="shared" si="1"/>
-        <v>19115422.52416908</v>
+        <v>19244033.085240126</v>
       </c>
       <c r="AI15" s="7">
         <f t="shared" si="1"/>
-        <v>19998191.403833099</v>
+        <v>20134635.628459804</v>
       </c>
       <c r="AJ15" s="7">
         <f t="shared" si="1"/>
-        <v>21283467.272481762</v>
+        <v>21467269.445184886</v>
       </c>
       <c r="AK15" s="7">
         <f t="shared" si="1"/>
-        <v>22369219.845159464</v>
+        <v>22568784.048341203</v>
       </c>
       <c r="AL15" s="7">
         <f t="shared" si="1"/>
-        <v>23219011.636098877</v>
+        <v>23406399.455165967</v>
       </c>
       <c r="AM15" s="7">
         <f t="shared" si="1"/>
-        <v>24249201.925952956</v>
+        <v>24445802.534477498</v>
       </c>
       <c r="AN15" s="7">
         <f t="shared" si="1"/>
-        <v>25752761.044876959</v>
+        <v>26005057.025262345</v>
       </c>
       <c r="AO15" s="7">
         <f t="shared" si="1"/>
-        <v>27021670.551320449</v>
+        <v>27292503.486629896</v>
       </c>
       <c r="AP15" s="7">
         <f t="shared" si="1"/>
-        <v>28013078.096270941</v>
+        <v>28269590.980380282</v>
       </c>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">

--- a/Knowledge/Model Outputs/MNST/MNST_model.xlsx
+++ b/Knowledge/Model Outputs/MNST/MNST_model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rodin\Desktop\Brain\Knowledge\Model Outputs\MNST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A5A73C-4B0C-4130-BC1E-E73248AE8B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02353A0E-DD92-4A98-89C3-92CCC41B09CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASSUMPTIONS" sheetId="1" r:id="rId1"/>
@@ -491,9 +491,6 @@
     <t>Net Sales / Revenue — Growth %</t>
   </si>
   <si>
-    <t>YoY</t>
-  </si>
-  <si>
     <t>COGS — % of Revenue</t>
   </si>
   <si>
@@ -553,6 +550,9 @@
   <si>
     <t>Purchase of PP&amp;E — % of Revenue</t>
   </si>
+  <si>
+    <t>QoQ</t>
+  </si>
 </sst>
 </file>
 
@@ -578,11 +578,13 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1238,83 +1240,83 @@
       </c>
       <c r="Z2" s="11">
         <f>'CF DRIVERS'!Z2</f>
-        <v>459253.84532008163</v>
+        <v>453479.13148567535</v>
       </c>
       <c r="AA2" s="11">
         <f>'CF DRIVERS'!AA2</f>
-        <v>520094.22488594597</v>
+        <v>457811.15428620751</v>
       </c>
       <c r="AB2" s="11">
         <f>'CF DRIVERS'!AB2</f>
-        <v>540343.58018952655</v>
+        <v>462186.49731474504</v>
       </c>
       <c r="AC2" s="11">
         <f>'CF DRIVERS'!AC2</f>
-        <v>524700.67627654527</v>
+        <v>466605.59377356787</v>
       </c>
       <c r="AD2" s="11">
         <f>'CF DRIVERS'!AD2</f>
-        <v>536536.27368350013</v>
+        <v>471068.88119697862</v>
       </c>
       <c r="AE2" s="11">
         <f>'CF DRIVERS'!AE2</f>
-        <v>608087.67533223424</v>
+        <v>475576.80149462388</v>
       </c>
       <c r="AF2" s="11">
         <f>'CF DRIVERS'!AF2</f>
-        <v>631901.95402005711</v>
+        <v>480129.80099524569</v>
       </c>
       <c r="AG2" s="11">
         <f>'CF DRIVERS'!AG2</f>
-        <v>613505.09803695814</v>
+        <v>484728.33049087337</v>
       </c>
       <c r="AH2" s="11">
         <f>'CF DRIVERS'!AH2</f>
-        <v>627424.36661911674</v>
+        <v>489372.84528145753</v>
       </c>
       <c r="AI2" s="11">
         <f>'CF DRIVERS'!AI2</f>
-        <v>711572.47868597391</v>
+        <v>494063.80521994748</v>
       </c>
       <c r="AJ2" s="11">
         <f>'CF DRIVERS'!AJ2</f>
-        <v>739579.28981249977</v>
+        <v>498801.67475782236</v>
       </c>
       <c r="AK2" s="11">
         <f>'CF DRIVERS'!AK2</f>
-        <v>717943.64518119651</v>
+        <v>503586.92299107614</v>
       </c>
       <c r="AL2" s="11">
         <f>'CF DRIVERS'!AL2</f>
-        <v>734313.41775798448</v>
+        <v>508420.02370666212</v>
       </c>
       <c r="AM2" s="11">
         <f>'CF DRIVERS'!AM2</f>
-        <v>833275.90628027054</v>
+        <v>513301.45542940422</v>
       </c>
       <c r="AN2" s="11">
         <f>'CF DRIVERS'!AN2</f>
-        <v>866213.35022972664</v>
+        <v>518231.70146937354</v>
       </c>
       <c r="AO2" s="11">
         <f>'CF DRIVERS'!AO2</f>
-        <v>840768.72430875013</v>
+        <v>523211.24996974273</v>
       </c>
       <c r="AP2" s="11">
         <f>'CF DRIVERS'!AP2</f>
-        <v>860020.41505916975</v>
+        <v>528240.59395511542</v>
       </c>
       <c r="AQ2" s="11">
         <f>'CF DRIVERS'!AQ2</f>
-        <v>976405.36885043816</v>
+        <v>533320.23138034204</v>
       </c>
       <c r="AR2" s="11">
         <f>'CF DRIVERS'!AR2</f>
-        <v>1015141.4894684708</v>
+        <v>538450.66517982085</v>
       </c>
       <c r="AS2" s="11">
         <f>'CF DRIVERS'!AS2</f>
-        <v>985217.30651522917</v>
+        <v>543632.40331729432</v>
       </c>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.25">
@@ -1419,83 +1421,83 @@
       </c>
       <c r="Z3" s="11">
         <f>'QTR P&amp;L'!Z2*'CF DRIVERS'!Z3</f>
-        <v>33178.64289163435</v>
+        <v>32742.179999999997</v>
       </c>
       <c r="AA3" s="11">
         <f>'QTR P&amp;L'!AA2*'CF DRIVERS'!AA3</f>
-        <v>37777.064346778025</v>
+        <v>33069.601799999997</v>
       </c>
       <c r="AB3" s="11">
         <f>'QTR P&amp;L'!AB2*'CF DRIVERS'!AB3</f>
-        <v>39307.545756414998</v>
+        <v>33400.297817999999</v>
       </c>
       <c r="AC3" s="11">
         <f>'QTR P&amp;L'!AC2*'CF DRIVERS'!AC3</f>
-        <v>38125.227935791736</v>
+        <v>33734.300796179996</v>
       </c>
       <c r="AD3" s="11">
         <f>'QTR P&amp;L'!AD2*'CF DRIVERS'!AD3</f>
-        <v>39019.78292441841</v>
+        <v>34071.643804141793</v>
       </c>
       <c r="AE3" s="11">
         <f>'QTR P&amp;L'!AE2*'CF DRIVERS'!AE3</f>
-        <v>44427.762013880674</v>
+        <v>34412.360242183218</v>
       </c>
       <c r="AF3" s="11">
         <f>'QTR P&amp;L'!AF2*'CF DRIVERS'!AF3</f>
-        <v>46227.686518597235</v>
+        <v>34756.483844605056</v>
       </c>
       <c r="AG3" s="11">
         <f>'QTR P&amp;L'!AG2*'CF DRIVERS'!AG3</f>
-        <v>44837.220221977754</v>
+        <v>35104.0486830511</v>
       </c>
       <c r="AH3" s="11">
         <f>'QTR P&amp;L'!AH2*'CF DRIVERS'!AH3</f>
-        <v>45889.262693521079</v>
+        <v>35455.089169881612</v>
       </c>
       <c r="AI3" s="11">
         <f>'QTR P&amp;L'!AI2*'CF DRIVERS'!AI3</f>
-        <v>52249.323013643989</v>
+        <v>35809.64006158043</v>
       </c>
       <c r="AJ3" s="11">
         <f>'QTR P&amp;L'!AJ2*'CF DRIVERS'!AJ3</f>
-        <v>54366.126394775936</v>
+        <v>36167.736462196233</v>
       </c>
       <c r="AK3" s="11">
         <f>'QTR P&amp;L'!AK2*'CF DRIVERS'!AK3</f>
-        <v>52730.866832321313</v>
+        <v>36529.4138268182</v>
       </c>
       <c r="AL3" s="11">
         <f>'QTR P&amp;L'!AL2*'CF DRIVERS'!AL3</f>
-        <v>53968.122647785654</v>
+        <v>36894.707965086382</v>
       </c>
       <c r="AM3" s="11">
         <f>'QTR P&amp;L'!AM2*'CF DRIVERS'!AM3</f>
-        <v>61447.87924566555</v>
+        <v>37263.65504473725</v>
       </c>
       <c r="AN3" s="11">
         <f>'QTR P&amp;L'!AN2*'CF DRIVERS'!AN3</f>
-        <v>63937.34841097219</v>
+        <v>37636.291595184623</v>
       </c>
       <c r="AO3" s="11">
         <f>'QTR P&amp;L'!AO2*'CF DRIVERS'!AO3</f>
-        <v>62014.199433466922</v>
+        <v>38012.654511136468</v>
       </c>
       <c r="AP3" s="11">
         <f>'QTR P&amp;L'!AP2*'CF DRIVERS'!AP3</f>
-        <v>63469.27562507226</v>
+        <v>38392.781056247826</v>
       </c>
       <c r="AQ3" s="11">
         <f>'QTR P&amp;L'!AQ2*'CF DRIVERS'!AQ3</f>
-        <v>72265.852378678683</v>
+        <v>38776.70886681031</v>
       </c>
       <c r="AR3" s="11">
         <f>'QTR P&amp;L'!AR2*'CF DRIVERS'!AR3</f>
-        <v>75193.595588205528</v>
+        <v>39164.475955478418</v>
       </c>
       <c r="AS3" s="11">
         <f>'QTR P&amp;L'!AS2*'CF DRIVERS'!AS3</f>
-        <v>72931.873917470963</v>
+        <v>39556.120715033205</v>
       </c>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.25">
@@ -2505,83 +2507,83 @@
       </c>
       <c r="Z9" s="11">
         <f>'QTR P&amp;L'!Z2*'CF DRIVERS'!Z9</f>
-        <v>39938.619950652334</v>
+        <v>39413.229999999996</v>
       </c>
       <c r="AA9" s="11">
         <f>'QTR P&amp;L'!AA2*'CF DRIVERS'!AA9</f>
-        <v>45473.946017777744</v>
+        <v>39807.362300000001</v>
       </c>
       <c r="AB9" s="11">
         <f>'QTR P&amp;L'!AB2*'CF DRIVERS'!AB9</f>
-        <v>47316.255106810495</v>
+        <v>40205.435922999997</v>
       </c>
       <c r="AC9" s="11">
         <f>'QTR P&amp;L'!AC2*'CF DRIVERS'!AC9</f>
-        <v>45893.04613913261</v>
+        <v>40607.490282229999</v>
       </c>
       <c r="AD9" s="11">
         <f>'QTR P&amp;L'!AD2*'CF DRIVERS'!AD9</f>
-        <v>46969.862084631372</v>
+        <v>41013.565185052299</v>
       </c>
       <c r="AE9" s="11">
         <f>'QTR P&amp;L'!AE2*'CF DRIVERS'!AE9</f>
-        <v>53479.688971178533</v>
+        <v>41423.700836902826</v>
       </c>
       <c r="AF9" s="11">
         <f>'QTR P&amp;L'!AF2*'CF DRIVERS'!AF9</f>
-        <v>55646.338793732488</v>
+        <v>41837.937845271852</v>
       </c>
       <c r="AG9" s="11">
         <f>'QTR P&amp;L'!AG2*'CF DRIVERS'!AG9</f>
-        <v>53972.572173552893</v>
+        <v>42256.317223724567</v>
       </c>
       <c r="AH9" s="11">
         <f>'QTR P&amp;L'!AH2*'CF DRIVERS'!AH9</f>
-        <v>55238.962862893241</v>
+        <v>42678.880395961809</v>
       </c>
       <c r="AI9" s="11">
         <f>'QTR P&amp;L'!AI2*'CF DRIVERS'!AI9</f>
-        <v>62894.852611556213</v>
+        <v>43105.669199921438</v>
       </c>
       <c r="AJ9" s="11">
         <f>'QTR P&amp;L'!AJ2*'CF DRIVERS'!AJ9</f>
-        <v>65442.943744319251</v>
+        <v>43536.725891920651</v>
       </c>
       <c r="AK9" s="11">
         <f>'QTR P&amp;L'!AK2*'CF DRIVERS'!AK9</f>
-        <v>63474.508495208676</v>
+        <v>43972.093150839864</v>
       </c>
       <c r="AL9" s="11">
         <f>'QTR P&amp;L'!AL2*'CF DRIVERS'!AL9</f>
-        <v>64963.848790318334</v>
+        <v>44411.814082348261</v>
       </c>
       <c r="AM9" s="11">
         <f>'QTR P&amp;L'!AM2*'CF DRIVERS'!AM9</f>
-        <v>73967.567147992071</v>
+        <v>44855.932223171745</v>
       </c>
       <c r="AN9" s="11">
         <f>'QTR P&amp;L'!AN2*'CF DRIVERS'!AN9</f>
-        <v>76964.252792935033</v>
+        <v>45304.491545403464</v>
       </c>
       <c r="AO9" s="11">
         <f>'QTR P&amp;L'!AO2*'CF DRIVERS'!AO9</f>
-        <v>74649.272147948053</v>
+        <v>45757.536460857496</v>
       </c>
       <c r="AP9" s="11">
         <f>'QTR P&amp;L'!AP2*'CF DRIVERS'!AP9</f>
-        <v>76400.812595385127</v>
+        <v>46215.111825466069</v>
       </c>
       <c r="AQ9" s="11">
         <f>'QTR P&amp;L'!AQ2*'CF DRIVERS'!AQ9</f>
-        <v>86989.646411659531</v>
+        <v>46677.262943720736</v>
       </c>
       <c r="AR9" s="11">
         <f>'QTR P&amp;L'!AR2*'CF DRIVERS'!AR9</f>
-        <v>90513.90217282201</v>
+        <v>47144.035573157948</v>
       </c>
       <c r="AS9" s="11">
         <f>'QTR P&amp;L'!AS2*'CF DRIVERS'!AS9</f>
-        <v>87791.366397725622</v>
+        <v>47615.475928889529</v>
       </c>
     </row>
     <row r="10" spans="1:45" x14ac:dyDescent="0.25">
@@ -2867,83 +2869,83 @@
       </c>
       <c r="Z11" s="11">
         <f>'CF DRIVERS'!Z11</f>
-        <v>-37965.789529045112</v>
+        <v>-16180.719999999739</v>
       </c>
       <c r="AA11" s="11">
         <f>'CF DRIVERS'!AA11</f>
-        <v>-229519.92722460465</v>
+        <v>-16342.527200000361</v>
       </c>
       <c r="AB11" s="11">
         <f>'CF DRIVERS'!AB11</f>
-        <v>-76390.558191563701</v>
+        <v>-16505.952471999917</v>
       </c>
       <c r="AC11" s="11">
         <f>'CF DRIVERS'!AC11</f>
-        <v>59012.750960932579</v>
+        <v>-16671.011996719986</v>
       </c>
       <c r="AD11" s="11">
         <f>'CF DRIVERS'!AD11</f>
-        <v>-44649.712491737213</v>
+        <v>-16837.722116687102</v>
       </c>
       <c r="AE11" s="11">
         <f>'CF DRIVERS'!AE11</f>
-        <v>-269927.18678648863</v>
+        <v>-17006.09933785419</v>
       </c>
       <c r="AF11" s="11">
         <f>'CF DRIVERS'!AF11</f>
-        <v>-89839.207946070936</v>
+        <v>-17176.160331232939</v>
       </c>
       <c r="AG11" s="11">
         <f>'CF DRIVERS'!AG11</f>
-        <v>69402.016827185173</v>
+        <v>-17347.921934544574</v>
       </c>
       <c r="AH11" s="11">
         <f>'CF DRIVERS'!AH11</f>
-        <v>-52510.348140386865</v>
+        <v>-17521.401153890416</v>
       </c>
       <c r="AI11" s="11">
         <f>'CF DRIVERS'!AI11</f>
-        <v>-317448.19305021642</v>
+        <v>-17696.615165429423</v>
       </c>
       <c r="AJ11" s="11">
         <f>'CF DRIVERS'!AJ11</f>
-        <v>-105655.50868390873</v>
+        <v>-17873.58131708391</v>
       </c>
       <c r="AK11" s="11">
         <f>'CF DRIVERS'!AK11</f>
-        <v>81620.325459315442</v>
+        <v>-18052.317130254582</v>
       </c>
       <c r="AL11" s="11">
         <f>'CF DRIVERS'!AL11</f>
-        <v>-61754.85816028202</v>
+        <v>-18232.840301556746</v>
       </c>
       <c r="AM11" s="11">
         <f>'CF DRIVERS'!AM11</f>
-        <v>-373335.32968859002</v>
+        <v>-18415.168704572599</v>
       </c>
       <c r="AN11" s="11">
         <f>'CF DRIVERS'!AN11</f>
-        <v>-124256.28821167396</v>
+        <v>-18599.320391618414</v>
       </c>
       <c r="AO11" s="11">
         <f>'CF DRIVERS'!AO11</f>
-        <v>95989.682038679253</v>
+        <v>-18785.313595534302</v>
       </c>
       <c r="AP11" s="11">
         <f>'CF DRIVERS'!AP11</f>
-        <v>-72626.875300858635</v>
+        <v>-18973.166731489589</v>
       </c>
       <c r="AQ11" s="11">
         <f>'CF DRIVERS'!AQ11</f>
-        <v>-439061.46402805392</v>
+        <v>-19162.898398805177</v>
       </c>
       <c r="AR11" s="11">
         <f>'CF DRIVERS'!AR11</f>
-        <v>-146131.75737323426</v>
+        <v>-19354.527382792672</v>
       </c>
       <c r="AS11" s="11">
         <f>'CF DRIVERS'!AS11</f>
-        <v>112888.78114654869</v>
+        <v>-19548.072656620992</v>
       </c>
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.25">
@@ -3205,83 +3207,83 @@
       </c>
       <c r="Z13" s="11">
         <f>'CF DRIVERS'!Z13</f>
-        <v>-18762.031924774405</v>
+        <v>-7996.229999999865</v>
       </c>
       <c r="AA13" s="11">
         <f>'CF DRIVERS'!AA13</f>
-        <v>-113424.75042341754</v>
+        <v>-8076.192300000228</v>
       </c>
       <c r="AB13" s="11">
         <f>'CF DRIVERS'!AB13</f>
-        <v>-37750.88334314723</v>
+        <v>-8156.9542229999788</v>
       </c>
       <c r="AC13" s="11">
         <f>'CF DRIVERS'!AC13</f>
-        <v>29163.073683763272</v>
+        <v>-8238.5237652298529</v>
       </c>
       <c r="AD13" s="11">
         <f>'CF DRIVERS'!AD13</f>
-        <v>-22065.110237233341</v>
+        <v>-8320.9090028823121</v>
       </c>
       <c r="AE13" s="11">
         <f>'CF DRIVERS'!AE13</f>
-        <v>-133393.31431467354</v>
+        <v>-8404.1180929112015</v>
       </c>
       <c r="AF13" s="11">
         <f>'CF DRIVERS'!AF13</f>
-        <v>-44396.971813034965</v>
+        <v>-8488.1592738402542</v>
       </c>
       <c r="AG13" s="11">
         <f>'CF DRIVERS'!AG13</f>
-        <v>34297.267922196537</v>
+        <v>-8573.0408665786963</v>
       </c>
       <c r="AH13" s="11">
         <f>'CF DRIVERS'!AH13</f>
-        <v>-25949.699463967467</v>
+        <v>-8658.771275244304</v>
       </c>
       <c r="AI13" s="11">
         <f>'CF DRIVERS'!AI13</f>
-        <v>-156877.36792392004</v>
+        <v>-8745.3589879969368</v>
       </c>
       <c r="AJ13" s="11">
         <f>'CF DRIVERS'!AJ13</f>
-        <v>-52213.112160863588</v>
+        <v>-8832.8125778769609</v>
       </c>
       <c r="AK13" s="11">
         <f>'CF DRIVERS'!AK13</f>
-        <v>40335.343238591449</v>
+        <v>-8921.1407036555465</v>
       </c>
       <c r="AL13" s="11">
         <f>'CF DRIVERS'!AL13</f>
-        <v>-30518.17530165473</v>
+        <v>-9010.3521106922999</v>
       </c>
       <c r="AM13" s="11">
         <f>'CF DRIVERS'!AM13</f>
-        <v>-184495.81744914898</v>
+        <v>-9100.4556317990646</v>
       </c>
       <c r="AN13" s="11">
         <f>'CF DRIVERS'!AN13</f>
-        <v>-61405.293428650592</v>
+        <v>-9191.4601881169947</v>
       </c>
       <c r="AO13" s="11">
         <f>'CF DRIVERS'!AO13</f>
-        <v>47436.428985122358</v>
+        <v>-9283.3747899982845</v>
       </c>
       <c r="AP13" s="11">
         <f>'CF DRIVERS'!AP13</f>
-        <v>-35890.936811649241</v>
+        <v>-9376.2085378981428</v>
       </c>
       <c r="AQ13" s="11">
         <f>'CF DRIVERS'!AQ13</f>
-        <v>-216976.52826975845</v>
+        <v>-9469.9706232773606</v>
       </c>
       <c r="AR13" s="11">
         <f>'CF DRIVERS'!AR13</f>
-        <v>-72215.76927729859</v>
+        <v>-9564.6703295101179</v>
       </c>
       <c r="AS13" s="11">
         <f>'CF DRIVERS'!AS13</f>
-        <v>55787.669428027002</v>
+        <v>-9660.3170328051783</v>
       </c>
     </row>
     <row r="14" spans="1:45" x14ac:dyDescent="0.25">
@@ -3386,83 +3388,83 @@
       </c>
       <c r="Z14" s="11">
         <f>'CF DRIVERS'!Z14</f>
-        <v>-2429.6789460061991</v>
+        <v>-1035.5099999999948</v>
       </c>
       <c r="AA14" s="11">
         <f>'CF DRIVERS'!AA14</f>
-        <v>-14688.479860003165</v>
+        <v>-1045.86510000001</v>
       </c>
       <c r="AB14" s="11">
         <f>'CF DRIVERS'!AB14</f>
-        <v>-4888.7309658004233</v>
+        <v>-1056.323750999989</v>
       </c>
       <c r="AC14" s="11">
         <f>'CF DRIVERS'!AC14</f>
-        <v>3776.611531968636</v>
+        <v>-1066.8869885099994</v>
       </c>
       <c r="AD14" s="11">
         <f>'CF DRIVERS'!AD14</f>
-        <v>-2857.4268501227925</v>
+        <v>-1077.555858395106</v>
       </c>
       <c r="AE14" s="11">
         <f>'CF DRIVERS'!AE14</f>
-        <v>-17274.404426334368</v>
+        <v>-1088.3314169790538</v>
       </c>
       <c r="AF14" s="11">
         <f>'CF DRIVERS'!AF14</f>
-        <v>-5749.397939043236</v>
+        <v>-1099.2147311488516</v>
       </c>
       <c r="AG14" s="11">
         <f>'CF DRIVERS'!AG14</f>
-        <v>4441.4885397385515</v>
+        <v>-1110.206878460318</v>
       </c>
       <c r="AH14" s="11">
         <f>'CF DRIVERS'!AH14</f>
-        <v>-3360.4802878272312</v>
+        <v>-1121.3089472449356</v>
       </c>
       <c r="AI14" s="11">
         <f>'CF DRIVERS'!AI14</f>
-        <v>-20315.584126381873</v>
+        <v>-1132.5220367173897</v>
       </c>
       <c r="AJ14" s="11">
         <f>'CF DRIVERS'!AJ14</f>
-        <v>-6761.5863692885032</v>
+        <v>-1143.8472570845624</v>
       </c>
       <c r="AK14" s="11">
         <f>'CF DRIVERS'!AK14</f>
-        <v>5223.4179453309334</v>
+        <v>-1155.2857296554139</v>
       </c>
       <c r="AL14" s="11">
         <f>'CF DRIVERS'!AL14</f>
-        <v>-3952.0968889859796</v>
+        <v>-1166.8385869519552</v>
       </c>
       <c r="AM14" s="11">
         <f>'CF DRIVERS'!AM14</f>
-        <v>-23892.167174627102</v>
+        <v>-1178.5069728214876</v>
       </c>
       <c r="AN14" s="11">
         <f>'CF DRIVERS'!AN14</f>
-        <v>-7951.9717914944631</v>
+        <v>-1190.292042549685</v>
       </c>
       <c r="AO14" s="11">
         <f>'CF DRIVERS'!AO14</f>
-        <v>6143.0069643299503</v>
+        <v>-1202.1949629751907</v>
       </c>
       <c r="AP14" s="11">
         <f>'CF DRIVERS'!AP14</f>
-        <v>-4647.8683051676489</v>
+        <v>-1214.2169126049266</v>
       </c>
       <c r="AQ14" s="11">
         <f>'CF DRIVERS'!AQ14</f>
-        <v>-28098.411975220544</v>
+        <v>-1226.3590817310032</v>
       </c>
       <c r="AR14" s="11">
         <f>'CF DRIVERS'!AR14</f>
-        <v>-9351.9260006697732</v>
+        <v>-1238.6226725482993</v>
       </c>
       <c r="AS14" s="11">
         <f>'CF DRIVERS'!AS14</f>
-        <v>7224.4907374370669</v>
+        <v>-1251.0088992737874</v>
       </c>
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.25">
@@ -3567,83 +3569,83 @@
       </c>
       <c r="Z15" s="11">
         <f>'CF DRIVERS'!Z15</f>
-        <v>-1751.2524987017387</v>
+        <v>-746.36999999999534</v>
       </c>
       <c r="AA15" s="11">
         <f>'CF DRIVERS'!AA15</f>
-        <v>-10587.093039285537</v>
+        <v>-753.83370000000286</v>
       </c>
       <c r="AB15" s="11">
         <f>'CF DRIVERS'!AB15</f>
-        <v>-3523.6763825983944</v>
+        <v>-761.37203699999372</v>
       </c>
       <c r="AC15" s="11">
         <f>'CF DRIVERS'!AC15</f>
-        <v>2722.0881972317293</v>
+        <v>-768.98575736999919</v>
       </c>
       <c r="AD15" s="11">
         <f>'CF DRIVERS'!AD15</f>
-        <v>-2059.5626098503562</v>
+        <v>-776.67561494369875</v>
       </c>
       <c r="AE15" s="11">
         <f>'CF DRIVERS'!AE15</f>
-        <v>-12450.963517187833</v>
+        <v>-784.44237109314417</v>
       </c>
       <c r="AF15" s="11">
         <f>'CF DRIVERS'!AF15</f>
-        <v>-4144.0238527524634</v>
+        <v>-792.28679480408027</v>
       </c>
       <c r="AG15" s="11">
         <f>'CF DRIVERS'!AG15</f>
-        <v>3201.3151021280792</v>
+        <v>-800.20966275209503</v>
       </c>
       <c r="AH15" s="11">
         <f>'CF DRIVERS'!AH15</f>
-        <v>-2422.1510873150401</v>
+        <v>-808.21175937962835</v>
       </c>
       <c r="AI15" s="11">
         <f>'CF DRIVERS'!AI15</f>
-        <v>-14642.970637084756</v>
+        <v>-816.29387697343191</v>
       </c>
       <c r="AJ15" s="11">
         <f>'CF DRIVERS'!AJ15</f>
-        <v>-4873.5842420120171</v>
+        <v>-824.45681574316404</v>
       </c>
       <c r="AK15" s="11">
         <f>'CF DRIVERS'!AK15</f>
-        <v>3764.9104806874384</v>
+        <v>-832.70138390059583</v>
       </c>
       <c r="AL15" s="11">
         <f>'CF DRIVERS'!AL15</f>
-        <v>-2848.573702844471</v>
+        <v>-841.02839773960295</v>
       </c>
       <c r="AM15" s="11">
         <f>'CF DRIVERS'!AM15</f>
-        <v>-17220.883249921695</v>
+        <v>-849.4386817170016</v>
       </c>
       <c r="AN15" s="11">
         <f>'CF DRIVERS'!AN15</f>
-        <v>-5731.5846162931703</v>
+        <v>-857.93306853415561</v>
       </c>
       <c r="AO15" s="11">
         <f>'CF DRIVERS'!AO15</f>
-        <v>4427.7275042896217</v>
+        <v>-866.51239921951492</v>
       </c>
       <c r="AP15" s="11">
         <f>'CF DRIVERS'!AP15</f>
-        <v>-3350.0685333101137</v>
+        <v>-875.17752321169246</v>
       </c>
       <c r="AQ15" s="11">
         <f>'CF DRIVERS'!AQ15</f>
-        <v>-20252.640482414805</v>
+        <v>-883.92929844382161</v>
       </c>
       <c r="AR15" s="11">
         <f>'CF DRIVERS'!AR15</f>
-        <v>-6740.6369896185643</v>
+        <v>-892.76859142826288</v>
       </c>
       <c r="AS15" s="11">
         <f>'CF DRIVERS'!AS15</f>
-        <v>5207.2342630210333</v>
+        <v>-901.69627734254755</v>
       </c>
     </row>
     <row r="16" spans="1:45" x14ac:dyDescent="0.25">
@@ -3748,83 +3750,83 @@
       </c>
       <c r="Z16" s="11">
         <f>'CF DRIVERS'!Z16</f>
-        <v>13279.785919855116</v>
+        <v>5659.7399999999907</v>
       </c>
       <c r="AA16" s="11">
         <f>'CF DRIVERS'!AA16</f>
-        <v>80282.157586941961</v>
+        <v>5716.3374000000767</v>
       </c>
       <c r="AB16" s="11">
         <f>'CF DRIVERS'!AB16</f>
-        <v>26720.11491572205</v>
+        <v>5773.5007739999564</v>
       </c>
       <c r="AC16" s="11">
         <f>'CF DRIVERS'!AC16</f>
-        <v>-20641.654210914741</v>
+        <v>5831.2357817399316</v>
       </c>
       <c r="AD16" s="11">
         <f>'CF DRIVERS'!AD16</f>
-        <v>15617.708221759414</v>
+        <v>5889.5481395573588</v>
       </c>
       <c r="AE16" s="11">
         <f>'CF DRIVERS'!AE16</f>
-        <v>94415.928101033904</v>
+        <v>5948.4436209531268</v>
       </c>
       <c r="AF16" s="11">
         <f>'CF DRIVERS'!AF16</f>
-        <v>31424.22332137858</v>
+        <v>6007.9280571625568</v>
       </c>
       <c r="AG16" s="11">
         <f>'CF DRIVERS'!AG16</f>
-        <v>-24275.642290175776</v>
+        <v>6068.0073377341032</v>
       </c>
       <c r="AH16" s="11">
         <f>'CF DRIVERS'!AH16</f>
-        <v>18367.224560098141</v>
+        <v>6128.6874111113138</v>
       </c>
       <c r="AI16" s="11">
         <f>'CF DRIVERS'!AI16</f>
-        <v>111037.96593316202</v>
+        <v>6189.9742852227064</v>
       </c>
       <c r="AJ16" s="11">
         <f>'CF DRIVERS'!AJ16</f>
-        <v>36956.495676253107</v>
+        <v>6251.8740280749043</v>
       </c>
       <c r="AK16" s="11">
         <f>'CF DRIVERS'!AK16</f>
-        <v>-28549.398346618982</v>
+        <v>6314.3927683554357</v>
       </c>
       <c r="AL16" s="11">
         <f>'CF DRIVERS'!AL16</f>
-        <v>21600.796560602612</v>
+        <v>6377.5366960392566</v>
       </c>
       <c r="AM16" s="11">
         <f>'CF DRIVERS'!AM16</f>
-        <v>130586.33354088711</v>
+        <v>6441.3120629995828</v>
       </c>
       <c r="AN16" s="11">
         <f>'CF DRIVERS'!AN16</f>
-        <v>43462.731240831083</v>
+        <v>6505.7251836294308</v>
       </c>
       <c r="AO16" s="11">
         <f>'CF DRIVERS'!AO16</f>
-        <v>-33575.554302997421</v>
+        <v>6570.7824354658369</v>
       </c>
       <c r="AP16" s="11">
         <f>'CF DRIVERS'!AP16</f>
-        <v>25403.64280546736</v>
+        <v>6636.490259820479</v>
       </c>
       <c r="AQ16" s="11">
         <f>'CF DRIVERS'!AQ16</f>
-        <v>153576.21480491222</v>
+        <v>6702.8551624186803</v>
       </c>
       <c r="AR16" s="11">
         <f>'CF DRIVERS'!AR16</f>
-        <v>51114.397410967387</v>
+        <v>6769.8837140428368</v>
       </c>
       <c r="AS16" s="11">
         <f>'CF DRIVERS'!AS16</f>
-        <v>-39486.571067688521</v>
+        <v>6837.5825511834119</v>
       </c>
     </row>
     <row r="17" spans="1:45" x14ac:dyDescent="0.25">
@@ -3929,83 +3931,83 @@
       </c>
       <c r="Z17" s="11">
         <f>'CF DRIVERS'!Z17</f>
-        <v>7181.8551263465197</v>
+        <v>3060.8499999999767</v>
       </c>
       <c r="AA17" s="11">
         <f>'CF DRIVERS'!AA17</f>
-        <v>43417.478903623065</v>
+        <v>3091.4585000000661</v>
       </c>
       <c r="AB17" s="11">
         <f>'CF DRIVERS'!AB17</f>
-        <v>14450.533724126464</v>
+        <v>3122.3730849999702</v>
       </c>
       <c r="AC17" s="11">
         <f>'CF DRIVERS'!AC17</f>
-        <v>-11163.234935081447</v>
+        <v>3153.5968158500036</v>
       </c>
       <c r="AD17" s="11">
         <f>'CF DRIVERS'!AD17</f>
-        <v>8446.2293692947133</v>
+        <v>3185.1327840084559</v>
       </c>
       <c r="AE17" s="11">
         <f>'CF DRIVERS'!AE17</f>
-        <v>51061.17834530375</v>
+        <v>3216.9841118486365</v>
       </c>
       <c r="AF17" s="11">
         <f>'CF DRIVERS'!AF17</f>
-        <v>16994.567586716264</v>
+        <v>3249.1539529670845</v>
       </c>
       <c r="AG17" s="11">
         <f>'CF DRIVERS'!AG17</f>
-        <v>-13128.53588749381</v>
+        <v>3281.6454924967256</v>
       </c>
       <c r="AH17" s="11">
         <f>'CF DRIVERS'!AH17</f>
-        <v>9933.1982201967621</v>
+        <v>3314.4619474217179</v>
       </c>
       <c r="AI17" s="11">
         <f>'CF DRIVERS'!AI17</f>
-        <v>60050.560277772252</v>
+        <v>3347.6065668959636</v>
       </c>
       <c r="AJ17" s="11">
         <f>'CF DRIVERS'!AJ17</f>
-        <v>19986.481674186361</v>
+        <v>3381.0826325648814</v>
       </c>
       <c r="AK17" s="11">
         <f>'CF DRIVERS'!AK17</f>
-        <v>-15439.830439074663</v>
+        <v>3414.893458890554</v>
       </c>
       <c r="AL17" s="11">
         <f>'CF DRIVERS'!AL17</f>
-        <v>11681.949727817962</v>
+        <v>3449.042393479438</v>
       </c>
       <c r="AM17" s="11">
         <f>'CF DRIVERS'!AM17</f>
-        <v>70622.533723920875</v>
+        <v>3483.5328174142633</v>
       </c>
       <c r="AN17" s="11">
         <f>'CF DRIVERS'!AN17</f>
-        <v>23505.125839437474</v>
+        <v>3518.368145588378</v>
       </c>
       <c r="AO17" s="11">
         <f>'CF DRIVERS'!AO17</f>
-        <v>-18158.031179582351</v>
+        <v>3553.5518270442844</v>
       </c>
       <c r="AP17" s="11">
         <f>'CF DRIVERS'!AP17</f>
-        <v>13738.57104409649</v>
+        <v>3589.0873453146196</v>
       </c>
       <c r="AQ17" s="11">
         <f>'CF DRIVERS'!AQ17</f>
-        <v>83055.715825394029</v>
+        <v>3624.9782187679084</v>
       </c>
       <c r="AR17" s="11">
         <f>'CF DRIVERS'!AR17</f>
-        <v>27643.231546918978</v>
+        <v>3661.228000955598</v>
       </c>
       <c r="AS17" s="11">
         <f>'CF DRIVERS'!AS17</f>
-        <v>-21354.774433548911</v>
+        <v>3697.840280965087</v>
       </c>
     </row>
     <row r="18" spans="1:45" x14ac:dyDescent="0.25">
@@ -4110,83 +4112,83 @@
       </c>
       <c r="Z18" s="11">
         <f>'CF DRIVERS'!Z18</f>
-        <v>9011.6637482264778</v>
+        <v>3840.6999999999534</v>
       </c>
       <c r="AA18" s="11">
         <f>'CF DRIVERS'!AA18</f>
-        <v>54479.478323062183</v>
+        <v>3879.1070000000182</v>
       </c>
       <c r="AB18" s="11">
         <f>'CF DRIVERS'!AB18</f>
-        <v>18132.272040202108</v>
+        <v>3917.8980699999956</v>
       </c>
       <c r="AC18" s="11">
         <f>'CF DRIVERS'!AC18</f>
-        <v>-14007.428137663519</v>
+        <v>3957.0770506999688</v>
       </c>
       <c r="AD18" s="11">
         <f>'CF DRIVERS'!AD18</f>
-        <v>10598.178002401371</v>
+        <v>3996.6478212070069</v>
       </c>
       <c r="AE18" s="11">
         <f>'CF DRIVERS'!AE18</f>
-        <v>64070.656082724745</v>
+        <v>4036.6142994191032</v>
       </c>
       <c r="AF18" s="11">
         <f>'CF DRIVERS'!AF18</f>
-        <v>21324.480366663192</v>
+        <v>4076.9804424133035</v>
       </c>
       <c r="AG18" s="11">
         <f>'CF DRIVERS'!AG18</f>
-        <v>-16473.452728195582</v>
+        <v>4117.7502468373859</v>
       </c>
       <c r="AH18" s="11">
         <f>'CF DRIVERS'!AH18</f>
-        <v>12464.000001408043</v>
+        <v>4158.9277493057307</v>
       </c>
       <c r="AI18" s="11">
         <f>'CF DRIVERS'!AI18</f>
-        <v>75350.372236091294</v>
+        <v>4200.5170267988578</v>
       </c>
       <c r="AJ18" s="11">
         <f>'CF DRIVERS'!AJ18</f>
-        <v>25078.680812861654</v>
+        <v>4242.5221970668645</v>
       </c>
       <c r="AK18" s="11">
         <f>'CF DRIVERS'!AK18</f>
-        <v>-19373.62391732831</v>
+        <v>4284.9474190375186</v>
       </c>
       <c r="AL18" s="11">
         <f>'CF DRIVERS'!AL18</f>
-        <v>14658.302210049704</v>
+        <v>4327.7968932278454</v>
       </c>
       <c r="AM18" s="11">
         <f>'CF DRIVERS'!AM18</f>
-        <v>88615.896000608569</v>
+        <v>4371.0748621601379</v>
       </c>
       <c r="AN18" s="11">
         <f>'CF DRIVERS'!AN18</f>
-        <v>29493.812768194242</v>
+        <v>4414.7856107817497</v>
       </c>
       <c r="AO18" s="11">
         <f>'CF DRIVERS'!AO18</f>
-        <v>-22784.373736518202</v>
+        <v>4458.9334668895463</v>
       </c>
       <c r="AP18" s="11">
         <f>'CF DRIVERS'!AP18</f>
-        <v>17238.913964768406</v>
+        <v>4503.5228015584289</v>
       </c>
       <c r="AQ18" s="11">
         <f>'CF DRIVERS'!AQ18</f>
-        <v>104216.83119740954</v>
+        <v>4548.558029574051</v>
       </c>
       <c r="AR18" s="11">
         <f>'CF DRIVERS'!AR18</f>
-        <v>34686.234020697419</v>
+        <v>4594.043609869841</v>
       </c>
       <c r="AS18" s="11">
         <f>'CF DRIVERS'!AS18</f>
-        <v>-26795.590168394847</v>
+        <v>4639.9840459684492</v>
       </c>
     </row>
     <row r="19" spans="1:45" x14ac:dyDescent="0.25">
@@ -4448,83 +4450,83 @@
       </c>
       <c r="Z20" s="11">
         <f>'CF DRIVERS'!Z20</f>
-        <v>2675.3897351108608</v>
+        <v>1140.2299999999959</v>
       </c>
       <c r="AA20" s="11">
         <f>'CF DRIVERS'!AA20</f>
-        <v>16173.909851929406</v>
+        <v>1151.6322999999975</v>
       </c>
       <c r="AB20" s="11">
         <f>'CF DRIVERS'!AB20</f>
-        <v>5383.123011013522</v>
+        <v>1163.148623000001</v>
       </c>
       <c r="AC20" s="11">
         <f>'CF DRIVERS'!AC20</f>
-        <v>-4158.5361484646273</v>
+        <v>1174.7801092299924</v>
       </c>
       <c r="AD20" s="11">
         <f>'CF DRIVERS'!AD20</f>
-        <v>3146.3953195193899</v>
+        <v>1186.5279103223002</v>
       </c>
       <c r="AE20" s="11">
         <f>'CF DRIVERS'!AE20</f>
-        <v>19021.346157004009</v>
+        <v>1198.3931894255365</v>
       </c>
       <c r="AF20" s="11">
         <f>'CF DRIVERS'!AF20</f>
-        <v>6330.8282991330489</v>
+        <v>1210.3771213197906</v>
       </c>
       <c r="AG20" s="11">
         <f>'CF DRIVERS'!AG20</f>
-        <v>-4890.6514448591333</v>
+        <v>1222.4808925329708</v>
       </c>
       <c r="AH20" s="11">
         <f>'CF DRIVERS'!AH20</f>
-        <v>3700.3220042194298</v>
+        <v>1234.705701458297</v>
       </c>
       <c r="AI20" s="11">
         <f>'CF DRIVERS'!AI20</f>
-        <v>22370.077052297303</v>
+        <v>1247.0527584728989</v>
       </c>
       <c r="AJ20" s="11">
         <f>'CF DRIVERS'!AJ20</f>
-        <v>7445.3782443953678</v>
+        <v>1259.5232860576216</v>
       </c>
       <c r="AK20" s="11">
         <f>'CF DRIVERS'!AK20</f>
-        <v>-5751.6565207527892</v>
+        <v>1272.1185189182142</v>
       </c>
       <c r="AL20" s="11">
         <f>'CF DRIVERS'!AL20</f>
-        <v>4351.768148765841</v>
+        <v>1284.8397041073622</v>
       </c>
       <c r="AM20" s="11">
         <f>'CF DRIVERS'!AM20</f>
-        <v>26308.356054045871</v>
+        <v>1297.6881011484656</v>
       </c>
       <c r="AN20" s="11">
         <f>'CF DRIVERS'!AN20</f>
-        <v>8756.146049594623</v>
+        <v>1310.6649821599276</v>
       </c>
       <c r="AO20" s="11">
         <f>'CF DRIVERS'!AO20</f>
-        <v>-6764.242577027675</v>
+        <v>1323.7716319815372</v>
       </c>
       <c r="AP20" s="11">
         <f>'CF DRIVERS'!AP20</f>
-        <v>5117.9021714916453</v>
+        <v>1337.0093483013334</v>
       </c>
       <c r="AQ20" s="11">
         <f>'CF DRIVERS'!AQ20</f>
-        <v>30939.973816289275</v>
+        <v>1350.3794417843746</v>
       </c>
       <c r="AR20" s="11">
         <f>'CF DRIVERS'!AR20</f>
-        <v>10297.676105246384</v>
+        <v>1363.8832362022367</v>
       </c>
       <c r="AS20" s="11">
         <f>'CF DRIVERS'!AS20</f>
-        <v>-7955.0956278045196</v>
+        <v>1377.5220685642271</v>
       </c>
     </row>
     <row r="21" spans="1:45" x14ac:dyDescent="0.25">
@@ -4810,83 +4812,83 @@
       </c>
       <c r="Z22" s="11">
         <f>'CF DRIVERS'!Z22</f>
-        <v>4815.9971645233672</v>
+        <v>2052.5399999999863</v>
       </c>
       <c r="AA22" s="11">
         <f>'CF DRIVERS'!AA22</f>
-        <v>29114.825015548769</v>
+        <v>2073.0654000000213</v>
       </c>
       <c r="AB22" s="11">
         <f>'CF DRIVERS'!AB22</f>
-        <v>9690.2162765632165</v>
+        <v>2093.7960539999913</v>
       </c>
       <c r="AC22" s="11">
         <f>'CF DRIVERS'!AC22</f>
-        <v>-7485.8246022026797</v>
+        <v>2114.7340145400012</v>
       </c>
       <c r="AD22" s="11">
         <f>'CF DRIVERS'!AD22</f>
-        <v>5663.8592644697201</v>
+        <v>2135.8813546853853</v>
       </c>
       <c r="AE22" s="11">
         <f>'CF DRIVERS'!AE22</f>
-        <v>34240.525017844666</v>
+        <v>2157.2401682322743</v>
       </c>
       <c r="AF22" s="11">
         <f>'CF DRIVERS'!AF22</f>
-        <v>11396.190520423574</v>
+        <v>2178.8125699146331</v>
       </c>
       <c r="AG22" s="11">
         <f>'CF DRIVERS'!AG22</f>
-        <v>-8803.7130373969849</v>
+        <v>2200.600695613648</v>
       </c>
       <c r="AH22" s="11">
         <f>'CF DRIVERS'!AH22</f>
-        <v>6660.9885080558233</v>
+        <v>2222.6067025698867</v>
       </c>
       <c r="AI22" s="11">
         <f>'CF DRIVERS'!AI22</f>
-        <v>40268.610677602192</v>
+        <v>2244.8327695955668</v>
       </c>
       <c r="AJ22" s="11">
         <f>'CF DRIVERS'!AJ22</f>
-        <v>13402.503584146376</v>
+        <v>2267.2810972915468</v>
       </c>
       <c r="AK22" s="11">
         <f>'CF DRIVERS'!AK22</f>
-        <v>-10353.617318528588</v>
+        <v>2289.953908264426</v>
       </c>
       <c r="AL22" s="11">
         <f>'CF DRIVERS'!AL22</f>
-        <v>7833.6635556578985</v>
+        <v>2312.8534473471009</v>
       </c>
       <c r="AM22" s="11">
         <f>'CF DRIVERS'!AM22</f>
-        <v>47357.948076415589</v>
+        <v>2335.9819818205142</v>
       </c>
       <c r="AN22" s="11">
         <f>'CF DRIVERS'!AN22</f>
-        <v>15762.030478618326</v>
+        <v>2359.3418016387732</v>
       </c>
       <c r="AO22" s="11">
         <f>'CF DRIVERS'!AO22</f>
-        <v>-12176.384114654415</v>
+        <v>2382.935219655119</v>
       </c>
       <c r="AP22" s="11">
         <f>'CF DRIVERS'!AP22</f>
-        <v>9212.7894574545571</v>
+        <v>2406.7645718516796</v>
       </c>
       <c r="AQ22" s="11">
         <f>'CF DRIVERS'!AQ22</f>
-        <v>55695.371860840714</v>
+        <v>2430.8322175702488</v>
       </c>
       <c r="AR22" s="11">
         <f>'CF DRIVERS'!AR22</f>
-        <v>18536.954924061356</v>
+        <v>2455.1405397459457</v>
       </c>
       <c r="AS22" s="11">
         <f>'CF DRIVERS'!AS22</f>
-        <v>-14320.051200103422</v>
+        <v>2479.6919451433496</v>
       </c>
     </row>
     <row r="23" spans="1:45" x14ac:dyDescent="0.25">
@@ -5172,83 +5174,83 @@
       </c>
       <c r="Z24" s="7">
         <f t="shared" ref="Z24:AS24" si="0">SUM(Z2:Z23)</f>
-        <v>512182.04695790313</v>
+        <v>519184.77148567565</v>
       </c>
       <c r="AA24" s="7">
         <f t="shared" si="0"/>
-        <v>462347.83438429626</v>
+        <v>524136.30068620708</v>
       </c>
       <c r="AB24" s="7">
         <f t="shared" si="0"/>
-        <v>582544.79213726963</v>
+        <v>529137.3451787451</v>
       </c>
       <c r="AC24" s="7">
         <f t="shared" si="0"/>
-        <v>649691.79669103888</v>
+        <v>534188.40011620778</v>
       </c>
       <c r="AD24" s="7">
         <f t="shared" si="0"/>
-        <v>598121.47668105084</v>
+        <v>539289.96560304507</v>
       </c>
       <c r="AE24" s="7">
         <f t="shared" si="0"/>
-        <v>539513.89097652014</v>
+        <v>544442.54674475105</v>
       </c>
       <c r="AF24" s="7">
         <f t="shared" si="0"/>
-        <v>680871.66787579993</v>
+        <v>549646.65369787393</v>
       </c>
       <c r="AG24" s="7">
         <f t="shared" si="0"/>
-        <v>759839.9834356159</v>
+        <v>554902.80172052816</v>
       </c>
       <c r="AH24" s="7">
         <f t="shared" si="0"/>
-        <v>699190.64649001264</v>
+        <v>560211.51122340863</v>
       </c>
       <c r="AI24" s="7">
         <f t="shared" si="0"/>
-        <v>630265.12475049612</v>
+        <v>565573.30782131816</v>
       </c>
       <c r="AJ24" s="7">
         <f t="shared" si="0"/>
-        <v>796509.10848736507</v>
+        <v>570988.72238520649</v>
       </c>
       <c r="AK24" s="7">
         <f t="shared" si="0"/>
-        <v>889379.89109034836</v>
+        <v>576458.29109473422</v>
       </c>
       <c r="AL24" s="7">
         <f t="shared" si="0"/>
-        <v>818053.16534521547</v>
+        <v>581982.55549135711</v>
       </c>
       <c r="AM24" s="7">
         <f t="shared" si="0"/>
-        <v>736993.22250751837</v>
+        <v>587562.06253194588</v>
       </c>
       <c r="AN24" s="7">
         <f t="shared" si="0"/>
-        <v>932504.65976219729</v>
+        <v>593197.36464294069</v>
       </c>
       <c r="AO24" s="7">
         <f t="shared" si="0"/>
-        <v>1041725.4554718061</v>
+        <v>598889.01977504569</v>
       </c>
       <c r="AP24" s="7">
         <f t="shared" si="0"/>
-        <v>957841.57377192006</v>
+        <v>604637.59145847172</v>
       </c>
       <c r="AQ24" s="7">
         <f t="shared" si="0"/>
-        <v>862510.93039017438</v>
+        <v>610443.64885873115</v>
       </c>
       <c r="AR24" s="7">
         <f t="shared" si="0"/>
-        <v>1092442.3915965687</v>
+        <v>616307.76683299418</v>
       </c>
       <c r="AS24" s="7">
         <f t="shared" si="0"/>
-        <v>1220891.6399079193</v>
+        <v>622230.52598699927</v>
       </c>
     </row>
     <row r="25" spans="1:45" x14ac:dyDescent="0.25">
@@ -5353,83 +5355,83 @@
       </c>
       <c r="Z25" s="11">
         <f>'CF DRIVERS'!Z24</f>
-        <v>-11434.491323871829</v>
+        <v>-4873.2899999999208</v>
       </c>
       <c r="AA25" s="11">
         <f>'CF DRIVERS'!AA24</f>
-        <v>-69126.538630196534</v>
+        <v>-4922.02290000004</v>
       </c>
       <c r="AB25" s="11">
         <f>'CF DRIVERS'!AB24</f>
-        <v>-23007.21743713296</v>
+        <v>-4971.2431290000095</v>
       </c>
       <c r="AC25" s="11">
         <f>'CF DRIVERS'!AC24</f>
-        <v>17773.390129141626</v>
+        <v>-5020.9555602899636</v>
       </c>
       <c r="AD25" s="11">
         <f>'CF DRIVERS'!AD24</f>
-        <v>-13447.547290161252</v>
+        <v>-5071.1651158928871</v>
       </c>
       <c r="AE25" s="11">
         <f>'CF DRIVERS'!AE24</f>
-        <v>-81296.348994032829</v>
+        <v>-5121.8767670519301</v>
       </c>
       <c r="AF25" s="11">
         <f>'CF DRIVERS'!AF24</f>
-        <v>-27057.665770837688</v>
+        <v>-5173.0955347223789</v>
       </c>
       <c r="AG25" s="11">
         <f>'CF DRIVERS'!AG24</f>
-        <v>20902.416863016784</v>
+        <v>-5224.8264900695649</v>
       </c>
       <c r="AH25" s="11">
         <f>'CF DRIVERS'!AH24</f>
-        <v>-15815.004183316021</v>
+        <v>-5277.0747549701482</v>
       </c>
       <c r="AI25" s="11">
         <f>'CF DRIVERS'!AI24</f>
-        <v>-95608.669126570923</v>
+        <v>-5329.8455025200965</v>
       </c>
       <c r="AJ25" s="11">
         <f>'CF DRIVERS'!AJ24</f>
-        <v>-31821.200410995632</v>
+        <v>-5383.1439575451659</v>
       </c>
       <c r="AK25" s="11">
         <f>'CF DRIVERS'!AK24</f>
-        <v>24582.312521174899</v>
+        <v>-5436.9753971206956</v>
       </c>
       <c r="AL25" s="11">
         <f>'CF DRIVERS'!AL24</f>
-        <v>-18599.254713258706</v>
+        <v>-5491.3451510918094</v>
       </c>
       <c r="AM25" s="11">
         <f>'CF DRIVERS'!AM24</f>
-        <v>-112440.69045247114</v>
+        <v>-5546.2586026027566</v>
       </c>
       <c r="AN25" s="11">
         <f>'CF DRIVERS'!AN24</f>
-        <v>-37423.3610605133</v>
+        <v>-5601.7211886288133</v>
       </c>
       <c r="AO25" s="11">
         <f>'CF DRIVERS'!AO24</f>
-        <v>28910.058241059422</v>
+        <v>-5657.7384005150525</v>
       </c>
       <c r="AP25" s="11">
         <f>'CF DRIVERS'!AP24</f>
-        <v>-21873.675901623676</v>
+        <v>-5714.3157845201204</v>
       </c>
       <c r="AQ25" s="11">
         <f>'CF DRIVERS'!AQ24</f>
-        <v>-132236.00940089661</v>
+        <v>-5771.4589423654834</v>
       </c>
       <c r="AR25" s="11">
         <f>'CF DRIVERS'!AR24</f>
-        <v>-44011.788838160923</v>
+        <v>-5829.1735317890998</v>
       </c>
       <c r="AS25" s="11">
         <f>'CF DRIVERS'!AS24</f>
-        <v>33999.708806138486</v>
+        <v>-5887.4652671070071</v>
       </c>
     </row>
     <row r="26" spans="1:45" x14ac:dyDescent="0.25">
@@ -6077,83 +6079,83 @@
       </c>
       <c r="Z29" s="11">
         <f>'QTR P&amp;L'!Z2*'CF DRIVERS'!Z28</f>
-        <v>-28835.063385431127</v>
+        <v>-28455.739999999998</v>
       </c>
       <c r="AA29" s="11">
         <f>'QTR P&amp;L'!AA2*'CF DRIVERS'!AA28</f>
-        <v>-32831.482846138693</v>
+        <v>-28740.297399999999</v>
       </c>
       <c r="AB29" s="11">
         <f>'QTR P&amp;L'!AB2*'CF DRIVERS'!AB28</f>
-        <v>-34161.601398643848</v>
+        <v>-29027.700374</v>
       </c>
       <c r="AC29" s="11">
         <f>'QTR P&amp;L'!AC2*'CF DRIVERS'!AC28</f>
-        <v>-33134.066625424035</v>
+        <v>-29317.977377740001</v>
       </c>
       <c r="AD29" s="11">
         <f>'QTR P&amp;L'!AD2*'CF DRIVERS'!AD28</f>
-        <v>-33911.511015872798</v>
+        <v>-29611.1571515174</v>
       </c>
       <c r="AE29" s="11">
         <f>'QTR P&amp;L'!AE2*'CF DRIVERS'!AE28</f>
-        <v>-38611.504934884149</v>
+        <v>-29907.268723032576</v>
       </c>
       <c r="AF29" s="11">
         <f>'QTR P&amp;L'!AF2*'CF DRIVERS'!AF28</f>
-        <v>-40175.792460206016</v>
+        <v>-30206.341410262903</v>
       </c>
       <c r="AG29" s="11">
         <f>'QTR P&amp;L'!AG2*'CF DRIVERS'!AG28</f>
-        <v>-38967.358952865732</v>
+        <v>-30508.404824365531</v>
       </c>
       <c r="AH29" s="11">
         <f>'QTR P&amp;L'!AH2*'CF DRIVERS'!AH28</f>
-        <v>-39881.673364404429</v>
+        <v>-30813.488872609181</v>
       </c>
       <c r="AI29" s="11">
         <f>'QTR P&amp;L'!AI2*'CF DRIVERS'!AI28</f>
-        <v>-45409.106872305689</v>
+        <v>-31121.623761335279</v>
       </c>
       <c r="AJ29" s="11">
         <f>'QTR P&amp;L'!AJ2*'CF DRIVERS'!AJ28</f>
-        <v>-47248.789100080736</v>
+        <v>-31432.839998948635</v>
       </c>
       <c r="AK29" s="11">
         <f>'QTR P&amp;L'!AK2*'CF DRIVERS'!AK28</f>
-        <v>-45827.609418650776</v>
+        <v>-31747.168398938124</v>
       </c>
       <c r="AL29" s="11">
         <f>'QTR P&amp;L'!AL2*'CF DRIVERS'!AL28</f>
-        <v>-46902.889983302892</v>
+        <v>-32064.640082927504</v>
       </c>
       <c r="AM29" s="11">
         <f>'QTR P&amp;L'!AM2*'CF DRIVERS'!AM28</f>
-        <v>-53403.434816070745</v>
+        <v>-32385.286483756779</v>
       </c>
       <c r="AN29" s="11">
         <f>'QTR P&amp;L'!AN2*'CF DRIVERS'!AN28</f>
-        <v>-55566.995315279491</v>
+        <v>-32709.139348594348</v>
       </c>
       <c r="AO29" s="11">
         <f>'QTR P&amp;L'!AO2*'CF DRIVERS'!AO28</f>
-        <v>-53895.615239635299</v>
+        <v>-33036.23074208029</v>
       </c>
       <c r="AP29" s="11">
         <f>'QTR P&amp;L'!AP2*'CF DRIVERS'!AP28</f>
-        <v>-55160.20024248214</v>
+        <v>-33366.593049501091</v>
       </c>
       <c r="AQ29" s="11">
         <f>'QTR P&amp;L'!AQ2*'CF DRIVERS'!AQ28</f>
-        <v>-62805.173820621058</v>
+        <v>-33700.258979996106</v>
       </c>
       <c r="AR29" s="11">
         <f>'QTR P&amp;L'!AR2*'CF DRIVERS'!AR28</f>
-        <v>-65349.631750943998</v>
+        <v>-34037.261569796072</v>
       </c>
       <c r="AS29" s="11">
         <f>'QTR P&amp;L'!AS2*'CF DRIVERS'!AS28</f>
-        <v>-63384.003200408013</v>
+        <v>-34377.634185494033</v>
       </c>
     </row>
     <row r="30" spans="1:45" x14ac:dyDescent="0.25">
@@ -6801,83 +6803,83 @@
       </c>
       <c r="Z33" s="7">
         <f t="shared" ref="Z33:AS33" si="1">SUM(Z25:Z32)</f>
-        <v>-40269.55470930296</v>
+        <v>-33329.029999999919</v>
       </c>
       <c r="AA33" s="7">
         <f t="shared" si="1"/>
-        <v>-101958.02147633523</v>
+        <v>-33662.320300000036</v>
       </c>
       <c r="AB33" s="7">
         <f t="shared" si="1"/>
-        <v>-57168.818835776809</v>
+        <v>-33998.94350300001</v>
       </c>
       <c r="AC33" s="7">
         <f t="shared" si="1"/>
-        <v>-15360.676496282409</v>
+        <v>-34338.93293802996</v>
       </c>
       <c r="AD33" s="7">
         <f t="shared" si="1"/>
-        <v>-47359.05830603405</v>
+        <v>-34682.322267410287</v>
       </c>
       <c r="AE33" s="7">
         <f t="shared" si="1"/>
-        <v>-119907.85392891697</v>
+        <v>-35029.145490084506</v>
       </c>
       <c r="AF33" s="7">
         <f t="shared" si="1"/>
-        <v>-67233.458231043711</v>
+        <v>-35379.436944985282</v>
       </c>
       <c r="AG33" s="7">
         <f t="shared" si="1"/>
-        <v>-18064.942089848948</v>
+        <v>-35733.231314435092</v>
       </c>
       <c r="AH33" s="7">
         <f t="shared" si="1"/>
-        <v>-55696.67754772045</v>
+        <v>-36090.563627579329</v>
       </c>
       <c r="AI33" s="7">
         <f t="shared" si="1"/>
-        <v>-141017.7759988766</v>
+        <v>-36451.469263855375</v>
       </c>
       <c r="AJ33" s="7">
         <f t="shared" si="1"/>
-        <v>-79069.989511076361</v>
+        <v>-36815.983956493801</v>
       </c>
       <c r="AK33" s="7">
         <f t="shared" si="1"/>
-        <v>-21245.296897475877</v>
+        <v>-37184.143796058823</v>
       </c>
       <c r="AL33" s="7">
         <f t="shared" si="1"/>
-        <v>-65502.144696561598</v>
+        <v>-37555.985234019317</v>
       </c>
       <c r="AM33" s="7">
         <f t="shared" si="1"/>
-        <v>-165844.12526854189</v>
+        <v>-37931.545086359532</v>
       </c>
       <c r="AN33" s="7">
         <f t="shared" si="1"/>
-        <v>-92990.356375792791</v>
+        <v>-38310.860537223161</v>
       </c>
       <c r="AO33" s="7">
         <f t="shared" si="1"/>
-        <v>-24985.556998575878</v>
+        <v>-38693.969142595342</v>
       </c>
       <c r="AP33" s="7">
         <f t="shared" si="1"/>
-        <v>-77033.876144105816</v>
+        <v>-39080.908834021211</v>
       </c>
       <c r="AQ33" s="7">
         <f t="shared" si="1"/>
-        <v>-195041.18322151765</v>
+        <v>-39471.717922361589</v>
       </c>
       <c r="AR33" s="7">
         <f t="shared" si="1"/>
-        <v>-109361.42058910492</v>
+        <v>-39866.435101585172</v>
       </c>
       <c r="AS33" s="7">
         <f t="shared" si="1"/>
-        <v>-29384.294394269527</v>
+        <v>-40265.09945260104</v>
       </c>
     </row>
     <row r="34" spans="1:45" x14ac:dyDescent="0.25">
@@ -8587,83 +8589,83 @@
       </c>
       <c r="Z43" s="7">
         <f t="shared" ref="Z43:AS43" si="3">Z24+Z33+Z41+Z42</f>
-        <v>497026.49224860017</v>
+        <v>510969.74148567574</v>
       </c>
       <c r="AA43" s="7">
         <f t="shared" si="3"/>
-        <v>385503.81290796102</v>
+        <v>515587.98038620705</v>
       </c>
       <c r="AB43" s="7">
         <f t="shared" si="3"/>
-        <v>550489.97330149286</v>
+        <v>520252.40167574509</v>
       </c>
       <c r="AC43" s="7">
         <f t="shared" si="3"/>
-        <v>659445.12019475643</v>
+        <v>524963.46717817779</v>
       </c>
       <c r="AD43" s="7">
         <f t="shared" si="3"/>
-        <v>575876.41837501677</v>
+        <v>529721.64333563484</v>
       </c>
       <c r="AE43" s="7">
         <f t="shared" si="3"/>
-        <v>444720.03704760317</v>
+        <v>534527.4012546665</v>
       </c>
       <c r="AF43" s="7">
         <f t="shared" si="3"/>
-        <v>638752.20964475628</v>
+        <v>539381.21675288863</v>
       </c>
       <c r="AG43" s="7">
         <f t="shared" si="3"/>
-        <v>766889.04134576698</v>
+        <v>544283.57040609303</v>
       </c>
       <c r="AH43" s="7">
         <f t="shared" si="3"/>
-        <v>668607.96894229215</v>
+        <v>549234.94759582938</v>
       </c>
       <c r="AI43" s="7">
         <f t="shared" si="3"/>
-        <v>514361.34875161952</v>
+        <v>554235.83855746279</v>
       </c>
       <c r="AJ43" s="7">
         <f t="shared" si="3"/>
-        <v>742553.11897628871</v>
+        <v>559286.73842871271</v>
       </c>
       <c r="AK43" s="7">
         <f t="shared" si="3"/>
-        <v>893248.59419287252</v>
+        <v>564388.14729867538</v>
       </c>
       <c r="AL43" s="7">
         <f t="shared" si="3"/>
-        <v>777665.02064865385</v>
+        <v>569540.57025733776</v>
       </c>
       <c r="AM43" s="7">
         <f t="shared" si="3"/>
-        <v>596263.09723897651</v>
+        <v>574744.51744558639</v>
       </c>
       <c r="AN43" s="7">
         <f t="shared" si="3"/>
-        <v>864628.30338640453</v>
+        <v>580000.50410571753</v>
       </c>
       <c r="AO43" s="7">
         <f t="shared" si="3"/>
-        <v>1041853.8984732302</v>
+        <v>585309.05063245038</v>
       </c>
       <c r="AP43" s="7">
         <f t="shared" si="3"/>
-        <v>905921.69762781425</v>
+        <v>590670.68262445054</v>
       </c>
       <c r="AQ43" s="7">
         <f t="shared" si="3"/>
-        <v>692583.74716865667</v>
+        <v>596085.93093636958</v>
       </c>
       <c r="AR43" s="7">
         <f t="shared" si="3"/>
-        <v>1008194.9710074639</v>
+        <v>601555.33173140907</v>
       </c>
       <c r="AS43" s="7">
         <f t="shared" si="3"/>
-        <v>1216621.3455136498</v>
+        <v>607079.42653439823</v>
       </c>
     </row>
   </sheetData>
@@ -8826,7 +8828,7 @@
         <v>147</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="D2" s="13">
         <f>IFERROR('QTR P&amp;L'!C2/'QTR P&amp;L'!B2-1,"")</f>
@@ -8842,168 +8844,167 @@
       </c>
       <c r="G2" s="13">
         <f>IFERROR('QTR P&amp;L'!F2/IF($B2="QoQ",'QTR P&amp;L'!E2,'QTR P&amp;L'!B2)-1,"")</f>
-        <v>0.17109454221224607</v>
+        <v>3.973390911682273E-2</v>
       </c>
       <c r="H2" s="13">
         <f>IFERROR('QTR P&amp;L'!G2/IF($B2="QoQ",'QTR P&amp;L'!F2,'QTR P&amp;L'!C2)-1,"")</f>
-        <v>0.33644788901321521</v>
+        <v>0.17536275461965434</v>
       </c>
       <c r="I2" s="13">
         <f>IFERROR('QTR P&amp;L'!H2/IF($B2="QoQ",'QTR P&amp;L'!G2,'QTR P&amp;L'!D2)-1,"")</f>
-        <v>0.13173941439164549</v>
+        <v>-3.5143833344163711E-2</v>
       </c>
       <c r="J2" s="13">
         <f>IFERROR('QTR P&amp;L'!I2/IF($B2="QoQ",'QTR P&amp;L'!H2,'QTR P&amp;L'!E2)-1,"")</f>
-        <v>0.19122649072167697</v>
+        <v>1.0270410908598482E-2</v>
       </c>
       <c r="K2" s="13">
         <f>IFERROR('QTR P&amp;L'!J2/IF($B2="QoQ",'QTR P&amp;L'!I2,'QTR P&amp;L'!F2)-1,"")</f>
-        <v>0.22089923268393385</v>
+        <v>6.563306115460299E-2</v>
       </c>
       <c r="L2" s="13">
         <f>IFERROR('QTR P&amp;L'!K2/IF($B2="QoQ",'QTR P&amp;L'!J2,'QTR P&amp;L'!G2)-1,"")</f>
-        <v>0.132238437413428</v>
+        <v>9.0008784557091159E-2</v>
       </c>
       <c r="M2" s="13">
         <f>IFERROR('QTR P&amp;L'!L2/IF($B2="QoQ",'QTR P&amp;L'!K2,'QTR P&amp;L'!H2)-1,"")</f>
-        <v>0.15152099489776027</v>
+        <v>-1.871187530168994E-2</v>
       </c>
       <c r="N2" s="13">
         <f>IFERROR('QTR P&amp;L'!M2/IF($B2="QoQ",'QTR P&amp;L'!L2,'QTR P&amp;L'!I2)-1,"")</f>
-        <v>6.167318342451189E-2</v>
+        <v>-6.855627641930051E-2</v>
       </c>
       <c r="O2" s="13">
         <f>IFERROR('QTR P&amp;L'!N2/IF($B2="QoQ",'QTR P&amp;L'!M2,'QTR P&amp;L'!J2)-1,"")</f>
-        <v>0.11876668506111665</v>
+        <v>0.1229395127735502</v>
       </c>
       <c r="P2" s="13">
         <f>IFERROR('QTR P&amp;L'!O2/IF($B2="QoQ",'QTR P&amp;L'!N2,'QTR P&amp;L'!K2)-1,"")</f>
-        <v>0.12064698032150867</v>
+        <v>9.1840746823000252E-2</v>
       </c>
       <c r="Q2" s="13">
         <f>IFERROR('QTR P&amp;L'!P2/IF($B2="QoQ",'QTR P&amp;L'!O2,'QTR P&amp;L'!L2)-1,"")</f>
-        <v>0.14267314992556734</v>
+        <v>5.7521424978745905E-4</v>
       </c>
       <c r="R2" s="13">
         <f>IFERROR('QTR P&amp;L'!Q2/IF($B2="QoQ",'QTR P&amp;L'!P2,'QTR P&amp;L'!M2)-1,"")</f>
-        <v>0.14354719415492179</v>
+        <v>-6.7843804080541914E-2</v>
       </c>
       <c r="S2" s="13">
         <f>IFERROR('QTR P&amp;L'!R2/IF($B2="QoQ",'QTR P&amp;L'!Q2,'QTR P&amp;L'!N2)-1,"")</f>
-        <v>0.11782003967202881</v>
+        <v>9.7675983233416641E-2</v>
       </c>
       <c r="T2" s="13">
         <f>IFERROR('QTR P&amp;L'!S2/IF($B2="QoQ",'QTR P&amp;L'!R2,'QTR P&amp;L'!O2)-1,"")</f>
-        <v>2.4602134492315519E-2</v>
+        <v>7.8932208869675335E-4</v>
       </c>
       <c r="U2" s="13">
         <f>IFERROR('QTR P&amp;L'!T2/IF($B2="QoQ",'QTR P&amp;L'!S2,'QTR P&amp;L'!P2)-1,"")</f>
-        <v>1.3439991207029101E-2</v>
+        <v>-1.0325176773403277E-2</v>
       </c>
       <c r="V2" s="13">
         <f>IFERROR('QTR P&amp;L'!U2/IF($B2="QoQ",'QTR P&amp;L'!T2,'QTR P&amp;L'!Q2)-1,"")</f>
-        <v>4.7357159206246058E-2</v>
+        <v>-3.6646990679823688E-2</v>
       </c>
       <c r="W2" s="13">
         <f>IFERROR('QTR P&amp;L'!V2/IF($B2="QoQ",'QTR P&amp;L'!U2,'QTR P&amp;L'!R2)-1,"")</f>
-        <v>-2.3453239379958246E-2</v>
+        <v>2.3463597126113678E-2</v>
       </c>
       <c r="X2" s="13">
         <f>IFERROR('QTR P&amp;L'!W2/IF($B2="QoQ",'QTR P&amp;L'!V2,'QTR P&amp;L'!S2)-1,"")</f>
-        <v>0.11101511788138141</v>
+        <v>0.13859582714587515</v>
       </c>
       <c r="Y2" s="13">
         <f>IFERROR('QTR P&amp;L'!X2/IF($B2="QoQ",'QTR P&amp;L'!W2,'QTR P&amp;L'!T2)-1,"")</f>
-        <v>0.16808694223681031</v>
+        <v>4.0513508291374567E-2</v>
       </c>
       <c r="Z2" s="13">
         <f>IFERROR('QTR P&amp;L'!Y2/IF($B2="QoQ",'QTR P&amp;L'!X2,'QTR P&amp;L'!U2)-1,"")</f>
-        <v>0.17605120413942066</v>
+        <v>-3.0078647696550997E-2</v>
       </c>
       <c r="AA2" s="14">
-        <f t="shared" ref="AA2:AT2" si="0">Z2</f>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AB2" s="14">
-        <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <f t="shared" ref="AA2:AT2" si="0">AA2</f>
+        <v>0.01</v>
       </c>
       <c r="AC2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AD2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AE2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AF2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AG2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AH2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AI2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AJ2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AK2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AL2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AM2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AN2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AO2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AP2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AQ2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AR2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AS2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
       <c r="AT2" s="14">
         <f t="shared" si="0"/>
-        <v>0.17605120413942066</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="3" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C3" s="13">
         <f>IFERROR('QTR P&amp;L'!B3/'QTR P&amp;L'!B2,"")</f>
@@ -9184,7 +9185,7 @@
     </row>
     <row r="4" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C4" s="13">
         <f>IFERROR('QTR P&amp;L'!B5/'QTR P&amp;L'!B2,"")</f>
@@ -9727,7 +9728,7 @@
     </row>
     <row r="7" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C7" s="13">
         <f>IFERROR('QTR P&amp;L'!B10/'QTR P&amp;L'!B9,"")</f>
@@ -10143,83 +10144,83 @@
       </c>
       <c r="W2" s="4">
         <f>V2+'QTR CF'!Z43</f>
-        <v>2585143.4922486003</v>
+        <v>2599086.7414856758</v>
       </c>
       <c r="X2" s="4">
         <f>W2+'QTR CF'!AA43</f>
-        <v>2970647.3051565615</v>
+        <v>3114674.7218718827</v>
       </c>
       <c r="Y2" s="4">
         <f>X2+'QTR CF'!AB43</f>
-        <v>3521137.2784580542</v>
+        <v>3634927.1235476276</v>
       </c>
       <c r="Z2" s="4">
         <f>Y2+'QTR CF'!AC43</f>
-        <v>4180582.3986528106</v>
+        <v>4159890.5907258056</v>
       </c>
       <c r="AA2" s="4">
         <f>Z2+'QTR CF'!AD43</f>
-        <v>4756458.8170278277</v>
+        <v>4689612.2340614405</v>
       </c>
       <c r="AB2" s="4">
         <f>AA2+'QTR CF'!AE43</f>
-        <v>5201178.8540754309</v>
+        <v>5224139.6353161074</v>
       </c>
       <c r="AC2" s="4">
         <f>AB2+'QTR CF'!AF43</f>
-        <v>5839931.0637201872</v>
+        <v>5763520.8520689961</v>
       </c>
       <c r="AD2" s="4">
         <f>AC2+'QTR CF'!AG43</f>
-        <v>6606820.1050659539</v>
+        <v>6307804.4224750893</v>
       </c>
       <c r="AE2" s="4">
         <f>AD2+'QTR CF'!AH43</f>
-        <v>7275428.074008246</v>
+        <v>6857039.3700709185</v>
       </c>
       <c r="AF2" s="4">
         <f>AE2+'QTR CF'!AI43</f>
-        <v>7789789.4227598654</v>
+        <v>7411275.2086283816</v>
       </c>
       <c r="AG2" s="4">
         <f>AF2+'QTR CF'!AJ43</f>
-        <v>8532342.5417361539</v>
+        <v>7970561.9470570944</v>
       </c>
       <c r="AH2" s="4">
         <f>AG2+'QTR CF'!AK43</f>
-        <v>9425591.1359290257</v>
+        <v>8534950.0943557695</v>
       </c>
       <c r="AI2" s="4">
         <f>AH2+'QTR CF'!AL43</f>
-        <v>10203256.15657768</v>
+        <v>9104490.6646131072</v>
       </c>
       <c r="AJ2" s="4">
         <f>AI2+'QTR CF'!AM43</f>
-        <v>10799519.253816657</v>
+        <v>9679235.1820586938</v>
       </c>
       <c r="AK2" s="4">
         <f>AJ2+'QTR CF'!AN43</f>
-        <v>11664147.557203062</v>
+        <v>10259235.686164411</v>
       </c>
       <c r="AL2" s="4">
         <f>AK2+'QTR CF'!AO43</f>
-        <v>12706001.455676291</v>
+        <v>10844544.736796862</v>
       </c>
       <c r="AM2" s="4">
         <f>AL2+'QTR CF'!AP43</f>
-        <v>13611923.153304106</v>
+        <v>11435215.419421311</v>
       </c>
       <c r="AN2" s="4">
         <f>AM2+'QTR CF'!AQ43</f>
-        <v>14304506.900472762</v>
+        <v>12031301.350357682</v>
       </c>
       <c r="AO2" s="4">
         <f>AN2+'QTR CF'!AR43</f>
-        <v>15312701.871480227</v>
+        <v>12632856.68208909</v>
       </c>
       <c r="AP2" s="4">
         <f>AO2+'QTR CF'!AS43</f>
-        <v>16529323.216993876</v>
+        <v>13239936.108623488</v>
       </c>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.25">
@@ -10393,7 +10394,7 @@
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B4" s="16">
         <f>IFERROR('QTR BS'!B4/'QTR P&amp;L'!E2*ASSUMPTIONS!$B$2,"")</f>
@@ -10562,7 +10563,7 @@
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B5" s="16">
         <f>IFERROR('QTR BS'!B5/'QTR P&amp;L'!E3*ASSUMPTIONS!$B$2,"")</f>
@@ -10731,7 +10732,7 @@
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B6" s="13">
         <f>IFERROR('QTR BS'!B6/'QTR P&amp;L'!E2,"")</f>
@@ -10900,7 +10901,7 @@
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B7" s="13">
         <f>IFERROR('QTR BS'!B7/'QTR P&amp;L'!E2,"")</f>
@@ -11069,7 +11070,7 @@
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B8" s="13">
         <f>IFERROR('QTR BS'!B9/'QTR P&amp;L'!E2,"")</f>
@@ -11326,83 +11327,83 @@
       </c>
       <c r="W9" s="4">
         <f>V9-'QTR CF'!Z29-'QTR CF'!Z3</f>
-        <v>1077200.4204937969</v>
+        <v>1077257.56</v>
       </c>
       <c r="X9" s="4">
         <f>W9-'QTR CF'!AA29-'QTR CF'!AA3</f>
-        <v>1072254.8389931577</v>
+        <v>1072928.2556</v>
       </c>
       <c r="Y9" s="4">
         <f>X9-'QTR CF'!AB29-'QTR CF'!AB3</f>
-        <v>1067108.8946353865</v>
+        <v>1068555.6581560001</v>
       </c>
       <c r="Z9" s="4">
         <f>Y9-'QTR CF'!AC29-'QTR CF'!AC3</f>
-        <v>1062117.7333250188</v>
+        <v>1064139.33473756</v>
       </c>
       <c r="AA9" s="4">
         <f>Z9-'QTR CF'!AD29-'QTR CF'!AD3</f>
-        <v>1057009.4614164731</v>
+        <v>1059678.8480849357</v>
       </c>
       <c r="AB9" s="4">
         <f>AA9-'QTR CF'!AE29-'QTR CF'!AE3</f>
-        <v>1051193.2043374765</v>
+        <v>1055173.756565785</v>
       </c>
       <c r="AC9" s="4">
         <f>AB9-'QTR CF'!AF29-'QTR CF'!AF3</f>
-        <v>1045141.3102790853</v>
+        <v>1050623.614131443</v>
       </c>
       <c r="AD9" s="4">
         <f>AC9-'QTR CF'!AG29-'QTR CF'!AG3</f>
-        <v>1039271.4490099732</v>
+        <v>1046027.9702727575</v>
       </c>
       <c r="AE9" s="4">
         <f>AD9-'QTR CF'!AH29-'QTR CF'!AH3</f>
-        <v>1033263.8596808566</v>
+        <v>1041386.369975485</v>
       </c>
       <c r="AF9" s="4">
         <f>AE9-'QTR CF'!AI29-'QTR CF'!AI3</f>
-        <v>1026423.6435395184</v>
+        <v>1036698.3536752398</v>
       </c>
       <c r="AG9" s="4">
         <f>AF9-'QTR CF'!AJ29-'QTR CF'!AJ3</f>
-        <v>1019306.3062448232</v>
+        <v>1031963.4572119924</v>
       </c>
       <c r="AH9" s="4">
         <f>AG9-'QTR CF'!AK29-'QTR CF'!AK3</f>
-        <v>1012403.0488311527</v>
+        <v>1027181.2117841122</v>
       </c>
       <c r="AI9" s="4">
         <f>AH9-'QTR CF'!AL29-'QTR CF'!AL3</f>
-        <v>1005337.8161666699</v>
+        <v>1022351.1439019534</v>
       </c>
       <c r="AJ9" s="4">
         <f>AI9-'QTR CF'!AM29-'QTR CF'!AM3</f>
-        <v>997293.37173707515</v>
+        <v>1017472.7753409729</v>
       </c>
       <c r="AK9" s="4">
         <f>AJ9-'QTR CF'!AN29-'QTR CF'!AN3</f>
-        <v>988923.01864138246</v>
+        <v>1012545.6230943826</v>
       </c>
       <c r="AL9" s="4">
         <f>AK9-'QTR CF'!AO29-'QTR CF'!AO3</f>
-        <v>980804.43444755091</v>
+        <v>1007569.1993253264</v>
       </c>
       <c r="AM9" s="4">
         <f>AL9-'QTR CF'!AP29-'QTR CF'!AP3</f>
-        <v>972495.35906496074</v>
+        <v>1002543.0113185795</v>
       </c>
       <c r="AN9" s="4">
         <f>AM9-'QTR CF'!AQ29-'QTR CF'!AQ3</f>
-        <v>963034.68050690321</v>
+        <v>997466.56143176532</v>
       </c>
       <c r="AO9" s="4">
         <f>AN9-'QTR CF'!AR29-'QTR CF'!AR3</f>
-        <v>953190.71666964167</v>
+        <v>992339.34704608307</v>
       </c>
       <c r="AP9" s="4">
         <f>AO9-'QTR CF'!AS29-'QTR CF'!AS3</f>
-        <v>943642.84595257882</v>
+        <v>987160.86051654397</v>
       </c>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.25">
@@ -11914,7 +11915,7 @@
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B13" s="13">
         <f>IFERROR('QTR BS'!B14/'QTR P&amp;L'!E2,"")</f>
@@ -12083,7 +12084,7 @@
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B14" s="16">
         <f>IFERROR('QTR BS'!B16/'QTR P&amp;L'!E3*ASSUMPTIONS!$B$2,"")</f>
@@ -12252,7 +12253,7 @@
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B15" s="13">
         <f>IFERROR('QTR BS'!B17/'QTR P&amp;L'!E2,"")</f>
@@ -12421,7 +12422,7 @@
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B16" s="13">
         <f>IFERROR('QTR BS'!B18/'QTR P&amp;L'!E2,"")</f>
@@ -12590,7 +12591,7 @@
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B17" s="13">
         <f>IFERROR('QTR BS'!B19/'QTR P&amp;L'!E2,"")</f>
@@ -12759,7 +12760,7 @@
     </row>
     <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B18" s="13">
         <f>IFERROR('QTR BS'!B20/'QTR P&amp;L'!E2,"")</f>
@@ -12928,7 +12929,7 @@
     </row>
     <row r="19" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B19" s="13">
         <f>IFERROR('QTR BS'!B21/'QTR P&amp;L'!E2,"")</f>
@@ -13097,7 +13098,7 @@
     </row>
     <row r="20" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B20" s="13">
         <f>IFERROR('QTR BS'!B23/'QTR P&amp;L'!E2,"")</f>
@@ -13435,7 +13436,7 @@
     </row>
     <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B22" s="13">
         <f>IFERROR('QTR BS'!B25/'QTR P&amp;L'!E2,"")</f>
@@ -14030,83 +14031,83 @@
       </c>
       <c r="W25" s="4">
         <f>V25+'QTR CF'!Z9</f>
-        <v>5470785.6199506521</v>
+        <v>5470260.2300000004</v>
       </c>
       <c r="X25" s="4">
         <f>W25+'QTR CF'!AA9</f>
-        <v>5516259.5659684297</v>
+        <v>5510067.5923000006</v>
       </c>
       <c r="Y25" s="4">
         <f>X25+'QTR CF'!AB9</f>
-        <v>5563575.8210752402</v>
+        <v>5550273.0282230005</v>
       </c>
       <c r="Z25" s="4">
         <f>Y25+'QTR CF'!AC9</f>
-        <v>5609468.8672143724</v>
+        <v>5590880.5185052305</v>
       </c>
       <c r="AA25" s="4">
         <f>Z25+'QTR CF'!AD9</f>
-        <v>5656438.7292990042</v>
+        <v>5631894.0836902829</v>
       </c>
       <c r="AB25" s="4">
         <f>AA25+'QTR CF'!AE9</f>
-        <v>5709918.4182701828</v>
+        <v>5673317.7845271854</v>
       </c>
       <c r="AC25" s="4">
         <f>AB25+'QTR CF'!AF9</f>
-        <v>5765564.757063915</v>
+        <v>5715155.7223724574</v>
       </c>
       <c r="AD25" s="4">
         <f>AC25+'QTR CF'!AG9</f>
-        <v>5819537.3292374676</v>
+        <v>5757412.0395961823</v>
       </c>
       <c r="AE25" s="4">
         <f>AD25+'QTR CF'!AH9</f>
-        <v>5874776.2921003606</v>
+        <v>5800090.9199921442</v>
       </c>
       <c r="AF25" s="4">
         <f>AE25+'QTR CF'!AI9</f>
-        <v>5937671.1447119173</v>
+        <v>5843196.5891920654</v>
       </c>
       <c r="AG25" s="4">
         <f>AF25+'QTR CF'!AJ9</f>
-        <v>6003114.0884562368</v>
+        <v>5886733.3150839861</v>
       </c>
       <c r="AH25" s="4">
         <f>AG25+'QTR CF'!AK9</f>
-        <v>6066588.5969514456</v>
+        <v>5930705.4082348263</v>
       </c>
       <c r="AI25" s="4">
         <f>AH25+'QTR CF'!AL9</f>
-        <v>6131552.4457417643</v>
+        <v>5975117.222317175</v>
       </c>
       <c r="AJ25" s="4">
         <f>AI25+'QTR CF'!AM9</f>
-        <v>6205520.0128897559</v>
+        <v>6019973.1545403469</v>
       </c>
       <c r="AK25" s="4">
         <f>AJ25+'QTR CF'!AN9</f>
-        <v>6282484.2656826908</v>
+        <v>6065277.6460857503</v>
       </c>
       <c r="AL25" s="4">
         <f>AK25+'QTR CF'!AO9</f>
-        <v>6357133.5378306387</v>
+        <v>6111035.1825466082</v>
       </c>
       <c r="AM25" s="4">
         <f>AL25+'QTR CF'!AP9</f>
-        <v>6433534.3504260238</v>
+        <v>6157250.2943720743</v>
       </c>
       <c r="AN25" s="4">
         <f>AM25+'QTR CF'!AQ9</f>
-        <v>6520523.996837683</v>
+        <v>6203927.5573157948</v>
       </c>
       <c r="AO25" s="4">
         <f>AN25+'QTR CF'!AR9</f>
-        <v>6611037.8990105046</v>
+        <v>6251071.5928889532</v>
       </c>
       <c r="AP25" s="4">
         <f>AO25+'QTR CF'!AS9</f>
-        <v>6698829.26540823</v>
+        <v>6298687.0688178428</v>
       </c>
     </row>
     <row r="26" spans="1:42" x14ac:dyDescent="0.25">
@@ -14199,83 +14200,83 @@
       </c>
       <c r="W26" s="4">
         <f>V26+'QTR P&amp;L'!Z11</f>
-        <v>9813469.8453200813</v>
+        <v>9807695.1314856745</v>
       </c>
       <c r="X26" s="4">
         <f>W26+'QTR P&amp;L'!AA11</f>
-        <v>10333564.070206027</v>
+        <v>10265506.285771882</v>
       </c>
       <c r="Y26" s="4">
         <f>X26+'QTR P&amp;L'!AB11</f>
-        <v>10873907.650395554</v>
+        <v>10727692.783086628</v>
       </c>
       <c r="Z26" s="4">
         <f>Y26+'QTR P&amp;L'!AC11</f>
-        <v>11398608.3266721</v>
+        <v>11194298.376860196</v>
       </c>
       <c r="AA26" s="4">
         <f>Z26+'QTR P&amp;L'!AD11</f>
-        <v>11935144.600355599</v>
+        <v>11665367.258057175</v>
       </c>
       <c r="AB26" s="4">
         <f>AA26+'QTR P&amp;L'!AE11</f>
-        <v>12543232.275687832</v>
+        <v>12140944.0595518</v>
       </c>
       <c r="AC26" s="4">
         <f>AB26+'QTR P&amp;L'!AF11</f>
-        <v>13175134.229707889</v>
+        <v>12621073.860547045</v>
       </c>
       <c r="AD26" s="4">
         <f>AC26+'QTR P&amp;L'!AG11</f>
-        <v>13788639.327744847</v>
+        <v>13105802.191037919</v>
       </c>
       <c r="AE26" s="4">
         <f>AD26+'QTR P&amp;L'!AH11</f>
-        <v>14416063.694363965</v>
+        <v>13595175.036319377</v>
       </c>
       <c r="AF26" s="4">
         <f>AE26+'QTR P&amp;L'!AI11</f>
-        <v>15127636.173049938</v>
+        <v>14089238.841539325</v>
       </c>
       <c r="AG26" s="4">
         <f>AF26+'QTR P&amp;L'!AJ11</f>
-        <v>15867215.462862438</v>
+        <v>14588040.516297147</v>
       </c>
       <c r="AH26" s="4">
         <f>AG26+'QTR P&amp;L'!AK11</f>
-        <v>16585159.108043633</v>
+        <v>15091627.439288223</v>
       </c>
       <c r="AI26" s="4">
         <f>AH26+'QTR P&amp;L'!AL11</f>
-        <v>17319472.525801618</v>
+        <v>15600047.462994885</v>
       </c>
       <c r="AJ26" s="4">
         <f>AI26+'QTR P&amp;L'!AM11</f>
-        <v>18152748.432081889</v>
+        <v>16113348.91842429</v>
       </c>
       <c r="AK26" s="4">
         <f>AJ26+'QTR P&amp;L'!AN11</f>
-        <v>19018961.782311615</v>
+        <v>16631580.619893663</v>
       </c>
       <c r="AL26" s="4">
         <f>AK26+'QTR P&amp;L'!AO11</f>
-        <v>19859730.506620366</v>
+        <v>17154791.869863406</v>
       </c>
       <c r="AM26" s="4">
         <f>AL26+'QTR P&amp;L'!AP11</f>
-        <v>20719750.921679534</v>
+        <v>17683032.46381852</v>
       </c>
       <c r="AN26" s="4">
         <f>AM26+'QTR P&amp;L'!AQ11</f>
-        <v>21696156.290529974</v>
+        <v>18216352.695198864</v>
       </c>
       <c r="AO26" s="4">
         <f>AN26+'QTR P&amp;L'!AR11</f>
-        <v>22711297.779998444</v>
+        <v>18754803.360378686</v>
       </c>
       <c r="AP26" s="4">
         <f>AO26+'QTR P&amp;L'!AS11</f>
-        <v>23696515.086513672</v>
+        <v>19298435.763695981</v>
       </c>
     </row>
     <row r="27" spans="1:42" x14ac:dyDescent="0.25">
@@ -14869,88 +14870,88 @@
       </c>
       <c r="Z2" s="4">
         <f>'QTR P&amp;L'!Z11</f>
-        <v>459253.84532008163</v>
+        <v>453479.13148567535</v>
       </c>
       <c r="AA2" s="4">
         <f>'QTR P&amp;L'!AA11</f>
-        <v>520094.22488594597</v>
+        <v>457811.15428620751</v>
       </c>
       <c r="AB2" s="4">
         <f>'QTR P&amp;L'!AB11</f>
-        <v>540343.58018952655</v>
+        <v>462186.49731474504</v>
       </c>
       <c r="AC2" s="4">
         <f>'QTR P&amp;L'!AC11</f>
-        <v>524700.67627654527</v>
+        <v>466605.59377356787</v>
       </c>
       <c r="AD2" s="4">
         <f>'QTR P&amp;L'!AD11</f>
-        <v>536536.27368350013</v>
+        <v>471068.88119697862</v>
       </c>
       <c r="AE2" s="4">
         <f>'QTR P&amp;L'!AE11</f>
-        <v>608087.67533223424</v>
+        <v>475576.80149462388</v>
       </c>
       <c r="AF2" s="4">
         <f>'QTR P&amp;L'!AF11</f>
-        <v>631901.95402005711</v>
+        <v>480129.80099524569</v>
       </c>
       <c r="AG2" s="4">
         <f>'QTR P&amp;L'!AG11</f>
-        <v>613505.09803695814</v>
+        <v>484728.33049087337</v>
       </c>
       <c r="AH2" s="4">
         <f>'QTR P&amp;L'!AH11</f>
-        <v>627424.36661911674</v>
+        <v>489372.84528145753</v>
       </c>
       <c r="AI2" s="4">
         <f>'QTR P&amp;L'!AI11</f>
-        <v>711572.47868597391</v>
+        <v>494063.80521994748</v>
       </c>
       <c r="AJ2" s="4">
         <f>'QTR P&amp;L'!AJ11</f>
-        <v>739579.28981249977</v>
+        <v>498801.67475782236</v>
       </c>
       <c r="AK2" s="4">
         <f>'QTR P&amp;L'!AK11</f>
-        <v>717943.64518119651</v>
+        <v>503586.92299107614</v>
       </c>
       <c r="AL2" s="4">
         <f>'QTR P&amp;L'!AL11</f>
-        <v>734313.41775798448</v>
+        <v>508420.02370666212</v>
       </c>
       <c r="AM2" s="4">
         <f>'QTR P&amp;L'!AM11</f>
-        <v>833275.90628027054</v>
+        <v>513301.45542940422</v>
       </c>
       <c r="AN2" s="4">
         <f>'QTR P&amp;L'!AN11</f>
-        <v>866213.35022972664</v>
+        <v>518231.70146937354</v>
       </c>
       <c r="AO2" s="4">
         <f>'QTR P&amp;L'!AO11</f>
-        <v>840768.72430875013</v>
+        <v>523211.24996974273</v>
       </c>
       <c r="AP2" s="4">
         <f>'QTR P&amp;L'!AP11</f>
-        <v>860020.41505916975</v>
+        <v>528240.59395511542</v>
       </c>
       <c r="AQ2" s="4">
         <f>'QTR P&amp;L'!AQ11</f>
-        <v>976405.36885043816</v>
+        <v>533320.23138034204</v>
       </c>
       <c r="AR2" s="4">
         <f>'QTR P&amp;L'!AR11</f>
-        <v>1015141.4894684708</v>
+        <v>538450.66517982085</v>
       </c>
       <c r="AS2" s="4">
         <f>'QTR P&amp;L'!AS11</f>
-        <v>985217.30651522917</v>
+        <v>543632.40331729432</v>
       </c>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B3" s="13">
         <f>IFERROR('QTR CF'!B3/'QTR P&amp;L'!B2,"")</f>
@@ -15936,7 +15937,7 @@
     </row>
     <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B9" s="13">
         <f>IFERROR('QTR CF'!B9/'QTR P&amp;L'!B2,"")</f>
@@ -16398,83 +16399,83 @@
       </c>
       <c r="Z11" s="4">
         <f>-('QTR BS'!W4-'QTR BS'!V4)</f>
-        <v>-37965.789529045112</v>
+        <v>-16180.719999999739</v>
       </c>
       <c r="AA11" s="4">
         <f>-('QTR BS'!X4-'QTR BS'!W4)</f>
-        <v>-229519.92722460465</v>
+        <v>-16342.527200000361</v>
       </c>
       <c r="AB11" s="4">
         <f>-('QTR BS'!Y4-'QTR BS'!X4)</f>
-        <v>-76390.558191563701</v>
+        <v>-16505.952471999917</v>
       </c>
       <c r="AC11" s="4">
         <f>-('QTR BS'!Z4-'QTR BS'!Y4)</f>
-        <v>59012.750960932579</v>
+        <v>-16671.011996719986</v>
       </c>
       <c r="AD11" s="4">
         <f>-('QTR BS'!AA4-'QTR BS'!Z4)</f>
-        <v>-44649.712491737213</v>
+        <v>-16837.722116687102</v>
       </c>
       <c r="AE11" s="4">
         <f>-('QTR BS'!AB4-'QTR BS'!AA4)</f>
-        <v>-269927.18678648863</v>
+        <v>-17006.09933785419</v>
       </c>
       <c r="AF11" s="4">
         <f>-('QTR BS'!AC4-'QTR BS'!AB4)</f>
-        <v>-89839.207946070936</v>
+        <v>-17176.160331232939</v>
       </c>
       <c r="AG11" s="4">
         <f>-('QTR BS'!AD4-'QTR BS'!AC4)</f>
-        <v>69402.016827185173</v>
+        <v>-17347.921934544574</v>
       </c>
       <c r="AH11" s="4">
         <f>-('QTR BS'!AE4-'QTR BS'!AD4)</f>
-        <v>-52510.348140386865</v>
+        <v>-17521.401153890416</v>
       </c>
       <c r="AI11" s="4">
         <f>-('QTR BS'!AF4-'QTR BS'!AE4)</f>
-        <v>-317448.19305021642</v>
+        <v>-17696.615165429423</v>
       </c>
       <c r="AJ11" s="4">
         <f>-('QTR BS'!AG4-'QTR BS'!AF4)</f>
-        <v>-105655.50868390873</v>
+        <v>-17873.58131708391</v>
       </c>
       <c r="AK11" s="4">
         <f>-('QTR BS'!AH4-'QTR BS'!AG4)</f>
-        <v>81620.325459315442</v>
+        <v>-18052.317130254582</v>
       </c>
       <c r="AL11" s="4">
         <f>-('QTR BS'!AI4-'QTR BS'!AH4)</f>
-        <v>-61754.85816028202</v>
+        <v>-18232.840301556746</v>
       </c>
       <c r="AM11" s="4">
         <f>-('QTR BS'!AJ4-'QTR BS'!AI4)</f>
-        <v>-373335.32968859002</v>
+        <v>-18415.168704572599</v>
       </c>
       <c r="AN11" s="4">
         <f>-('QTR BS'!AK4-'QTR BS'!AJ4)</f>
-        <v>-124256.28821167396</v>
+        <v>-18599.320391618414</v>
       </c>
       <c r="AO11" s="4">
         <f>-('QTR BS'!AL4-'QTR BS'!AK4)</f>
-        <v>95989.682038679253</v>
+        <v>-18785.313595534302</v>
       </c>
       <c r="AP11" s="4">
         <f>-('QTR BS'!AM4-'QTR BS'!AL4)</f>
-        <v>-72626.875300858635</v>
+        <v>-18973.166731489589</v>
       </c>
       <c r="AQ11" s="4">
         <f>-('QTR BS'!AN4-'QTR BS'!AM4)</f>
-        <v>-439061.46402805392</v>
+        <v>-19162.898398805177</v>
       </c>
       <c r="AR11" s="4">
         <f>-('QTR BS'!AO4-'QTR BS'!AN4)</f>
-        <v>-146131.75737323426</v>
+        <v>-19354.527382792672</v>
       </c>
       <c r="AS11" s="4">
         <f>-('QTR BS'!AP4-'QTR BS'!AO4)</f>
-        <v>112888.78114654869</v>
+        <v>-19548.072656620992</v>
       </c>
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.25">
@@ -16740,83 +16741,83 @@
       </c>
       <c r="Z13" s="4">
         <f>-('QTR BS'!W5-'QTR BS'!V5)</f>
-        <v>-18762.031924774405</v>
+        <v>-7996.229999999865</v>
       </c>
       <c r="AA13" s="4">
         <f>-('QTR BS'!X5-'QTR BS'!W5)</f>
-        <v>-113424.75042341754</v>
+        <v>-8076.192300000228</v>
       </c>
       <c r="AB13" s="4">
         <f>-('QTR BS'!Y5-'QTR BS'!X5)</f>
-        <v>-37750.88334314723</v>
+        <v>-8156.9542229999788</v>
       </c>
       <c r="AC13" s="4">
         <f>-('QTR BS'!Z5-'QTR BS'!Y5)</f>
-        <v>29163.073683763272</v>
+        <v>-8238.5237652298529</v>
       </c>
       <c r="AD13" s="4">
         <f>-('QTR BS'!AA5-'QTR BS'!Z5)</f>
-        <v>-22065.110237233341</v>
+        <v>-8320.9090028823121</v>
       </c>
       <c r="AE13" s="4">
         <f>-('QTR BS'!AB5-'QTR BS'!AA5)</f>
-        <v>-133393.31431467354</v>
+        <v>-8404.1180929112015</v>
       </c>
       <c r="AF13" s="4">
         <f>-('QTR BS'!AC5-'QTR BS'!AB5)</f>
-        <v>-44396.971813034965</v>
+        <v>-8488.1592738402542</v>
       </c>
       <c r="AG13" s="4">
         <f>-('QTR BS'!AD5-'QTR BS'!AC5)</f>
-        <v>34297.267922196537</v>
+        <v>-8573.0408665786963</v>
       </c>
       <c r="AH13" s="4">
         <f>-('QTR BS'!AE5-'QTR BS'!AD5)</f>
-        <v>-25949.699463967467</v>
+        <v>-8658.771275244304</v>
       </c>
       <c r="AI13" s="4">
         <f>-('QTR BS'!AF5-'QTR BS'!AE5)</f>
-        <v>-156877.36792392004</v>
+        <v>-8745.3589879969368</v>
       </c>
       <c r="AJ13" s="4">
         <f>-('QTR BS'!AG5-'QTR BS'!AF5)</f>
-        <v>-52213.112160863588</v>
+        <v>-8832.8125778769609</v>
       </c>
       <c r="AK13" s="4">
         <f>-('QTR BS'!AH5-'QTR BS'!AG5)</f>
-        <v>40335.343238591449</v>
+        <v>-8921.1407036555465</v>
       </c>
       <c r="AL13" s="4">
         <f>-('QTR BS'!AI5-'QTR BS'!AH5)</f>
-        <v>-30518.17530165473</v>
+        <v>-9010.3521106922999</v>
       </c>
       <c r="AM13" s="4">
         <f>-('QTR BS'!AJ5-'QTR BS'!AI5)</f>
-        <v>-184495.81744914898</v>
+        <v>-9100.4556317990646</v>
       </c>
       <c r="AN13" s="4">
         <f>-('QTR BS'!AK5-'QTR BS'!AJ5)</f>
-        <v>-61405.293428650592</v>
+        <v>-9191.4601881169947</v>
       </c>
       <c r="AO13" s="4">
         <f>-('QTR BS'!AL5-'QTR BS'!AK5)</f>
-        <v>47436.428985122358</v>
+        <v>-9283.3747899982845</v>
       </c>
       <c r="AP13" s="4">
         <f>-('QTR BS'!AM5-'QTR BS'!AL5)</f>
-        <v>-35890.936811649241</v>
+        <v>-9376.2085378981428</v>
       </c>
       <c r="AQ13" s="4">
         <f>-('QTR BS'!AN5-'QTR BS'!AM5)</f>
-        <v>-216976.52826975845</v>
+        <v>-9469.9706232773606</v>
       </c>
       <c r="AR13" s="4">
         <f>-('QTR BS'!AO5-'QTR BS'!AN5)</f>
-        <v>-72215.76927729859</v>
+        <v>-9564.6703295101179</v>
       </c>
       <c r="AS13" s="4">
         <f>-('QTR BS'!AP5-'QTR BS'!AO5)</f>
-        <v>55787.669428027002</v>
+        <v>-9660.3170328051783</v>
       </c>
     </row>
     <row r="14" spans="1:45" x14ac:dyDescent="0.25">
@@ -16921,83 +16922,83 @@
       </c>
       <c r="Z14" s="4">
         <f>-('QTR BS'!W6-'QTR BS'!V6)</f>
-        <v>-2429.6789460061991</v>
+        <v>-1035.5099999999948</v>
       </c>
       <c r="AA14" s="4">
         <f>-('QTR BS'!X6-'QTR BS'!W6)</f>
-        <v>-14688.479860003165</v>
+        <v>-1045.86510000001</v>
       </c>
       <c r="AB14" s="4">
         <f>-('QTR BS'!Y6-'QTR BS'!X6)</f>
-        <v>-4888.7309658004233</v>
+        <v>-1056.323750999989</v>
       </c>
       <c r="AC14" s="4">
         <f>-('QTR BS'!Z6-'QTR BS'!Y6)</f>
-        <v>3776.611531968636</v>
+        <v>-1066.8869885099994</v>
       </c>
       <c r="AD14" s="4">
         <f>-('QTR BS'!AA6-'QTR BS'!Z6)</f>
-        <v>-2857.4268501227925</v>
+        <v>-1077.555858395106</v>
       </c>
       <c r="AE14" s="4">
         <f>-('QTR BS'!AB6-'QTR BS'!AA6)</f>
-        <v>-17274.404426334368</v>
+        <v>-1088.3314169790538</v>
       </c>
       <c r="AF14" s="4">
         <f>-('QTR BS'!AC6-'QTR BS'!AB6)</f>
-        <v>-5749.397939043236</v>
+        <v>-1099.2147311488516</v>
       </c>
       <c r="AG14" s="4">
         <f>-('QTR BS'!AD6-'QTR BS'!AC6)</f>
-        <v>4441.4885397385515</v>
+        <v>-1110.206878460318</v>
       </c>
       <c r="AH14" s="4">
         <f>-('QTR BS'!AE6-'QTR BS'!AD6)</f>
-        <v>-3360.4802878272312</v>
+        <v>-1121.3089472449356</v>
       </c>
       <c r="AI14" s="4">
         <f>-('QTR BS'!AF6-'QTR BS'!AE6)</f>
-        <v>-20315.584126381873</v>
+        <v>-1132.5220367173897</v>
       </c>
       <c r="AJ14" s="4">
         <f>-('QTR BS'!AG6-'QTR BS'!AF6)</f>
-        <v>-6761.5863692885032</v>
+        <v>-1143.8472570845624</v>
       </c>
       <c r="AK14" s="4">
         <f>-('QTR BS'!AH6-'QTR BS'!AG6)</f>
-        <v>5223.4179453309334</v>
+        <v>-1155.2857296554139</v>
       </c>
       <c r="AL14" s="4">
         <f>-('QTR BS'!AI6-'QTR BS'!AH6)</f>
-        <v>-3952.0968889859796</v>
+        <v>-1166.8385869519552</v>
       </c>
       <c r="AM14" s="4">
         <f>-('QTR BS'!AJ6-'QTR BS'!AI6)</f>
-        <v>-23892.167174627102</v>
+        <v>-1178.5069728214876</v>
       </c>
       <c r="AN14" s="4">
         <f>-('QTR BS'!AK6-'QTR BS'!AJ6)</f>
-        <v>-7951.9717914944631</v>
+        <v>-1190.292042549685</v>
       </c>
       <c r="AO14" s="4">
         <f>-('QTR BS'!AL6-'QTR BS'!AK6)</f>
-        <v>6143.0069643299503</v>
+        <v>-1202.1949629751907</v>
       </c>
       <c r="AP14" s="4">
         <f>-('QTR BS'!AM6-'QTR BS'!AL6)</f>
-        <v>-4647.8683051676489</v>
+        <v>-1214.2169126049266</v>
       </c>
       <c r="AQ14" s="4">
         <f>-('QTR BS'!AN6-'QTR BS'!AM6)</f>
-        <v>-28098.411975220544</v>
+        <v>-1226.3590817310032</v>
       </c>
       <c r="AR14" s="4">
         <f>-('QTR BS'!AO6-'QTR BS'!AN6)</f>
-        <v>-9351.9260006697732</v>
+        <v>-1238.6226725482993</v>
       </c>
       <c r="AS14" s="4">
         <f>-('QTR BS'!AP6-'QTR BS'!AO6)</f>
-        <v>7224.4907374370669</v>
+        <v>-1251.0088992737874</v>
       </c>
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.25">
@@ -17102,83 +17103,83 @@
       </c>
       <c r="Z15" s="4">
         <f>-('QTR BS'!W7-'QTR BS'!V7)</f>
-        <v>-1751.2524987017387</v>
+        <v>-746.36999999999534</v>
       </c>
       <c r="AA15" s="4">
         <f>-('QTR BS'!X7-'QTR BS'!W7)</f>
-        <v>-10587.093039285537</v>
+        <v>-753.83370000000286</v>
       </c>
       <c r="AB15" s="4">
         <f>-('QTR BS'!Y7-'QTR BS'!X7)</f>
-        <v>-3523.6763825983944</v>
+        <v>-761.37203699999372</v>
       </c>
       <c r="AC15" s="4">
         <f>-('QTR BS'!Z7-'QTR BS'!Y7)</f>
-        <v>2722.0881972317293</v>
+        <v>-768.98575736999919</v>
       </c>
       <c r="AD15" s="4">
         <f>-('QTR BS'!AA7-'QTR BS'!Z7)</f>
-        <v>-2059.5626098503562</v>
+        <v>-776.67561494369875</v>
       </c>
       <c r="AE15" s="4">
         <f>-('QTR BS'!AB7-'QTR BS'!AA7)</f>
-        <v>-12450.963517187833</v>
+        <v>-784.44237109314417</v>
       </c>
       <c r="AF15" s="4">
         <f>-('QTR BS'!AC7-'QTR BS'!AB7)</f>
-        <v>-4144.0238527524634</v>
+        <v>-792.28679480408027</v>
       </c>
       <c r="AG15" s="4">
         <f>-('QTR BS'!AD7-'QTR BS'!AC7)</f>
-        <v>3201.3151021280792</v>
+        <v>-800.20966275209503</v>
       </c>
       <c r="AH15" s="4">
         <f>-('QTR BS'!AE7-'QTR BS'!AD7)</f>
-        <v>-2422.1510873150401</v>
+        <v>-808.21175937962835</v>
       </c>
       <c r="AI15" s="4">
         <f>-('QTR BS'!AF7-'QTR BS'!AE7)</f>
-        <v>-14642.970637084756</v>
+        <v>-816.29387697343191</v>
       </c>
       <c r="AJ15" s="4">
         <f>-('QTR BS'!AG7-'QTR BS'!AF7)</f>
-        <v>-4873.5842420120171</v>
+        <v>-824.45681574316404</v>
       </c>
       <c r="AK15" s="4">
         <f>-('QTR BS'!AH7-'QTR BS'!AG7)</f>
-        <v>3764.9104806874384</v>
+        <v>-832.70138390059583</v>
       </c>
       <c r="AL15" s="4">
         <f>-('QTR BS'!AI7-'QTR BS'!AH7)</f>
-        <v>-2848.573702844471</v>
+        <v>-841.02839773960295</v>
       </c>
       <c r="AM15" s="4">
         <f>-('QTR BS'!AJ7-'QTR BS'!AI7)</f>
-        <v>-17220.883249921695</v>
+        <v>-849.4386817170016</v>
       </c>
       <c r="AN15" s="4">
         <f>-('QTR BS'!AK7-'QTR BS'!AJ7)</f>
-        <v>-5731.5846162931703</v>
+        <v>-857.93306853415561</v>
       </c>
       <c r="AO15" s="4">
         <f>-('QTR BS'!AL7-'QTR BS'!AK7)</f>
-        <v>4427.7275042896217</v>
+        <v>-866.51239921951492</v>
       </c>
       <c r="AP15" s="4">
         <f>-('QTR BS'!AM7-'QTR BS'!AL7)</f>
-        <v>-3350.0685333101137</v>
+        <v>-875.17752321169246</v>
       </c>
       <c r="AQ15" s="4">
         <f>-('QTR BS'!AN7-'QTR BS'!AM7)</f>
-        <v>-20252.640482414805</v>
+        <v>-883.92929844382161</v>
       </c>
       <c r="AR15" s="4">
         <f>-('QTR BS'!AO7-'QTR BS'!AN7)</f>
-        <v>-6740.6369896185643</v>
+        <v>-892.76859142826288</v>
       </c>
       <c r="AS15" s="4">
         <f>-('QTR BS'!AP7-'QTR BS'!AO7)</f>
-        <v>5207.2342630210333</v>
+        <v>-901.69627734254755</v>
       </c>
     </row>
     <row r="16" spans="1:45" x14ac:dyDescent="0.25">
@@ -17283,83 +17284,83 @@
       </c>
       <c r="Z16" s="4">
         <f>('QTR BS'!W16-'QTR BS'!V16)</f>
-        <v>13279.785919855116</v>
+        <v>5659.7399999999907</v>
       </c>
       <c r="AA16" s="4">
         <f>('QTR BS'!X16-'QTR BS'!W16)</f>
-        <v>80282.157586941961</v>
+        <v>5716.3374000000767</v>
       </c>
       <c r="AB16" s="4">
         <f>('QTR BS'!Y16-'QTR BS'!X16)</f>
-        <v>26720.11491572205</v>
+        <v>5773.5007739999564</v>
       </c>
       <c r="AC16" s="4">
         <f>('QTR BS'!Z16-'QTR BS'!Y16)</f>
-        <v>-20641.654210914741</v>
+        <v>5831.2357817399316</v>
       </c>
       <c r="AD16" s="4">
         <f>('QTR BS'!AA16-'QTR BS'!Z16)</f>
-        <v>15617.708221759414</v>
+        <v>5889.5481395573588</v>
       </c>
       <c r="AE16" s="4">
         <f>('QTR BS'!AB16-'QTR BS'!AA16)</f>
-        <v>94415.928101033904</v>
+        <v>5948.4436209531268</v>
       </c>
       <c r="AF16" s="4">
         <f>('QTR BS'!AC16-'QTR BS'!AB16)</f>
-        <v>31424.22332137858</v>
+        <v>6007.9280571625568</v>
       </c>
       <c r="AG16" s="4">
         <f>('QTR BS'!AD16-'QTR BS'!AC16)</f>
-        <v>-24275.642290175776</v>
+        <v>6068.0073377341032</v>
       </c>
       <c r="AH16" s="4">
         <f>('QTR BS'!AE16-'QTR BS'!AD16)</f>
-        <v>18367.224560098141</v>
+        <v>6128.6874111113138</v>
       </c>
       <c r="AI16" s="4">
         <f>('QTR BS'!AF16-'QTR BS'!AE16)</f>
-        <v>111037.96593316202</v>
+        <v>6189.9742852227064</v>
       </c>
       <c r="AJ16" s="4">
         <f>('QTR BS'!AG16-'QTR BS'!AF16)</f>
-        <v>36956.495676253107</v>
+        <v>6251.8740280749043</v>
       </c>
       <c r="AK16" s="4">
         <f>('QTR BS'!AH16-'QTR BS'!AG16)</f>
-        <v>-28549.398346618982</v>
+        <v>6314.3927683554357</v>
       </c>
       <c r="AL16" s="4">
         <f>('QTR BS'!AI16-'QTR BS'!AH16)</f>
-        <v>21600.796560602612</v>
+        <v>6377.5366960392566</v>
       </c>
       <c r="AM16" s="4">
         <f>('QTR BS'!AJ16-'QTR BS'!AI16)</f>
-        <v>130586.33354088711</v>
+        <v>6441.3120629995828</v>
       </c>
       <c r="AN16" s="4">
         <f>('QTR BS'!AK16-'QTR BS'!AJ16)</f>
-        <v>43462.731240831083</v>
+        <v>6505.7251836294308</v>
       </c>
       <c r="AO16" s="4">
         <f>('QTR BS'!AL16-'QTR BS'!AK16)</f>
-        <v>-33575.554302997421</v>
+        <v>6570.7824354658369</v>
       </c>
       <c r="AP16" s="4">
         <f>('QTR BS'!AM16-'QTR BS'!AL16)</f>
-        <v>25403.64280546736</v>
+        <v>6636.490259820479</v>
       </c>
       <c r="AQ16" s="4">
         <f>('QTR BS'!AN16-'QTR BS'!AM16)</f>
-        <v>153576.21480491222</v>
+        <v>6702.8551624186803</v>
       </c>
       <c r="AR16" s="4">
         <f>('QTR BS'!AO16-'QTR BS'!AN16)</f>
-        <v>51114.397410967387</v>
+        <v>6769.8837140428368</v>
       </c>
       <c r="AS16" s="4">
         <f>('QTR BS'!AP16-'QTR BS'!AO16)</f>
-        <v>-39486.571067688521</v>
+        <v>6837.5825511834119</v>
       </c>
     </row>
     <row r="17" spans="1:45" x14ac:dyDescent="0.25">
@@ -17464,83 +17465,83 @@
       </c>
       <c r="Z17" s="4">
         <f>('QTR BS'!W17-'QTR BS'!V17)</f>
-        <v>7181.8551263465197</v>
+        <v>3060.8499999999767</v>
       </c>
       <c r="AA17" s="4">
         <f>('QTR BS'!X17-'QTR BS'!W17)</f>
-        <v>43417.478903623065</v>
+        <v>3091.4585000000661</v>
       </c>
       <c r="AB17" s="4">
         <f>('QTR BS'!Y17-'QTR BS'!X17)</f>
-        <v>14450.533724126464</v>
+        <v>3122.3730849999702</v>
       </c>
       <c r="AC17" s="4">
         <f>('QTR BS'!Z17-'QTR BS'!Y17)</f>
-        <v>-11163.234935081447</v>
+        <v>3153.5968158500036</v>
       </c>
       <c r="AD17" s="4">
         <f>('QTR BS'!AA17-'QTR BS'!Z17)</f>
-        <v>8446.2293692947133</v>
+        <v>3185.1327840084559</v>
       </c>
       <c r="AE17" s="4">
         <f>('QTR BS'!AB17-'QTR BS'!AA17)</f>
-        <v>51061.17834530375</v>
+        <v>3216.9841118486365</v>
       </c>
       <c r="AF17" s="4">
         <f>('QTR BS'!AC17-'QTR BS'!AB17)</f>
-        <v>16994.567586716264</v>
+        <v>3249.1539529670845</v>
       </c>
       <c r="AG17" s="4">
         <f>('QTR BS'!AD17-'QTR BS'!AC17)</f>
-        <v>-13128.53588749381</v>
+        <v>3281.6454924967256</v>
       </c>
       <c r="AH17" s="4">
         <f>('QTR BS'!AE17-'QTR BS'!AD17)</f>
-        <v>9933.1982201967621</v>
+        <v>3314.4619474217179</v>
       </c>
       <c r="AI17" s="4">
         <f>('QTR BS'!AF17-'QTR BS'!AE17)</f>
-        <v>60050.560277772252</v>
+        <v>3347.6065668959636</v>
       </c>
       <c r="AJ17" s="4">
         <f>('QTR BS'!AG17-'QTR BS'!AF17)</f>
-        <v>19986.481674186361</v>
+        <v>3381.0826325648814</v>
       </c>
       <c r="AK17" s="4">
         <f>('QTR BS'!AH17-'QTR BS'!AG17)</f>
-        <v>-15439.830439074663</v>
+        <v>3414.893458890554</v>
       </c>
       <c r="AL17" s="4">
         <f>('QTR BS'!AI17-'QTR BS'!AH17)</f>
-        <v>11681.949727817962</v>
+        <v>3449.042393479438</v>
       </c>
       <c r="AM17" s="4">
         <f>('QTR BS'!AJ17-'QTR BS'!AI17)</f>
-        <v>70622.533723920875</v>
+        <v>3483.5328174142633</v>
       </c>
       <c r="AN17" s="4">
         <f>('QTR BS'!AK17-'QTR BS'!AJ17)</f>
-        <v>23505.125839437474</v>
+        <v>3518.368145588378</v>
       </c>
       <c r="AO17" s="4">
         <f>('QTR BS'!AL17-'QTR BS'!AK17)</f>
-        <v>-18158.031179582351</v>
+        <v>3553.5518270442844</v>
       </c>
       <c r="AP17" s="4">
         <f>('QTR BS'!AM17-'QTR BS'!AL17)</f>
-        <v>13738.57104409649</v>
+        <v>3589.0873453146196</v>
       </c>
       <c r="AQ17" s="4">
         <f>('QTR BS'!AN17-'QTR BS'!AM17)</f>
-        <v>83055.715825394029</v>
+        <v>3624.9782187679084</v>
       </c>
       <c r="AR17" s="4">
         <f>('QTR BS'!AO17-'QTR BS'!AN17)</f>
-        <v>27643.231546918978</v>
+        <v>3661.228000955598</v>
       </c>
       <c r="AS17" s="4">
         <f>('QTR BS'!AP17-'QTR BS'!AO17)</f>
-        <v>-21354.774433548911</v>
+        <v>3697.840280965087</v>
       </c>
     </row>
     <row r="18" spans="1:45" x14ac:dyDescent="0.25">
@@ -17645,83 +17646,83 @@
       </c>
       <c r="Z18" s="4">
         <f>('QTR BS'!W18-'QTR BS'!V18)</f>
-        <v>9011.6637482264778</v>
+        <v>3840.6999999999534</v>
       </c>
       <c r="AA18" s="4">
         <f>('QTR BS'!X18-'QTR BS'!W18)</f>
-        <v>54479.478323062183</v>
+        <v>3879.1070000000182</v>
       </c>
       <c r="AB18" s="4">
         <f>('QTR BS'!Y18-'QTR BS'!X18)</f>
-        <v>18132.272040202108</v>
+        <v>3917.8980699999956</v>
       </c>
       <c r="AC18" s="4">
         <f>('QTR BS'!Z18-'QTR BS'!Y18)</f>
-        <v>-14007.428137663519</v>
+        <v>3957.0770506999688</v>
       </c>
       <c r="AD18" s="4">
         <f>('QTR BS'!AA18-'QTR BS'!Z18)</f>
-        <v>10598.178002401371</v>
+        <v>3996.6478212070069</v>
       </c>
       <c r="AE18" s="4">
         <f>('QTR BS'!AB18-'QTR BS'!AA18)</f>
-        <v>64070.656082724745</v>
+        <v>4036.6142994191032</v>
       </c>
       <c r="AF18" s="4">
         <f>('QTR BS'!AC18-'QTR BS'!AB18)</f>
-        <v>21324.480366663192</v>
+        <v>4076.9804424133035</v>
       </c>
       <c r="AG18" s="4">
         <f>('QTR BS'!AD18-'QTR BS'!AC18)</f>
-        <v>-16473.452728195582</v>
+        <v>4117.7502468373859</v>
       </c>
       <c r="AH18" s="4">
         <f>('QTR BS'!AE18-'QTR BS'!AD18)</f>
-        <v>12464.000001408043</v>
+        <v>4158.9277493057307</v>
       </c>
       <c r="AI18" s="4">
         <f>('QTR BS'!AF18-'QTR BS'!AE18)</f>
-        <v>75350.372236091294</v>
+        <v>4200.5170267988578</v>
       </c>
       <c r="AJ18" s="4">
         <f>('QTR BS'!AG18-'QTR BS'!AF18)</f>
-        <v>25078.680812861654</v>
+        <v>4242.5221970668645</v>
       </c>
       <c r="AK18" s="4">
         <f>('QTR BS'!AH18-'QTR BS'!AG18)</f>
-        <v>-19373.62391732831</v>
+        <v>4284.9474190375186</v>
       </c>
       <c r="AL18" s="4">
         <f>('QTR BS'!AI18-'QTR BS'!AH18)</f>
-        <v>14658.302210049704</v>
+        <v>4327.7968932278454</v>
       </c>
       <c r="AM18" s="4">
         <f>('QTR BS'!AJ18-'QTR BS'!AI18)</f>
-        <v>88615.896000608569</v>
+        <v>4371.0748621601379</v>
       </c>
       <c r="AN18" s="4">
         <f>('QTR BS'!AK18-'QTR BS'!AJ18)</f>
-        <v>29493.812768194242</v>
+        <v>4414.7856107817497</v>
       </c>
       <c r="AO18" s="4">
         <f>('QTR BS'!AL18-'QTR BS'!AK18)</f>
-        <v>-22784.373736518202</v>
+        <v>4458.9334668895463</v>
       </c>
       <c r="AP18" s="4">
         <f>('QTR BS'!AM18-'QTR BS'!AL18)</f>
-        <v>17238.913964768406</v>
+        <v>4503.5228015584289</v>
       </c>
       <c r="AQ18" s="4">
         <f>('QTR BS'!AN18-'QTR BS'!AM18)</f>
-        <v>104216.83119740954</v>
+        <v>4548.558029574051</v>
       </c>
       <c r="AR18" s="4">
         <f>('QTR BS'!AO18-'QTR BS'!AN18)</f>
-        <v>34686.234020697419</v>
+        <v>4594.043609869841</v>
       </c>
       <c r="AS18" s="4">
         <f>('QTR BS'!AP18-'QTR BS'!AO18)</f>
-        <v>-26795.590168394847</v>
+        <v>4639.9840459684492</v>
       </c>
     </row>
     <row r="19" spans="1:45" x14ac:dyDescent="0.25">
@@ -17987,83 +17988,83 @@
       </c>
       <c r="Z20" s="4">
         <f>('QTR BS'!W20-'QTR BS'!V20)</f>
-        <v>2675.3897351108608</v>
+        <v>1140.2299999999959</v>
       </c>
       <c r="AA20" s="4">
         <f>('QTR BS'!X20-'QTR BS'!W20)</f>
-        <v>16173.909851929406</v>
+        <v>1151.6322999999975</v>
       </c>
       <c r="AB20" s="4">
         <f>('QTR BS'!Y20-'QTR BS'!X20)</f>
-        <v>5383.123011013522</v>
+        <v>1163.148623000001</v>
       </c>
       <c r="AC20" s="4">
         <f>('QTR BS'!Z20-'QTR BS'!Y20)</f>
-        <v>-4158.5361484646273</v>
+        <v>1174.7801092299924</v>
       </c>
       <c r="AD20" s="4">
         <f>('QTR BS'!AA20-'QTR BS'!Z20)</f>
-        <v>3146.3953195193899</v>
+        <v>1186.5279103223002</v>
       </c>
       <c r="AE20" s="4">
         <f>('QTR BS'!AB20-'QTR BS'!AA20)</f>
-        <v>19021.346157004009</v>
+        <v>1198.3931894255365</v>
       </c>
       <c r="AF20" s="4">
         <f>('QTR BS'!AC20-'QTR BS'!AB20)</f>
-        <v>6330.8282991330489</v>
+        <v>1210.3771213197906</v>
       </c>
       <c r="AG20" s="4">
         <f>('QTR BS'!AD20-'QTR BS'!AC20)</f>
-        <v>-4890.6514448591333</v>
+        <v>1222.4808925329708</v>
       </c>
       <c r="AH20" s="4">
         <f>('QTR BS'!AE20-'QTR BS'!AD20)</f>
-        <v>3700.3220042194298</v>
+        <v>1234.705701458297</v>
       </c>
       <c r="AI20" s="4">
         <f>('QTR BS'!AF20-'QTR BS'!AE20)</f>
-        <v>22370.077052297303</v>
+        <v>1247.0527584728989</v>
       </c>
       <c r="AJ20" s="4">
         <f>('QTR BS'!AG20-'QTR BS'!AF20)</f>
-        <v>7445.3782443953678</v>
+        <v>1259.5232860576216</v>
       </c>
       <c r="AK20" s="4">
         <f>('QTR BS'!AH20-'QTR BS'!AG20)</f>
-        <v>-5751.6565207527892</v>
+        <v>1272.1185189182142</v>
       </c>
       <c r="AL20" s="4">
         <f>('QTR BS'!AI20-'QTR BS'!AH20)</f>
-        <v>4351.768148765841</v>
+        <v>1284.8397041073622</v>
       </c>
       <c r="AM20" s="4">
         <f>('QTR BS'!AJ20-'QTR BS'!AI20)</f>
-        <v>26308.356054045871</v>
+        <v>1297.6881011484656</v>
       </c>
       <c r="AN20" s="4">
         <f>('QTR BS'!AK20-'QTR BS'!AJ20)</f>
-        <v>8756.146049594623</v>
+        <v>1310.6649821599276</v>
       </c>
       <c r="AO20" s="4">
         <f>('QTR BS'!AL20-'QTR BS'!AK20)</f>
-        <v>-6764.242577027675</v>
+        <v>1323.7716319815372</v>
       </c>
       <c r="AP20" s="4">
         <f>('QTR BS'!AM20-'QTR BS'!AL20)</f>
-        <v>5117.9021714916453</v>
+        <v>1337.0093483013334</v>
       </c>
       <c r="AQ20" s="4">
         <f>('QTR BS'!AN20-'QTR BS'!AM20)</f>
-        <v>30939.973816289275</v>
+        <v>1350.3794417843746</v>
       </c>
       <c r="AR20" s="4">
         <f>('QTR BS'!AO20-'QTR BS'!AN20)</f>
-        <v>10297.676105246384</v>
+        <v>1363.8832362022367</v>
       </c>
       <c r="AS20" s="4">
         <f>('QTR BS'!AP20-'QTR BS'!AO20)</f>
-        <v>-7955.0956278045196</v>
+        <v>1377.5220685642271</v>
       </c>
     </row>
     <row r="21" spans="1:45" x14ac:dyDescent="0.25">
@@ -18329,83 +18330,83 @@
       </c>
       <c r="Z22" s="4">
         <f>-('QTR BS'!W14-'QTR BS'!V14)+('QTR BS'!W19-'QTR BS'!V19)+('QTR BS'!W21-'QTR BS'!V21)+('QTR BS'!W23-'QTR BS'!V23)+('QTR BS'!W25-'QTR BS'!V25)-('QTR BS'!W3-'QTR BS'!V3)-('QTR BS'!W12-'QTR BS'!V12)-('QTR BS'!W13-'QTR BS'!V13)+('QTR BS'!W24-'QTR BS'!V24)+('QTR BS'!W26-'QTR BS'!V26)+('QTR BS'!W28-'QTR BS'!V28)+('QTR BS'!W32-'QTR BS'!V32)</f>
-        <v>4815.9971645233672</v>
+        <v>2052.5399999999863</v>
       </c>
       <c r="AA22" s="4">
         <f>-('QTR BS'!X14-'QTR BS'!W14)+('QTR BS'!X19-'QTR BS'!W19)+('QTR BS'!X21-'QTR BS'!W21)+('QTR BS'!X23-'QTR BS'!W23)+('QTR BS'!X25-'QTR BS'!W25)-('QTR BS'!X3-'QTR BS'!W3)-('QTR BS'!X12-'QTR BS'!W12)-('QTR BS'!X13-'QTR BS'!W13)+('QTR BS'!X24-'QTR BS'!W24)+('QTR BS'!X26-'QTR BS'!W26)+('QTR BS'!X28-'QTR BS'!W28)+('QTR BS'!X32-'QTR BS'!W32)</f>
-        <v>29114.825015548769</v>
+        <v>2073.0654000000213</v>
       </c>
       <c r="AB22" s="4">
         <f>-('QTR BS'!Y14-'QTR BS'!X14)+('QTR BS'!Y19-'QTR BS'!X19)+('QTR BS'!Y21-'QTR BS'!X21)+('QTR BS'!Y23-'QTR BS'!X23)+('QTR BS'!Y25-'QTR BS'!X25)-('QTR BS'!Y3-'QTR BS'!X3)-('QTR BS'!Y12-'QTR BS'!X12)-('QTR BS'!Y13-'QTR BS'!X13)+('QTR BS'!Y24-'QTR BS'!X24)+('QTR BS'!Y26-'QTR BS'!X26)+('QTR BS'!Y28-'QTR BS'!X28)+('QTR BS'!Y32-'QTR BS'!X32)</f>
-        <v>9690.2162765632165</v>
+        <v>2093.7960539999913</v>
       </c>
       <c r="AC22" s="4">
         <f>-('QTR BS'!Z14-'QTR BS'!Y14)+('QTR BS'!Z19-'QTR BS'!Y19)+('QTR BS'!Z21-'QTR BS'!Y21)+('QTR BS'!Z23-'QTR BS'!Y23)+('QTR BS'!Z25-'QTR BS'!Y25)-('QTR BS'!Z3-'QTR BS'!Y3)-('QTR BS'!Z12-'QTR BS'!Y12)-('QTR BS'!Z13-'QTR BS'!Y13)+('QTR BS'!Z24-'QTR BS'!Y24)+('QTR BS'!Z26-'QTR BS'!Y26)+('QTR BS'!Z28-'QTR BS'!Y28)+('QTR BS'!Z32-'QTR BS'!Y32)</f>
-        <v>-7485.8246022026797</v>
+        <v>2114.7340145400012</v>
       </c>
       <c r="AD22" s="4">
         <f>-('QTR BS'!AA14-'QTR BS'!Z14)+('QTR BS'!AA19-'QTR BS'!Z19)+('QTR BS'!AA21-'QTR BS'!Z21)+('QTR BS'!AA23-'QTR BS'!Z23)+('QTR BS'!AA25-'QTR BS'!Z25)-('QTR BS'!AA3-'QTR BS'!Z3)-('QTR BS'!AA12-'QTR BS'!Z12)-('QTR BS'!AA13-'QTR BS'!Z13)+('QTR BS'!AA24-'QTR BS'!Z24)+('QTR BS'!AA26-'QTR BS'!Z26)+('QTR BS'!AA28-'QTR BS'!Z28)+('QTR BS'!AA32-'QTR BS'!Z32)</f>
-        <v>5663.8592644697201</v>
+        <v>2135.8813546853853</v>
       </c>
       <c r="AE22" s="4">
         <f>-('QTR BS'!AB14-'QTR BS'!AA14)+('QTR BS'!AB19-'QTR BS'!AA19)+('QTR BS'!AB21-'QTR BS'!AA21)+('QTR BS'!AB23-'QTR BS'!AA23)+('QTR BS'!AB25-'QTR BS'!AA25)-('QTR BS'!AB3-'QTR BS'!AA3)-('QTR BS'!AB12-'QTR BS'!AA12)-('QTR BS'!AB13-'QTR BS'!AA13)+('QTR BS'!AB24-'QTR BS'!AA24)+('QTR BS'!AB26-'QTR BS'!AA26)+('QTR BS'!AB28-'QTR BS'!AA28)+('QTR BS'!AB32-'QTR BS'!AA32)</f>
-        <v>34240.525017844666</v>
+        <v>2157.2401682322743</v>
       </c>
       <c r="AF22" s="4">
         <f>-('QTR BS'!AC14-'QTR BS'!AB14)+('QTR BS'!AC19-'QTR BS'!AB19)+('QTR BS'!AC21-'QTR BS'!AB21)+('QTR BS'!AC23-'QTR BS'!AB23)+('QTR BS'!AC25-'QTR BS'!AB25)-('QTR BS'!AC3-'QTR BS'!AB3)-('QTR BS'!AC12-'QTR BS'!AB12)-('QTR BS'!AC13-'QTR BS'!AB13)+('QTR BS'!AC24-'QTR BS'!AB24)+('QTR BS'!AC26-'QTR BS'!AB26)+('QTR BS'!AC28-'QTR BS'!AB28)+('QTR BS'!AC32-'QTR BS'!AB32)</f>
-        <v>11396.190520423574</v>
+        <v>2178.8125699146331</v>
       </c>
       <c r="AG22" s="4">
         <f>-('QTR BS'!AD14-'QTR BS'!AC14)+('QTR BS'!AD19-'QTR BS'!AC19)+('QTR BS'!AD21-'QTR BS'!AC21)+('QTR BS'!AD23-'QTR BS'!AC23)+('QTR BS'!AD25-'QTR BS'!AC25)-('QTR BS'!AD3-'QTR BS'!AC3)-('QTR BS'!AD12-'QTR BS'!AC12)-('QTR BS'!AD13-'QTR BS'!AC13)+('QTR BS'!AD24-'QTR BS'!AC24)+('QTR BS'!AD26-'QTR BS'!AC26)+('QTR BS'!AD28-'QTR BS'!AC28)+('QTR BS'!AD32-'QTR BS'!AC32)</f>
-        <v>-8803.7130373969849</v>
+        <v>2200.600695613648</v>
       </c>
       <c r="AH22" s="4">
         <f>-('QTR BS'!AE14-'QTR BS'!AD14)+('QTR BS'!AE19-'QTR BS'!AD19)+('QTR BS'!AE21-'QTR BS'!AD21)+('QTR BS'!AE23-'QTR BS'!AD23)+('QTR BS'!AE25-'QTR BS'!AD25)-('QTR BS'!AE3-'QTR BS'!AD3)-('QTR BS'!AE12-'QTR BS'!AD12)-('QTR BS'!AE13-'QTR BS'!AD13)+('QTR BS'!AE24-'QTR BS'!AD24)+('QTR BS'!AE26-'QTR BS'!AD26)+('QTR BS'!AE28-'QTR BS'!AD28)+('QTR BS'!AE32-'QTR BS'!AD32)</f>
-        <v>6660.9885080558233</v>
+        <v>2222.6067025698867</v>
       </c>
       <c r="AI22" s="4">
         <f>-('QTR BS'!AF14-'QTR BS'!AE14)+('QTR BS'!AF19-'QTR BS'!AE19)+('QTR BS'!AF21-'QTR BS'!AE21)+('QTR BS'!AF23-'QTR BS'!AE23)+('QTR BS'!AF25-'QTR BS'!AE25)-('QTR BS'!AF3-'QTR BS'!AE3)-('QTR BS'!AF12-'QTR BS'!AE12)-('QTR BS'!AF13-'QTR BS'!AE13)+('QTR BS'!AF24-'QTR BS'!AE24)+('QTR BS'!AF26-'QTR BS'!AE26)+('QTR BS'!AF28-'QTR BS'!AE28)+('QTR BS'!AF32-'QTR BS'!AE32)</f>
-        <v>40268.610677602192</v>
+        <v>2244.8327695955668</v>
       </c>
       <c r="AJ22" s="4">
         <f>-('QTR BS'!AG14-'QTR BS'!AF14)+('QTR BS'!AG19-'QTR BS'!AF19)+('QTR BS'!AG21-'QTR BS'!AF21)+('QTR BS'!AG23-'QTR BS'!AF23)+('QTR BS'!AG25-'QTR BS'!AF25)-('QTR BS'!AG3-'QTR BS'!AF3)-('QTR BS'!AG12-'QTR BS'!AF12)-('QTR BS'!AG13-'QTR BS'!AF13)+('QTR BS'!AG24-'QTR BS'!AF24)+('QTR BS'!AG26-'QTR BS'!AF26)+('QTR BS'!AG28-'QTR BS'!AF28)+('QTR BS'!AG32-'QTR BS'!AF32)</f>
-        <v>13402.503584146376</v>
+        <v>2267.2810972915468</v>
       </c>
       <c r="AK22" s="4">
         <f>-('QTR BS'!AH14-'QTR BS'!AG14)+('QTR BS'!AH19-'QTR BS'!AG19)+('QTR BS'!AH21-'QTR BS'!AG21)+('QTR BS'!AH23-'QTR BS'!AG23)+('QTR BS'!AH25-'QTR BS'!AG25)-('QTR BS'!AH3-'QTR BS'!AG3)-('QTR BS'!AH12-'QTR BS'!AG12)-('QTR BS'!AH13-'QTR BS'!AG13)+('QTR BS'!AH24-'QTR BS'!AG24)+('QTR BS'!AH26-'QTR BS'!AG26)+('QTR BS'!AH28-'QTR BS'!AG28)+('QTR BS'!AH32-'QTR BS'!AG32)</f>
-        <v>-10353.617318528588</v>
+        <v>2289.953908264426</v>
       </c>
       <c r="AL22" s="4">
         <f>-('QTR BS'!AI14-'QTR BS'!AH14)+('QTR BS'!AI19-'QTR BS'!AH19)+('QTR BS'!AI21-'QTR BS'!AH21)+('QTR BS'!AI23-'QTR BS'!AH23)+('QTR BS'!AI25-'QTR BS'!AH25)-('QTR BS'!AI3-'QTR BS'!AH3)-('QTR BS'!AI12-'QTR BS'!AH12)-('QTR BS'!AI13-'QTR BS'!AH13)+('QTR BS'!AI24-'QTR BS'!AH24)+('QTR BS'!AI26-'QTR BS'!AH26)+('QTR BS'!AI28-'QTR BS'!AH28)+('QTR BS'!AI32-'QTR BS'!AH32)</f>
-        <v>7833.6635556578985</v>
+        <v>2312.8534473471009</v>
       </c>
       <c r="AM22" s="4">
         <f>-('QTR BS'!AJ14-'QTR BS'!AI14)+('QTR BS'!AJ19-'QTR BS'!AI19)+('QTR BS'!AJ21-'QTR BS'!AI21)+('QTR BS'!AJ23-'QTR BS'!AI23)+('QTR BS'!AJ25-'QTR BS'!AI25)-('QTR BS'!AJ3-'QTR BS'!AI3)-('QTR BS'!AJ12-'QTR BS'!AI12)-('QTR BS'!AJ13-'QTR BS'!AI13)+('QTR BS'!AJ24-'QTR BS'!AI24)+('QTR BS'!AJ26-'QTR BS'!AI26)+('QTR BS'!AJ28-'QTR BS'!AI28)+('QTR BS'!AJ32-'QTR BS'!AI32)</f>
-        <v>47357.948076415589</v>
+        <v>2335.9819818205142</v>
       </c>
       <c r="AN22" s="4">
         <f>-('QTR BS'!AK14-'QTR BS'!AJ14)+('QTR BS'!AK19-'QTR BS'!AJ19)+('QTR BS'!AK21-'QTR BS'!AJ21)+('QTR BS'!AK23-'QTR BS'!AJ23)+('QTR BS'!AK25-'QTR BS'!AJ25)-('QTR BS'!AK3-'QTR BS'!AJ3)-('QTR BS'!AK12-'QTR BS'!AJ12)-('QTR BS'!AK13-'QTR BS'!AJ13)+('QTR BS'!AK24-'QTR BS'!AJ24)+('QTR BS'!AK26-'QTR BS'!AJ26)+('QTR BS'!AK28-'QTR BS'!AJ28)+('QTR BS'!AK32-'QTR BS'!AJ32)</f>
-        <v>15762.030478618326</v>
+        <v>2359.3418016387732</v>
       </c>
       <c r="AO22" s="4">
         <f>-('QTR BS'!AL14-'QTR BS'!AK14)+('QTR BS'!AL19-'QTR BS'!AK19)+('QTR BS'!AL21-'QTR BS'!AK21)+('QTR BS'!AL23-'QTR BS'!AK23)+('QTR BS'!AL25-'QTR BS'!AK25)-('QTR BS'!AL3-'QTR BS'!AK3)-('QTR BS'!AL12-'QTR BS'!AK12)-('QTR BS'!AL13-'QTR BS'!AK13)+('QTR BS'!AL24-'QTR BS'!AK24)+('QTR BS'!AL26-'QTR BS'!AK26)+('QTR BS'!AL28-'QTR BS'!AK28)+('QTR BS'!AL32-'QTR BS'!AK32)</f>
-        <v>-12176.384114654415</v>
+        <v>2382.935219655119</v>
       </c>
       <c r="AP22" s="4">
         <f>-('QTR BS'!AM14-'QTR BS'!AL14)+('QTR BS'!AM19-'QTR BS'!AL19)+('QTR BS'!AM21-'QTR BS'!AL21)+('QTR BS'!AM23-'QTR BS'!AL23)+('QTR BS'!AM25-'QTR BS'!AL25)-('QTR BS'!AM3-'QTR BS'!AL3)-('QTR BS'!AM12-'QTR BS'!AL12)-('QTR BS'!AM13-'QTR BS'!AL13)+('QTR BS'!AM24-'QTR BS'!AL24)+('QTR BS'!AM26-'QTR BS'!AL26)+('QTR BS'!AM28-'QTR BS'!AL28)+('QTR BS'!AM32-'QTR BS'!AL32)</f>
-        <v>9212.7894574545571</v>
+        <v>2406.7645718516796</v>
       </c>
       <c r="AQ22" s="4">
         <f>-('QTR BS'!AN14-'QTR BS'!AM14)+('QTR BS'!AN19-'QTR BS'!AM19)+('QTR BS'!AN21-'QTR BS'!AM21)+('QTR BS'!AN23-'QTR BS'!AM23)+('QTR BS'!AN25-'QTR BS'!AM25)-('QTR BS'!AN3-'QTR BS'!AM3)-('QTR BS'!AN12-'QTR BS'!AM12)-('QTR BS'!AN13-'QTR BS'!AM13)+('QTR BS'!AN24-'QTR BS'!AM24)+('QTR BS'!AN26-'QTR BS'!AM26)+('QTR BS'!AN28-'QTR BS'!AM28)+('QTR BS'!AN32-'QTR BS'!AM32)</f>
-        <v>55695.371860840714</v>
+        <v>2430.8322175702488</v>
       </c>
       <c r="AR22" s="4">
         <f>-('QTR BS'!AO14-'QTR BS'!AN14)+('QTR BS'!AO19-'QTR BS'!AN19)+('QTR BS'!AO21-'QTR BS'!AN21)+('QTR BS'!AO23-'QTR BS'!AN23)+('QTR BS'!AO25-'QTR BS'!AN25)-('QTR BS'!AO3-'QTR BS'!AN3)-('QTR BS'!AO12-'QTR BS'!AN12)-('QTR BS'!AO13-'QTR BS'!AN13)+('QTR BS'!AO24-'QTR BS'!AN24)+('QTR BS'!AO26-'QTR BS'!AN26)+('QTR BS'!AO28-'QTR BS'!AN28)+('QTR BS'!AO32-'QTR BS'!AN32)</f>
-        <v>18536.954924061356</v>
+        <v>2455.1405397459457</v>
       </c>
       <c r="AS22" s="4">
         <f>-('QTR BS'!AP14-'QTR BS'!AO14)+('QTR BS'!AP19-'QTR BS'!AO19)+('QTR BS'!AP21-'QTR BS'!AO21)+('QTR BS'!AP23-'QTR BS'!AO23)+('QTR BS'!AP25-'QTR BS'!AO25)-('QTR BS'!AP3-'QTR BS'!AO3)-('QTR BS'!AP12-'QTR BS'!AO12)-('QTR BS'!AP13-'QTR BS'!AO13)+('QTR BS'!AP24-'QTR BS'!AO24)+('QTR BS'!AP26-'QTR BS'!AO26)+('QTR BS'!AP28-'QTR BS'!AO28)+('QTR BS'!AP32-'QTR BS'!AO32)</f>
-        <v>-14320.051200103422</v>
+        <v>2479.6919451433496</v>
       </c>
     </row>
     <row r="23" spans="1:45" x14ac:dyDescent="0.25">
@@ -18671,83 +18672,83 @@
       </c>
       <c r="Z24" s="4">
         <f>-('QTR BS'!W9-'QTR BS'!V9)</f>
-        <v>-11434.491323871829</v>
+        <v>-4873.2899999999208</v>
       </c>
       <c r="AA24" s="4">
         <f>-('QTR BS'!X9-'QTR BS'!W9)</f>
-        <v>-69126.538630196534</v>
+        <v>-4922.02290000004</v>
       </c>
       <c r="AB24" s="4">
         <f>-('QTR BS'!Y9-'QTR BS'!X9)</f>
-        <v>-23007.21743713296</v>
+        <v>-4971.2431290000095</v>
       </c>
       <c r="AC24" s="4">
         <f>-('QTR BS'!Z9-'QTR BS'!Y9)</f>
-        <v>17773.390129141626</v>
+        <v>-5020.9555602899636</v>
       </c>
       <c r="AD24" s="4">
         <f>-('QTR BS'!AA9-'QTR BS'!Z9)</f>
-        <v>-13447.547290161252</v>
+        <v>-5071.1651158928871</v>
       </c>
       <c r="AE24" s="4">
         <f>-('QTR BS'!AB9-'QTR BS'!AA9)</f>
-        <v>-81296.348994032829</v>
+        <v>-5121.8767670519301</v>
       </c>
       <c r="AF24" s="4">
         <f>-('QTR BS'!AC9-'QTR BS'!AB9)</f>
-        <v>-27057.665770837688</v>
+        <v>-5173.0955347223789</v>
       </c>
       <c r="AG24" s="4">
         <f>-('QTR BS'!AD9-'QTR BS'!AC9)</f>
-        <v>20902.416863016784</v>
+        <v>-5224.8264900695649</v>
       </c>
       <c r="AH24" s="4">
         <f>-('QTR BS'!AE9-'QTR BS'!AD9)</f>
-        <v>-15815.004183316021</v>
+        <v>-5277.0747549701482</v>
       </c>
       <c r="AI24" s="4">
         <f>-('QTR BS'!AF9-'QTR BS'!AE9)</f>
-        <v>-95608.669126570923</v>
+        <v>-5329.8455025200965</v>
       </c>
       <c r="AJ24" s="4">
         <f>-('QTR BS'!AG9-'QTR BS'!AF9)</f>
-        <v>-31821.200410995632</v>
+        <v>-5383.1439575451659</v>
       </c>
       <c r="AK24" s="4">
         <f>-('QTR BS'!AH9-'QTR BS'!AG9)</f>
-        <v>24582.312521174899</v>
+        <v>-5436.9753971206956</v>
       </c>
       <c r="AL24" s="4">
         <f>-('QTR BS'!AI9-'QTR BS'!AH9)</f>
-        <v>-18599.254713258706</v>
+        <v>-5491.3451510918094</v>
       </c>
       <c r="AM24" s="4">
         <f>-('QTR BS'!AJ9-'QTR BS'!AI9)</f>
-        <v>-112440.69045247114</v>
+        <v>-5546.2586026027566</v>
       </c>
       <c r="AN24" s="4">
         <f>-('QTR BS'!AK9-'QTR BS'!AJ9)</f>
-        <v>-37423.3610605133</v>
+        <v>-5601.7211886288133</v>
       </c>
       <c r="AO24" s="4">
         <f>-('QTR BS'!AL9-'QTR BS'!AK9)</f>
-        <v>28910.058241059422</v>
+        <v>-5657.7384005150525</v>
       </c>
       <c r="AP24" s="4">
         <f>-('QTR BS'!AM9-'QTR BS'!AL9)</f>
-        <v>-21873.675901623676</v>
+        <v>-5714.3157845201204</v>
       </c>
       <c r="AQ24" s="4">
         <f>-('QTR BS'!AN9-'QTR BS'!AM9)</f>
-        <v>-132236.00940089661</v>
+        <v>-5771.4589423654834</v>
       </c>
       <c r="AR24" s="4">
         <f>-('QTR BS'!AO9-'QTR BS'!AN9)</f>
-        <v>-44011.788838160923</v>
+        <v>-5829.1735317890998</v>
       </c>
       <c r="AS24" s="4">
         <f>-('QTR BS'!AP9-'QTR BS'!AO9)</f>
-        <v>33999.708806138486</v>
+        <v>-5887.4652671070071</v>
       </c>
     </row>
     <row r="25" spans="1:45" x14ac:dyDescent="0.25">
@@ -19235,7 +19236,7 @@
     </row>
     <row r="28" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B28" s="13">
         <f>IFERROR('QTR CF'!B29/'QTR P&amp;L'!B2,"")</f>
@@ -21288,23 +21289,23 @@
       </c>
       <c r="I2" s="11">
         <f>'QTR P&amp;L'!Z2+'QTR P&amp;L'!AA2+'QTR P&amp;L'!AB2+'QTR P&amp;L'!AC2</f>
-        <v>9754572.0726953745</v>
+        <v>8739459.0295755304</v>
       </c>
       <c r="J2" s="11">
         <f>'QTR P&amp;L'!AD2+'QTR P&amp;L'!AE2+'QTR P&amp;L'!AF2+'QTR P&amp;L'!AG2</f>
-        <v>11471876.231958158</v>
+        <v>9094316.1114070043</v>
       </c>
       <c r="K2" s="11">
         <f>'QTR P&amp;L'!AH2+'QTR P&amp;L'!AI2+'QTR P&amp;L'!AJ2+'QTR P&amp;L'!AK2</f>
-        <v>13491513.856332794</v>
+        <v>9463581.813737737</v>
       </c>
       <c r="L2" s="11">
         <f>'QTR P&amp;L'!AL2+'QTR P&amp;L'!AM2+'QTR P&amp;L'!AN2+'QTR P&amp;L'!AO2</f>
-        <v>15866711.116403863</v>
+        <v>9847841.1843385641</v>
       </c>
       <c r="M2" s="11">
         <f>'QTR P&amp;L'!AP2+'QTR P&amp;L'!AQ2+'QTR P&amp;L'!AR2+'QTR P&amp;L'!AS2</f>
-        <v>18660064.714179095</v>
+        <v>10247703.02626586</v>
       </c>
       <c r="N2" s="5"/>
     </row>
@@ -21335,23 +21336,23 @@
       </c>
       <c r="I3" s="11">
         <f>'QTR P&amp;L'!Z3+'QTR P&amp;L'!AA3+'QTR P&amp;L'!AB3+'QTR P&amp;L'!AC3</f>
-        <v>-4338044.6402482064</v>
+        <v>-3886604.4680771995</v>
       </c>
       <c r="J3" s="11">
         <f>'QTR P&amp;L'!AD3+'QTR P&amp;L'!AE3+'QTR P&amp;L'!AF3+'QTR P&amp;L'!AG3</f>
-        <v>-5101762.6227744631</v>
+        <v>-4044416.1947650518</v>
       </c>
       <c r="K3" s="11">
         <f>'QTR P&amp;L'!AH3+'QTR P&amp;L'!AI3+'QTR P&amp;L'!AJ3+'QTR P&amp;L'!AK3</f>
-        <v>-5999934.0757473968</v>
+        <v>-4208635.7103814539</v>
       </c>
       <c r="L3" s="11">
         <f>'QTR P&amp;L'!AL3+'QTR P&amp;L'!AM3+'QTR P&amp;L'!AN3+'QTR P&amp;L'!AO3</f>
-        <v>-7056229.6945398673</v>
+        <v>-4379523.1968521401</v>
       </c>
       <c r="M3" s="11">
         <f>'QTR P&amp;L'!AP3+'QTR P&amp;L'!AQ3+'QTR P&amp;L'!AR3+'QTR P&amp;L'!AS3</f>
-        <v>-8298487.4289479479</v>
+        <v>-4557349.4005323565</v>
       </c>
       <c r="N3" s="5"/>
     </row>
@@ -21389,23 +21390,23 @@
       </c>
       <c r="I4" s="7">
         <f t="shared" si="0"/>
-        <v>5416527.432447168</v>
+        <v>4852854.5614983309</v>
       </c>
       <c r="J4" s="7">
         <f t="shared" si="0"/>
-        <v>6370113.6091836952</v>
+        <v>5049899.9166419525</v>
       </c>
       <c r="K4" s="7">
         <f t="shared" si="0"/>
-        <v>7491579.780585397</v>
+        <v>5254946.1033562832</v>
       </c>
       <c r="L4" s="7">
         <f t="shared" si="0"/>
-        <v>8810481.4218639955</v>
+        <v>5468317.9874864239</v>
       </c>
       <c r="M4" s="7">
         <f t="shared" si="0"/>
-        <v>10361577.285231147</v>
+        <v>5690353.6257335031</v>
       </c>
       <c r="N4" s="7">
         <f t="shared" si="0"/>
@@ -21439,23 +21440,23 @@
       </c>
       <c r="I5" s="11">
         <f>'QTR P&amp;L'!Z5+'QTR P&amp;L'!AA5+'QTR P&amp;L'!AB5+'QTR P&amp;L'!AC5</f>
-        <v>-2932702.5524019599</v>
+        <v>-2627509.8089019894</v>
       </c>
       <c r="J5" s="11">
         <f>'QTR P&amp;L'!AD5+'QTR P&amp;L'!AE5+'QTR P&amp;L'!AF5+'QTR P&amp;L'!AG5</f>
-        <v>-3449008.3681350774</v>
+        <v>-2734197.2434577448</v>
       </c>
       <c r="K5" s="11">
         <f>'QTR P&amp;L'!AH5+'QTR P&amp;L'!AI5+'QTR P&amp;L'!AJ5+'QTR P&amp;L'!AK5</f>
-        <v>-4056210.4444321962</v>
+        <v>-2845216.6156730754</v>
       </c>
       <c r="L5" s="11">
         <f>'QTR P&amp;L'!AL5+'QTR P&amp;L'!AM5+'QTR P&amp;L'!AN5+'QTR P&amp;L'!AO5</f>
-        <v>-4770311.1774173789</v>
+        <v>-2960743.8195880316</v>
       </c>
       <c r="M5" s="11">
         <f>'QTR P&amp;L'!AP5+'QTR P&amp;L'!AQ5+'QTR P&amp;L'!AR5+'QTR P&amp;L'!AS5</f>
-        <v>-5610130.2043214459</v>
+        <v>-3080961.8912460222</v>
       </c>
       <c r="N5" s="5"/>
     </row>
@@ -21493,23 +21494,23 @@
       </c>
       <c r="I6" s="7">
         <f t="shared" si="1"/>
-        <v>2483824.8800452081</v>
+        <v>2225344.7525963415</v>
       </c>
       <c r="J6" s="7">
         <f t="shared" si="1"/>
-        <v>2921105.2410486178</v>
+        <v>2315702.6731842076</v>
       </c>
       <c r="K6" s="7">
         <f t="shared" si="1"/>
-        <v>3435369.3361532008</v>
+        <v>2409729.4876832077</v>
       </c>
       <c r="L6" s="7">
         <f t="shared" si="1"/>
-        <v>4040170.2444466166</v>
+        <v>2507574.1678983923</v>
       </c>
       <c r="M6" s="7">
         <f t="shared" si="1"/>
-        <v>4751447.0809097011</v>
+        <v>2609391.7344874809</v>
       </c>
       <c r="N6" s="7">
         <f t="shared" si="1"/>
@@ -21644,23 +21645,23 @@
       </c>
       <c r="I9" s="7">
         <f t="shared" si="2"/>
-        <v>2586436.8800452081</v>
+        <v>2327956.7525963415</v>
       </c>
       <c r="J9" s="7">
         <f t="shared" si="2"/>
-        <v>3023717.2410486178</v>
+        <v>2418314.6731842076</v>
       </c>
       <c r="K9" s="7">
         <f t="shared" si="2"/>
-        <v>3537981.3361532008</v>
+        <v>2512341.4876832077</v>
       </c>
       <c r="L9" s="7">
         <f t="shared" si="2"/>
-        <v>4142782.2444466166</v>
+        <v>2610186.1678983923</v>
       </c>
       <c r="M9" s="7">
         <f t="shared" si="2"/>
-        <v>4854059.0809097011</v>
+        <v>2712003.7344874809</v>
       </c>
       <c r="N9" s="7">
         <f t="shared" si="2"/>
@@ -21694,23 +21695,23 @@
       </c>
       <c r="I10" s="11">
         <f>'QTR P&amp;L'!Z10+'QTR P&amp;L'!AA10+'QTR P&amp;L'!AB10+'QTR P&amp;L'!AC10</f>
-        <v>-542044.55337310943</v>
+        <v>-487874.37573614449</v>
       </c>
       <c r="J10" s="11">
         <f>'QTR P&amp;L'!AD10+'QTR P&amp;L'!AE10+'QTR P&amp;L'!AF10+'QTR P&amp;L'!AG10</f>
-        <v>-633686.23997587035</v>
+        <v>-506810.85900648747</v>
       </c>
       <c r="K10" s="11">
         <f>'QTR P&amp;L'!AH10+'QTR P&amp;L'!AI10+'QTR P&amp;L'!AJ10+'QTR P&amp;L'!AK10</f>
-        <v>-741461.55585441482</v>
+        <v>-526516.23943290464</v>
       </c>
       <c r="L10" s="11">
         <f>'QTR P&amp;L'!AL10+'QTR P&amp;L'!AM10+'QTR P&amp;L'!AN10+'QTR P&amp;L'!AO10</f>
-        <v>-868210.84586988366</v>
+        <v>-547021.73732320964</v>
       </c>
       <c r="M10" s="11">
         <f>'QTR P&amp;L'!AP10+'QTR P&amp;L'!AQ10+'QTR P&amp;L'!AR10+'QTR P&amp;L'!AS10</f>
-        <v>-1017274.5010163925</v>
+        <v>-568359.84065490752</v>
       </c>
       <c r="N10" s="5"/>
     </row>
@@ -21748,23 +21749,23 @@
       </c>
       <c r="I11" s="7">
         <f t="shared" si="3"/>
-        <v>2044392.3266720986</v>
+        <v>1840082.3768601972</v>
       </c>
       <c r="J11" s="7">
         <f t="shared" si="3"/>
-        <v>2390031.0010727476</v>
+        <v>1911503.8141777201</v>
       </c>
       <c r="K11" s="7">
         <f t="shared" si="3"/>
-        <v>2796519.7802987862</v>
+        <v>1985825.2482503031</v>
       </c>
       <c r="L11" s="7">
         <f t="shared" si="3"/>
-        <v>3274571.3985767327</v>
+        <v>2063164.4305751827</v>
       </c>
       <c r="M11" s="7">
         <f t="shared" si="3"/>
-        <v>3836784.5798933087</v>
+        <v>2143643.8938325737</v>
       </c>
       <c r="N11" s="7">
         <f t="shared" si="3"/>
@@ -21933,23 +21934,23 @@
       </c>
       <c r="I16" s="7">
         <f t="shared" si="4"/>
-        <v>2044392.3266720986</v>
+        <v>1840082.3768601972</v>
       </c>
       <c r="J16" s="7">
         <f t="shared" si="4"/>
-        <v>2390031.0010727476</v>
+        <v>1911503.8141777201</v>
       </c>
       <c r="K16" s="7">
         <f t="shared" si="4"/>
-        <v>2796519.7802987862</v>
+        <v>1985825.2482503031</v>
       </c>
       <c r="L16" s="7">
         <f t="shared" si="4"/>
-        <v>3274571.3985767327</v>
+        <v>2063164.4305751827</v>
       </c>
       <c r="M16" s="7">
         <f t="shared" si="4"/>
-        <v>3836784.5798933087</v>
+        <v>2143643.8938325737</v>
       </c>
       <c r="N16" s="7">
         <f t="shared" si="4"/>
@@ -22033,23 +22034,23 @@
       </c>
       <c r="H2" s="11">
         <f>'QTR BS'!Z2</f>
-        <v>4180582.3986528106</v>
+        <v>4159890.5907258056</v>
       </c>
       <c r="I2" s="11">
         <f>'QTR BS'!AD2</f>
-        <v>6606820.1050659539</v>
+        <v>6307804.4224750893</v>
       </c>
       <c r="J2" s="11">
         <f>'QTR BS'!AH2</f>
-        <v>9425591.1359290257</v>
+        <v>8534950.0943557695</v>
       </c>
       <c r="K2" s="11">
         <f>'QTR BS'!AL2</f>
-        <v>12706001.455676291</v>
+        <v>10844544.736796862</v>
       </c>
       <c r="L2" s="11">
         <f>'QTR BS'!AP2</f>
-        <v>16529323.216993876</v>
+        <v>13239936.108623488</v>
       </c>
       <c r="M2" s="5"/>
     </row>
@@ -22121,23 +22122,23 @@
       </c>
       <c r="H4" s="11">
         <f>'QTR BS'!Z4</f>
-        <v>1902935.5239842809</v>
+        <v>1683772.21166872</v>
       </c>
       <c r="I4" s="11">
         <f>'QTR BS'!AD4</f>
-        <v>2237949.6143813925</v>
+        <v>1752140.1153890388</v>
       </c>
       <c r="J4" s="11">
         <f>'QTR BS'!AH4</f>
-        <v>2631943.3387965891</v>
+        <v>1823284.0301556971</v>
       </c>
       <c r="K4" s="11">
         <f>'QTR BS'!AL4</f>
-        <v>3095300.1328184558</v>
+        <v>1897316.6731489792</v>
       </c>
       <c r="L4" s="11">
         <f>'QTR BS'!AP4</f>
-        <v>3640231.4483740539</v>
+        <v>1974355.3383186876</v>
       </c>
       <c r="M4" s="5"/>
     </row>
@@ -22165,23 +22166,23 @@
       </c>
       <c r="H5" s="11">
         <f>'QTR BS'!Z5</f>
-        <v>940397.59200757591</v>
+        <v>832090.90028822992</v>
       </c>
       <c r="I5" s="11">
         <f>'QTR BS'!AD5</f>
-        <v>1105955.7204503212</v>
+        <v>865877.12752444239</v>
       </c>
       <c r="J5" s="11">
         <f>'QTR BS'!AH5</f>
-        <v>1300660.5567604809</v>
+        <v>901035.21106921614</v>
       </c>
       <c r="K5" s="11">
         <f>'QTR BS'!AL5</f>
-        <v>1529643.4139548128</v>
+        <v>937620.85378982278</v>
       </c>
       <c r="L5" s="11">
         <f>'QTR BS'!AP5</f>
-        <v>1798938.9788854921</v>
+        <v>975692.02031331358</v>
       </c>
       <c r="M5" s="5"/>
     </row>
@@ -22209,23 +22210,23 @@
       </c>
       <c r="H6" s="11">
         <f>'QTR BS'!Z6</f>
-        <v>121781.27823984115</v>
+        <v>107755.58583950999</v>
       </c>
       <c r="I6" s="11">
         <f>'QTR BS'!AD6</f>
-        <v>143221.018915603</v>
+        <v>112130.89472449332</v>
       </c>
       <c r="J6" s="11">
         <f>'QTR BS'!AH6</f>
-        <v>168435.25175376967</v>
+        <v>116683.85869519562</v>
       </c>
       <c r="K6" s="11">
         <f>'QTR BS'!AL6</f>
-        <v>198088.48064454726</v>
+        <v>121421.69126049394</v>
       </c>
       <c r="L6" s="11">
         <f>'QTR BS'!AP6</f>
-        <v>232962.19618816816</v>
+        <v>126351.89882665196</v>
       </c>
       <c r="M6" s="5"/>
     </row>
@@ -22253,23 +22254,23 @@
       </c>
       <c r="H7" s="11">
         <f>'QTR BS'!Z7</f>
-        <v>87776.933723353941</v>
+        <v>77667.561494369991</v>
       </c>
       <c r="I7" s="11">
         <f>'QTR BS'!AD7</f>
-        <v>103230.16860101651</v>
+        <v>80821.175937963009</v>
       </c>
       <c r="J7" s="11">
         <f>'QTR BS'!AH7</f>
-        <v>121403.96408674089</v>
+        <v>84102.839773959829</v>
       </c>
       <c r="K7" s="11">
         <f>'QTR BS'!AL7</f>
-        <v>142777.2781515106</v>
+        <v>87517.752321170105</v>
       </c>
       <c r="L7" s="11">
         <f>'QTR BS'!AP7</f>
-        <v>167913.38989383305</v>
+        <v>91071.324011596429</v>
       </c>
       <c r="M7" s="5"/>
     </row>
@@ -22303,23 +22304,23 @@
       </c>
       <c r="H8" s="7">
         <f t="shared" si="0"/>
-        <v>7910557.7266078629</v>
+        <v>7538260.8500166358</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" si="0"/>
-        <v>10874260.627414286</v>
+        <v>9795857.7360510286</v>
       </c>
       <c r="J8" s="7">
         <f t="shared" si="0"/>
-        <v>14325118.247326607</v>
+        <v>12137140.034049841</v>
       </c>
       <c r="K8" s="7">
         <f t="shared" si="0"/>
-        <v>18348894.76124562</v>
+        <v>14565505.707317328</v>
       </c>
       <c r="L8" s="7">
         <f t="shared" si="0"/>
-        <v>23046453.230335422</v>
+        <v>17084490.690093737</v>
       </c>
       <c r="M8" s="7">
         <f t="shared" si="0"/>
@@ -22350,23 +22351,23 @@
       </c>
       <c r="H9" s="11">
         <f>'QTR BS'!Z9</f>
-        <v>573123.8572620597</v>
+        <v>507116.51158928993</v>
       </c>
       <c r="I9" s="11">
         <f>'QTR BS'!AD9</f>
-        <v>674023.00245407468</v>
+        <v>527707.47549702669</v>
       </c>
       <c r="J9" s="11">
         <f>'QTR BS'!AH9</f>
-        <v>792685.56365378236</v>
+        <v>549134.5151091828</v>
       </c>
       <c r="K9" s="11">
         <f>'QTR BS'!AL9</f>
-        <v>932238.81163896609</v>
+        <v>571431.57845202123</v>
       </c>
       <c r="L9" s="11">
         <f>'QTR BS'!AP9</f>
-        <v>1096360.5769735088</v>
+        <v>594633.99197780294</v>
       </c>
       <c r="M9" s="5"/>
     </row>
@@ -22394,23 +22395,23 @@
       </c>
       <c r="H10" s="11">
         <f>'QTR BS'!Z10</f>
-        <v>1062117.7333250188</v>
+        <v>1064139.33473756</v>
       </c>
       <c r="I10" s="11">
         <f>'QTR BS'!AD10</f>
-        <v>1039271.4490099732</v>
+        <v>1046027.9702727575</v>
       </c>
       <c r="J10" s="11">
         <f>'QTR BS'!AH10</f>
-        <v>1012403.0488311527</v>
+        <v>1027181.2117841122</v>
       </c>
       <c r="K10" s="11">
         <f>'QTR BS'!AL10</f>
-        <v>980804.43444755091</v>
+        <v>1007569.1993253264</v>
       </c>
       <c r="L10" s="11">
         <f>'QTR BS'!AP10</f>
-        <v>943642.84595257882</v>
+        <v>987160.86051654397</v>
       </c>
       <c r="M10" s="5"/>
     </row>
@@ -22570,23 +22571,23 @@
       </c>
       <c r="H14" s="11">
         <f>'QTR BS'!Z14</f>
-        <v>187499.01952715195</v>
+        <v>165904.53791830997</v>
       </c>
       <c r="I14" s="11">
         <f>'QTR BS'!AD14</f>
-        <v>220508.44768986781</v>
+        <v>172640.92743499044</v>
       </c>
       <c r="J14" s="11">
         <f>'QTR BS'!AH14</f>
-        <v>259329.22542858348</v>
+        <v>179650.8413789701</v>
       </c>
       <c r="K14" s="11">
         <f>'QTR BS'!AL14</f>
-        <v>304984.44783382886</v>
+        <v>186945.38593883021</v>
       </c>
       <c r="L14" s="11">
         <f>'QTR BS'!AP14</f>
-        <v>358677.3271187708</v>
+        <v>194536.11825894436</v>
       </c>
       <c r="M14" s="5"/>
     </row>
@@ -22620,23 +22621,23 @@
       </c>
       <c r="H15" s="7">
         <f t="shared" si="1"/>
-        <v>12617835.336722095</v>
+        <v>12159958.234261796</v>
       </c>
       <c r="I15" s="7">
         <f t="shared" si="1"/>
-        <v>15677580.5265682</v>
+        <v>14411751.109255802</v>
       </c>
       <c r="J15" s="7">
         <f t="shared" si="1"/>
-        <v>19244033.085240126</v>
+        <v>16747603.602322105</v>
       </c>
       <c r="K15" s="7">
         <f t="shared" si="1"/>
-        <v>23406399.455165967</v>
+        <v>19170928.871033505</v>
       </c>
       <c r="L15" s="7">
         <f t="shared" si="1"/>
-        <v>28269590.980380282</v>
+        <v>21685278.660847031</v>
       </c>
       <c r="M15" s="7">
         <f t="shared" si="1"/>
@@ -22667,23 +22668,23 @@
       </c>
       <c r="H16" s="11">
         <f>'QTR BS'!Z16</f>
-        <v>665614.40421160439</v>
+        <v>588954.81395573996</v>
       </c>
       <c r="I16" s="11">
         <f>'QTR BS'!AD16</f>
-        <v>782796.62156560051</v>
+        <v>612868.7411111471</v>
       </c>
       <c r="J16" s="11">
         <f>'QTR BS'!AH16</f>
-        <v>920608.90938849479</v>
+        <v>637753.66960391146</v>
       </c>
       <c r="K16" s="11">
         <f>'QTR BS'!AL16</f>
-        <v>1082683.2164278182</v>
+        <v>663649.02598204557</v>
       </c>
       <c r="L16" s="11">
         <f>'QTR BS'!AP16</f>
-        <v>1273290.9003814766</v>
+        <v>690595.83766951098</v>
       </c>
       <c r="M16" s="5"/>
     </row>
@@ -22711,23 +22712,23 @@
       </c>
       <c r="H17" s="11">
         <f>'QTR BS'!Z17</f>
-        <v>359971.6328190146</v>
+        <v>318513.27840085002</v>
       </c>
       <c r="I17" s="11">
         <f>'QTR BS'!AD17</f>
-        <v>423345.07223283552</v>
+        <v>331446.19474217092</v>
       </c>
       <c r="J17" s="11">
         <f>'QTR BS'!AH17</f>
-        <v>497875.48196591623</v>
+        <v>344904.23934794404</v>
       </c>
       <c r="K17" s="11">
         <f>'QTR BS'!AL17</f>
-        <v>585527.06007751019</v>
+        <v>358908.7345314704</v>
       </c>
       <c r="L17" s="11">
         <f>'QTR BS'!AP17</f>
-        <v>688609.80406037078</v>
+        <v>373481.86837747361</v>
       </c>
       <c r="M17" s="5"/>
     </row>
@@ -22755,23 +22756,23 @@
       </c>
       <c r="H18" s="11">
         <f>'QTR BS'!Z18</f>
-        <v>451685.98597382725</v>
+        <v>399664.78212069994</v>
       </c>
       <c r="I18" s="11">
         <f>'QTR BS'!AD18</f>
-        <v>531205.84769742098</v>
+        <v>415892.77493057674</v>
       </c>
       <c r="J18" s="11">
         <f>'QTR BS'!AH18</f>
-        <v>624725.27683045366</v>
+        <v>432779.68932278571</v>
       </c>
       <c r="K18" s="11">
         <f>'QTR BS'!AL18</f>
-        <v>734708.91407278797</v>
+        <v>450352.28015584499</v>
       </c>
       <c r="L18" s="11">
         <f>'QTR BS'!AP18</f>
-        <v>864055.30308726849</v>
+        <v>468638.38864281576</v>
       </c>
       <c r="M18" s="5"/>
     </row>
@@ -22799,23 +22800,23 @@
       </c>
       <c r="H19" s="11">
         <f>'QTR BS'!Z19</f>
-        <v>53302.168725210962</v>
+        <v>47163.295545230001</v>
       </c>
       <c r="I19" s="11">
         <f>'QTR BS'!AD19</f>
-        <v>62686.079712526924</v>
+        <v>49078.314469181481</v>
       </c>
       <c r="J19" s="11">
         <f>'QTR BS'!AH19</f>
-        <v>73722.039528697002</v>
+        <v>51071.090840671277</v>
       </c>
       <c r="K19" s="11">
         <f>'QTR BS'!AL19</f>
-        <v>86700.893359338064</v>
+        <v>53144.781923876806</v>
       </c>
       <c r="L19" s="11">
         <f>'QTR BS'!AP19</f>
-        <v>101964.69003521305</v>
+        <v>55302.673180561724</v>
       </c>
       <c r="M19" s="5"/>
     </row>
@@ -22843,23 +22844,23 @@
       </c>
       <c r="H20" s="11">
         <f>'QTR BS'!Z20</f>
-        <v>134096.88644958916</v>
+        <v>118652.79103222999</v>
       </c>
       <c r="I20" s="11">
         <f>'QTR BS'!AD20</f>
-        <v>157704.80478038648</v>
+        <v>123470.57014583058</v>
       </c>
       <c r="J20" s="11">
         <f>'QTR BS'!AH20</f>
-        <v>185468.92556054579</v>
+        <v>128483.97041073762</v>
       </c>
       <c r="K20" s="11">
         <f>'QTR BS'!AL20</f>
-        <v>218120.95323592445</v>
+        <v>133700.93483013491</v>
       </c>
       <c r="L20" s="11">
         <f>'QTR BS'!AP20</f>
-        <v>256521.40970114723</v>
+        <v>139129.72892498708</v>
       </c>
       <c r="M20" s="5"/>
     </row>
@@ -22887,23 +22888,23 @@
       </c>
       <c r="H21" s="11">
         <f>'QTR BS'!Z21</f>
-        <v>37992.334149723982</v>
+        <v>33616.712543049995</v>
       </c>
       <c r="I21" s="11">
         <f>'QTR BS'!AD21</f>
-        <v>44680.930324850116</v>
+        <v>34981.685875315125</v>
       </c>
       <c r="J21" s="11">
         <f>'QTR BS'!AH21</f>
-        <v>52547.06191060954</v>
+        <v>36402.08259841329</v>
       </c>
       <c r="K21" s="11">
         <f>'QTR BS'!AL21</f>
-        <v>61798.035433961035</v>
+        <v>37880.15312426009</v>
       </c>
       <c r="L21" s="11">
         <f>'QTR BS'!AP21</f>
-        <v>72677.653985560464</v>
+        <v>39418.239240519084</v>
       </c>
       <c r="M21" s="5"/>
     </row>
@@ -22937,23 +22938,23 @@
       </c>
       <c r="H22" s="7">
         <f t="shared" si="2"/>
-        <v>1702663.4123289702</v>
+        <v>1506565.6735977998</v>
       </c>
       <c r="I22" s="7">
         <f t="shared" si="2"/>
-        <v>2002419.3563136205</v>
+        <v>1567738.2812742221</v>
       </c>
       <c r="J22" s="7">
         <f t="shared" si="2"/>
-        <v>2354947.695184717</v>
+        <v>1631394.7421244634</v>
       </c>
       <c r="K22" s="7">
         <f t="shared" si="2"/>
-        <v>2769539.0726073394</v>
+        <v>1697635.9105476327</v>
       </c>
       <c r="L22" s="7">
         <f t="shared" si="2"/>
-        <v>3257119.7612510365</v>
+        <v>1766566.7360358683</v>
       </c>
       <c r="M22" s="7">
         <f t="shared" si="2"/>
@@ -22984,23 +22985,23 @@
       </c>
       <c r="H23" s="11">
         <f>'QTR BS'!Z23</f>
-        <v>188157.60820147005</v>
+        <v>166487.27616390999</v>
       </c>
       <c r="I23" s="11">
         <f>'QTR BS'!AD23</f>
-        <v>221282.98169333217</v>
+        <v>173247.32719014215</v>
       </c>
       <c r="J23" s="11">
         <f>'QTR BS'!AH23</f>
-        <v>260240.11707600468</v>
+        <v>180281.863395844</v>
       </c>
       <c r="K23" s="11">
         <f>'QTR BS'!AL23</f>
-        <v>306055.70305261912</v>
+        <v>187602.02997998748</v>
       </c>
       <c r="L23" s="11">
         <f>'QTR BS'!AP23</f>
-        <v>359937.1781087697</v>
+        <v>195219.42468131523</v>
       </c>
       <c r="M23" s="5"/>
     </row>
@@ -23028,23 +23029,23 @@
       </c>
       <c r="H24" s="11">
         <f>'QTR BS'!Z25</f>
-        <v>149436.12230517963</v>
+        <v>132225.38913465998</v>
       </c>
       <c r="I24" s="11">
         <f>'QTR BS'!AD25</f>
-        <v>175744.53157893225</v>
+        <v>137594.27015733763</v>
       </c>
       <c r="J24" s="11">
         <f>'QTR BS'!AH25</f>
-        <v>206684.56798432171</v>
+        <v>143181.1492787489</v>
       </c>
       <c r="K24" s="11">
         <f>'QTR BS'!AL25</f>
-        <v>243071.63505499749</v>
+        <v>148994.87809587471</v>
       </c>
       <c r="L24" s="11">
         <f>'QTR BS'!AP25</f>
-        <v>285864.68909856764</v>
+        <v>155044.66761602843</v>
       </c>
       <c r="M24" s="5"/>
     </row>
@@ -23122,23 +23123,23 @@
       </c>
       <c r="H26" s="7">
         <f t="shared" si="3"/>
-        <v>2040257.1428356199</v>
+        <v>1805278.3388963698</v>
       </c>
       <c r="I26" s="7">
         <f t="shared" si="3"/>
-        <v>2399446.8695858847</v>
+        <v>1878579.8786217018</v>
       </c>
       <c r="J26" s="7">
         <f t="shared" si="3"/>
-        <v>2821872.3802450434</v>
+        <v>1954857.7547990563</v>
       </c>
       <c r="K26" s="7">
         <f t="shared" si="3"/>
-        <v>3318666.410714956</v>
+        <v>2034232.8186234948</v>
       </c>
       <c r="L26" s="7">
         <f t="shared" si="3"/>
-        <v>3902921.6284583742</v>
+        <v>2116830.8283332121</v>
       </c>
       <c r="M26" s="7">
         <f t="shared" si="3"/>
@@ -23213,23 +23214,23 @@
       </c>
       <c r="H28" s="11">
         <f>'QTR BS'!Z29</f>
-        <v>5609468.8672143724</v>
+        <v>5590880.5185052305</v>
       </c>
       <c r="I28" s="11">
         <f>'QTR BS'!AD29</f>
-        <v>5819537.3292374676</v>
+        <v>5757412.0395961823</v>
       </c>
       <c r="J28" s="11">
         <f>'QTR BS'!AH29</f>
-        <v>6066588.5969514456</v>
+        <v>5930705.4082348263</v>
       </c>
       <c r="K28" s="11">
         <f>'QTR BS'!AL29</f>
-        <v>6357133.5378306387</v>
+        <v>6111035.1825466082</v>
       </c>
       <c r="L28" s="11">
         <f>'QTR BS'!AP29</f>
-        <v>6698829.26540823</v>
+        <v>6298687.0688178428</v>
       </c>
       <c r="M28" s="5"/>
     </row>
@@ -23257,23 +23258,23 @@
       </c>
       <c r="H29" s="11">
         <f>'QTR BS'!Z30</f>
-        <v>11398608.3266721</v>
+        <v>11194298.376860196</v>
       </c>
       <c r="I29" s="11">
         <f>'QTR BS'!AD30</f>
-        <v>13788639.327744847</v>
+        <v>13105802.191037919</v>
       </c>
       <c r="J29" s="11">
         <f>'QTR BS'!AH30</f>
-        <v>16585159.108043633</v>
+        <v>15091627.439288223</v>
       </c>
       <c r="K29" s="11">
         <f>'QTR BS'!AL30</f>
-        <v>19859730.506620366</v>
+        <v>17154791.869863406</v>
       </c>
       <c r="L29" s="11">
         <f>'QTR BS'!AP30</f>
-        <v>23696515.086513672</v>
+        <v>19298435.763695981</v>
       </c>
       <c r="M29" s="5"/>
     </row>
@@ -23395,23 +23396,23 @@
       </c>
       <c r="H32" s="7">
         <f t="shared" si="4"/>
-        <v>10577578.193886474</v>
+        <v>10354679.895365424</v>
       </c>
       <c r="I32" s="7">
         <f t="shared" si="4"/>
-        <v>13278133.656982314</v>
+        <v>12533171.230634101</v>
       </c>
       <c r="J32" s="7">
         <f t="shared" si="4"/>
-        <v>16422160.704995081</v>
+        <v>14792745.847523049</v>
       </c>
       <c r="K32" s="7">
         <f t="shared" si="4"/>
-        <v>20087733.044451006</v>
+        <v>17136696.052410014</v>
       </c>
       <c r="L32" s="7">
         <f t="shared" si="4"/>
-        <v>24366669.351921901</v>
+        <v>19568447.832513824</v>
       </c>
       <c r="M32" s="7">
         <f t="shared" si="4"/>
@@ -23448,23 +23449,23 @@
       </c>
       <c r="H33" s="7">
         <f t="shared" si="5"/>
-        <v>12617835.336722095</v>
+        <v>12159958.234261794</v>
       </c>
       <c r="I33" s="7">
         <f t="shared" si="5"/>
-        <v>15677580.526568199</v>
+        <v>14411751.109255802</v>
       </c>
       <c r="J33" s="7">
         <f t="shared" si="5"/>
-        <v>19244033.085240126</v>
+        <v>16747603.602322105</v>
       </c>
       <c r="K33" s="7">
         <f t="shared" si="5"/>
-        <v>23406399.45516596</v>
+        <v>19170928.871033508</v>
       </c>
       <c r="L33" s="7">
         <f t="shared" si="5"/>
-        <v>28269590.980380274</v>
+        <v>21685278.660847038</v>
       </c>
       <c r="M33" s="7">
         <f t="shared" si="5"/>
@@ -23554,23 +23555,23 @@
       </c>
       <c r="I2" s="11">
         <f>'QTR CF'!Z2+'QTR CF'!AA2+'QTR CF'!AB2+'QTR CF'!AC2</f>
-        <v>2044392.3266720993</v>
+        <v>1840082.3768601958</v>
       </c>
       <c r="J2" s="11">
         <f>'QTR CF'!AD2+'QTR CF'!AE2+'QTR CF'!AF2+'QTR CF'!AG2</f>
-        <v>2390031.0010727495</v>
+        <v>1911503.8141777215</v>
       </c>
       <c r="K2" s="11">
         <f>'QTR CF'!AH2+'QTR CF'!AI2+'QTR CF'!AJ2+'QTR CF'!AK2</f>
-        <v>2796519.7802987872</v>
+        <v>1985825.2482503033</v>
       </c>
       <c r="L2" s="11">
         <f>'QTR CF'!AL2+'QTR CF'!AM2+'QTR CF'!AN2+'QTR CF'!AO2</f>
-        <v>3274571.3985767318</v>
+        <v>2063164.4305751827</v>
       </c>
       <c r="M2" s="11">
         <f>'QTR CF'!AP2+'QTR CF'!AQ2+'QTR CF'!AR2+'QTR CF'!AS2</f>
-        <v>3836784.5798933078</v>
+        <v>2143643.8938325727</v>
       </c>
       <c r="N2" s="5"/>
     </row>
@@ -23601,23 +23602,23 @@
       </c>
       <c r="I3" s="11">
         <f>'QTR CF'!Z3+'QTR CF'!AA3+'QTR CF'!AB3+'QTR CF'!AC3</f>
-        <v>148388.48093061912</v>
+        <v>132946.38041417999</v>
       </c>
       <c r="J3" s="11">
         <f>'QTR CF'!AD3+'QTR CF'!AE3+'QTR CF'!AF3+'QTR CF'!AG3</f>
-        <v>174512.45167887409</v>
+        <v>138344.53657398117</v>
       </c>
       <c r="K3" s="11">
         <f>'QTR CF'!AH3+'QTR CF'!AI3+'QTR CF'!AJ3+'QTR CF'!AK3</f>
-        <v>205235.5789342623</v>
+        <v>143961.87952047648</v>
       </c>
       <c r="L3" s="11">
         <f>'QTR CF'!AL3+'QTR CF'!AM3+'QTR CF'!AN3+'QTR CF'!AO3</f>
-        <v>241367.54973789031</v>
+        <v>149807.30911614472</v>
       </c>
       <c r="M3" s="11">
         <f>'QTR CF'!AP3+'QTR CF'!AQ3+'QTR CF'!AR3+'QTR CF'!AS3</f>
-        <v>283860.5975094274</v>
+        <v>155890.08659356975</v>
       </c>
       <c r="N3" s="5"/>
     </row>
@@ -23883,23 +23884,23 @@
       </c>
       <c r="I9" s="11">
         <f>'QTR CF'!Z9+'QTR CF'!AA9+'QTR CF'!AB9+'QTR CF'!AC9</f>
-        <v>178621.86721437317</v>
+        <v>160033.51850522999</v>
       </c>
       <c r="J9" s="11">
         <f>'QTR CF'!AD9+'QTR CF'!AE9+'QTR CF'!AF9+'QTR CF'!AG9</f>
-        <v>210068.46202309529</v>
+        <v>166531.52109095154</v>
       </c>
       <c r="K9" s="11">
         <f>'QTR CF'!AH9+'QTR CF'!AI9+'QTR CF'!AJ9+'QTR CF'!AK9</f>
-        <v>247051.26771397737</v>
+        <v>173293.36863864376</v>
       </c>
       <c r="L9" s="11">
         <f>'QTR CF'!AL9+'QTR CF'!AM9+'QTR CF'!AN9+'QTR CF'!AO9</f>
-        <v>290544.94087919348</v>
+        <v>180329.77431178096</v>
       </c>
       <c r="M9" s="11">
         <f>'QTR CF'!AP9+'QTR CF'!AQ9+'QTR CF'!AR9+'QTR CF'!AS9</f>
-        <v>341695.7275775923</v>
+        <v>187651.88627123428</v>
       </c>
       <c r="N9" s="5"/>
     </row>
@@ -23977,23 +23978,23 @@
       </c>
       <c r="I11" s="11">
         <f>'QTR CF'!Z11+'QTR CF'!AA11+'QTR CF'!AB11+'QTR CF'!AC11</f>
-        <v>-284863.52398428088</v>
+        <v>-65700.211668720003</v>
       </c>
       <c r="J11" s="11">
         <f>'QTR CF'!AD11+'QTR CF'!AE11+'QTR CF'!AF11+'QTR CF'!AG11</f>
-        <v>-335014.09039711161</v>
+        <v>-68367.903720318805</v>
       </c>
       <c r="K11" s="11">
         <f>'QTR CF'!AH11+'QTR CF'!AI11+'QTR CF'!AJ11+'QTR CF'!AK11</f>
-        <v>-393993.72441519657</v>
+        <v>-71143.91476665833</v>
       </c>
       <c r="L11" s="11">
         <f>'QTR CF'!AL11+'QTR CF'!AM11+'QTR CF'!AN11+'QTR CF'!AO11</f>
-        <v>-463356.79402186675</v>
+        <v>-74032.642993282061</v>
       </c>
       <c r="M11" s="11">
         <f>'QTR CF'!AP11+'QTR CF'!AQ11+'QTR CF'!AR11+'QTR CF'!AS11</f>
-        <v>-544931.31555559812</v>
+        <v>-77038.665169708431</v>
       </c>
       <c r="N11" s="5"/>
     </row>
@@ -24024,23 +24025,23 @@
       </c>
       <c r="I12" s="11">
         <f>'QTR CF'!Z13+'QTR CF'!AA13+'QTR CF'!AB13+'QTR CF'!AC13</f>
-        <v>-140774.59200757591</v>
+        <v>-32467.900288229925</v>
       </c>
       <c r="J12" s="11">
         <f>'QTR CF'!AD13+'QTR CF'!AE13+'QTR CF'!AF13+'QTR CF'!AG13</f>
-        <v>-165558.12844274531</v>
+        <v>-33786.227236212464</v>
       </c>
       <c r="K12" s="11">
         <f>'QTR CF'!AH13+'QTR CF'!AI13+'QTR CF'!AJ13+'QTR CF'!AK13</f>
-        <v>-194704.83631015965</v>
+        <v>-35158.083544773748</v>
       </c>
       <c r="L12" s="11">
         <f>'QTR CF'!AL13+'QTR CF'!AM13+'QTR CF'!AN13+'QTR CF'!AO13</f>
-        <v>-228982.85719433194</v>
+        <v>-36585.642720606644</v>
       </c>
       <c r="M12" s="11">
         <f>'QTR CF'!AP13+'QTR CF'!AQ13+'QTR CF'!AR13+'QTR CF'!AS13</f>
-        <v>-269295.56493067928</v>
+        <v>-38071.1665234908</v>
       </c>
       <c r="N12" s="5"/>
     </row>
@@ -24071,23 +24072,23 @@
       </c>
       <c r="I13" s="11">
         <f>'QTR CF'!Z14+'QTR CF'!AA14+'QTR CF'!AB14+'QTR CF'!AC14</f>
-        <v>-18230.278239841151</v>
+        <v>-4204.5858395099931</v>
       </c>
       <c r="J13" s="11">
         <f>'QTR CF'!AD14+'QTR CF'!AE14+'QTR CF'!AF14+'QTR CF'!AG14</f>
-        <v>-21439.740675761845</v>
+        <v>-4375.3088849833293</v>
       </c>
       <c r="K13" s="11">
         <f>'QTR CF'!AH14+'QTR CF'!AI14+'QTR CF'!AJ14+'QTR CF'!AK14</f>
-        <v>-25214.232838166674</v>
+        <v>-4552.9639707023016</v>
       </c>
       <c r="L13" s="11">
         <f>'QTR CF'!AL14+'QTR CF'!AM14+'QTR CF'!AN14+'QTR CF'!AO14</f>
-        <v>-29653.228890777595</v>
+        <v>-4737.8325652983185</v>
       </c>
       <c r="M13" s="11">
         <f>'QTR CF'!AP14+'QTR CF'!AQ14+'QTR CF'!AR14+'QTR CF'!AS14</f>
-        <v>-34873.7155436209</v>
+        <v>-4930.2075661580166</v>
       </c>
       <c r="N13" s="5"/>
     </row>
@@ -24118,23 +24119,23 @@
       </c>
       <c r="I14" s="11">
         <f>'QTR CF'!Z15+'QTR CF'!AA15+'QTR CF'!AB15+'QTR CF'!AC15</f>
-        <v>-13139.933723353941</v>
+        <v>-3030.5614943699911</v>
       </c>
       <c r="J14" s="11">
         <f>'QTR CF'!AD15+'QTR CF'!AE15+'QTR CF'!AF15+'QTR CF'!AG15</f>
-        <v>-15453.234877662573</v>
+        <v>-3153.6144435930182</v>
       </c>
       <c r="K14" s="11">
         <f>'QTR CF'!AH15+'QTR CF'!AI15+'QTR CF'!AJ15+'QTR CF'!AK15</f>
-        <v>-18173.795485724375</v>
+        <v>-3281.6638359968201</v>
       </c>
       <c r="L14" s="11">
         <f>'QTR CF'!AL15+'QTR CF'!AM15+'QTR CF'!AN15+'QTR CF'!AO15</f>
-        <v>-21373.314064769715</v>
+        <v>-3414.9125472102751</v>
       </c>
       <c r="M14" s="11">
         <f>'QTR CF'!AP15+'QTR CF'!AQ15+'QTR CF'!AR15+'QTR CF'!AS15</f>
-        <v>-25136.11174232245</v>
+        <v>-3553.5716904263245</v>
       </c>
       <c r="N14" s="5"/>
     </row>
@@ -24165,23 +24166,23 @@
       </c>
       <c r="I15" s="11">
         <f>'QTR CF'!Z16+'QTR CF'!AA16+'QTR CF'!AB16+'QTR CF'!AC16</f>
-        <v>99640.404211604386</v>
+        <v>22980.813955739955</v>
       </c>
       <c r="J15" s="11">
         <f>'QTR CF'!AD16+'QTR CF'!AE16+'QTR CF'!AF16+'QTR CF'!AG16</f>
-        <v>117182.21735399612</v>
+        <v>23913.927155407146</v>
       </c>
       <c r="K15" s="11">
         <f>'QTR CF'!AH16+'QTR CF'!AI16+'QTR CF'!AJ16+'QTR CF'!AK16</f>
-        <v>137812.28782289429</v>
+        <v>24884.92849276436</v>
       </c>
       <c r="L15" s="11">
         <f>'QTR CF'!AL16+'QTR CF'!AM16+'QTR CF'!AN16+'QTR CF'!AO16</f>
-        <v>162074.30703932338</v>
+        <v>25895.356378134107</v>
       </c>
       <c r="M15" s="11">
         <f>'QTR CF'!AP16+'QTR CF'!AQ16+'QTR CF'!AR16+'QTR CF'!AS16</f>
-        <v>190607.68395365844</v>
+        <v>26946.811687465408</v>
       </c>
       <c r="N15" s="5"/>
     </row>
@@ -24212,23 +24213,23 @@
       </c>
       <c r="I16" s="11">
         <f>'QTR CF'!Z17+'QTR CF'!AA17+'QTR CF'!AB17+'QTR CF'!AC17</f>
-        <v>53886.632819014601</v>
+        <v>12428.278400850017</v>
       </c>
       <c r="J16" s="11">
         <f>'QTR CF'!AD17+'QTR CF'!AE17+'QTR CF'!AF17+'QTR CF'!AG17</f>
-        <v>63373.439413820917</v>
+        <v>12932.916341320903</v>
       </c>
       <c r="K16" s="11">
         <f>'QTR CF'!AH17+'QTR CF'!AI17+'QTR CF'!AJ17+'QTR CF'!AK17</f>
-        <v>74530.409733080713</v>
+        <v>13458.044605773117</v>
       </c>
       <c r="L16" s="11">
         <f>'QTR CF'!AL17+'QTR CF'!AM17+'QTR CF'!AN17+'QTR CF'!AO17</f>
-        <v>87651.578111593961</v>
+        <v>14004.495183526364</v>
       </c>
       <c r="M16" s="11">
         <f>'QTR CF'!AP17+'QTR CF'!AQ17+'QTR CF'!AR17+'QTR CF'!AS17</f>
-        <v>103082.74398286059</v>
+        <v>14573.133846003213</v>
       </c>
       <c r="N16" s="5"/>
     </row>
@@ -24259,23 +24260,23 @@
       </c>
       <c r="I17" s="11">
         <f>'QTR CF'!Z18+'QTR CF'!AA18+'QTR CF'!AB18+'QTR CF'!AC18</f>
-        <v>67615.98597382725</v>
+        <v>15594.782120699936</v>
       </c>
       <c r="J17" s="11">
         <f>'QTR CF'!AD18+'QTR CF'!AE18+'QTR CF'!AF18+'QTR CF'!AG18</f>
-        <v>79519.861723593727</v>
+        <v>16227.9928098768</v>
       </c>
       <c r="K17" s="11">
         <f>'QTR CF'!AH18+'QTR CF'!AI18+'QTR CF'!AJ18+'QTR CF'!AK18</f>
-        <v>93519.429133032681</v>
+        <v>16886.914392208972</v>
       </c>
       <c r="L17" s="11">
         <f>'QTR CF'!AL18+'QTR CF'!AM18+'QTR CF'!AN18+'QTR CF'!AO18</f>
-        <v>109983.63724233431</v>
+        <v>17572.590833059279</v>
       </c>
       <c r="M17" s="11">
         <f>'QTR CF'!AP18+'QTR CF'!AQ18+'QTR CF'!AR18+'QTR CF'!AS18</f>
-        <v>129346.38901448052</v>
+        <v>18286.10848697077</v>
       </c>
       <c r="N17" s="5"/>
     </row>
@@ -24306,23 +24307,23 @@
       </c>
       <c r="I18" s="11">
         <f>'QTR CF'!Z20+'QTR CF'!AA20+'QTR CF'!AB20+'QTR CF'!AC20</f>
-        <v>20073.886449589161</v>
+        <v>4629.7910322299867</v>
       </c>
       <c r="J18" s="11">
         <f>'QTR CF'!AD20+'QTR CF'!AE20+'QTR CF'!AF20+'QTR CF'!AG20</f>
-        <v>23607.918330797314</v>
+        <v>4817.7791136005981</v>
       </c>
       <c r="K18" s="11">
         <f>'QTR CF'!AH20+'QTR CF'!AI20+'QTR CF'!AJ20+'QTR CF'!AK20</f>
-        <v>27764.120780159312</v>
+        <v>5013.4002649070317</v>
       </c>
       <c r="L18" s="11">
         <f>'QTR CF'!AL20+'QTR CF'!AM20+'QTR CF'!AN20+'QTR CF'!AO20</f>
-        <v>32652.02767537866</v>
+        <v>5216.9644193972927</v>
       </c>
       <c r="M18" s="11">
         <f>'QTR CF'!AP20+'QTR CF'!AQ20+'QTR CF'!AR20+'QTR CF'!AS20</f>
-        <v>38400.456465222785</v>
+        <v>5428.7940948521718</v>
       </c>
       <c r="N18" s="5"/>
     </row>
@@ -24400,23 +24401,23 @@
       </c>
       <c r="I20" s="11">
         <f>'QTR CF'!Z22+'QTR CF'!AA22+'QTR CF'!AB22+'QTR CF'!AC22</f>
-        <v>36135.213854432674</v>
+        <v>8334.1354685400001</v>
       </c>
       <c r="J20" s="11">
         <f>'QTR CF'!AD22+'QTR CF'!AE22+'QTR CF'!AF22+'QTR CF'!AG22</f>
-        <v>42496.861765340975</v>
+        <v>8672.5347884459406</v>
       </c>
       <c r="K20" s="11">
         <f>'QTR CF'!AH22+'QTR CF'!AI22+'QTR CF'!AJ22+'QTR CF'!AK22</f>
-        <v>49978.485451275803</v>
+        <v>9024.6744777214262</v>
       </c>
       <c r="L20" s="11">
         <f>'QTR CF'!AL22+'QTR CF'!AM22+'QTR CF'!AN22+'QTR CF'!AO22</f>
-        <v>58777.257996037399</v>
+        <v>9391.1124504615073</v>
       </c>
       <c r="M20" s="11">
         <f>'QTR CF'!AP22+'QTR CF'!AQ22+'QTR CF'!AR22+'QTR CF'!AS22</f>
-        <v>69125.065042253205</v>
+        <v>9772.4292743112237</v>
       </c>
       <c r="N20" s="5"/>
     </row>
@@ -24501,23 +24502,23 @@
       </c>
       <c r="I22" s="7">
         <f t="shared" si="0"/>
-        <v>2206766.4701705077</v>
+        <v>2106646.817466836</v>
       </c>
       <c r="J22" s="7">
         <f t="shared" si="0"/>
-        <v>2578347.0189689868</v>
+        <v>2188281.9677661979</v>
       </c>
       <c r="K22" s="7">
         <f t="shared" si="0"/>
-        <v>3015344.7708182232</v>
+        <v>2273231.832524668</v>
       </c>
       <c r="L22" s="7">
         <f t="shared" si="0"/>
-        <v>3529276.5030867378</v>
+        <v>2361631.0024412903</v>
       </c>
       <c r="M22" s="7">
         <f t="shared" si="0"/>
-        <v>4133686.5356665836</v>
+        <v>2453619.5331371957</v>
       </c>
       <c r="N22" s="7">
         <f t="shared" si="0"/>
@@ -24551,23 +24552,23 @@
       </c>
       <c r="I23" s="11">
         <f>'QTR CF'!Z25+'QTR CF'!AA25+'QTR CF'!AB25+'QTR CF'!AC25</f>
-        <v>-85794.857262059697</v>
+        <v>-19787.511589289934</v>
       </c>
       <c r="J23" s="11">
         <f>'QTR CF'!AD25+'QTR CF'!AE25+'QTR CF'!AF25+'QTR CF'!AG25</f>
-        <v>-100899.14519201498</v>
+        <v>-20590.963907736761</v>
       </c>
       <c r="K23" s="11">
         <f>'QTR CF'!AH25+'QTR CF'!AI25+'QTR CF'!AJ25+'QTR CF'!AK25</f>
-        <v>-118662.56119970768</v>
+        <v>-21427.039612156106</v>
       </c>
       <c r="L23" s="11">
         <f>'QTR CF'!AL25+'QTR CF'!AM25+'QTR CF'!AN25+'QTR CF'!AO25</f>
-        <v>-139553.24798518373</v>
+        <v>-22297.063342838432</v>
       </c>
       <c r="M23" s="11">
         <f>'QTR CF'!AP25+'QTR CF'!AQ25+'QTR CF'!AR25+'QTR CF'!AS25</f>
-        <v>-164121.76533454272</v>
+        <v>-23202.413525781711</v>
       </c>
       <c r="N23" s="5"/>
     </row>
@@ -24739,23 +24740,23 @@
       </c>
       <c r="I27" s="11">
         <f>'QTR CF'!Z29+'QTR CF'!AA29+'QTR CF'!AB29+'QTR CF'!AC29</f>
-        <v>-128962.21425563771</v>
+        <v>-115541.71515174001</v>
       </c>
       <c r="J27" s="11">
         <f>'QTR CF'!AD29+'QTR CF'!AE29+'QTR CF'!AF29+'QTR CF'!AG29</f>
-        <v>-151666.16736382869</v>
+        <v>-120233.1721091784</v>
       </c>
       <c r="K27" s="11">
         <f>'QTR CF'!AH29+'QTR CF'!AI29+'QTR CF'!AJ29+'QTR CF'!AK29</f>
-        <v>-178367.17875544162</v>
+        <v>-125115.12103183122</v>
       </c>
       <c r="L27" s="11">
         <f>'QTR CF'!AL29+'QTR CF'!AM29+'QTR CF'!AN29+'QTR CF'!AO29</f>
-        <v>-209768.93535428843</v>
+        <v>-130195.29665735891</v>
       </c>
       <c r="M27" s="11">
         <f>'QTR CF'!AP29+'QTR CF'!AQ29+'QTR CF'!AR29+'QTR CF'!AS29</f>
-        <v>-246699.00901445519</v>
+        <v>-135481.74778478729</v>
       </c>
       <c r="N27" s="5"/>
     </row>
@@ -24934,23 +24935,23 @@
       </c>
       <c r="I31" s="7">
         <f t="shared" si="1"/>
-        <v>-214757.07151769742</v>
+        <v>-135329.22674102994</v>
       </c>
       <c r="J31" s="7">
         <f t="shared" si="1"/>
-        <v>-252565.31255584367</v>
+        <v>-140824.13601691514</v>
       </c>
       <c r="K31" s="7">
         <f t="shared" si="1"/>
-        <v>-297029.7399551493</v>
+        <v>-146542.16064398733</v>
       </c>
       <c r="L31" s="7">
         <f t="shared" si="1"/>
-        <v>-349322.18333947216</v>
+        <v>-152492.36000019734</v>
       </c>
       <c r="M31" s="7">
         <f t="shared" si="1"/>
-        <v>-410820.77434899792</v>
+        <v>-158684.161310569</v>
       </c>
       <c r="N31" s="7">
         <f t="shared" si="1"/>
@@ -25377,23 +25378,23 @@
       </c>
       <c r="I40" s="7">
         <f t="shared" si="3"/>
-        <v>2092465.3986528101</v>
+        <v>2071773.5907258061</v>
       </c>
       <c r="J40" s="7">
         <f t="shared" si="3"/>
-        <v>2426237.7064131433</v>
+        <v>2147913.8317492828</v>
       </c>
       <c r="K40" s="7">
         <f t="shared" si="3"/>
-        <v>2818771.0308630741</v>
+        <v>2227145.6718806806</v>
       </c>
       <c r="L40" s="7">
         <f t="shared" si="3"/>
-        <v>3280410.3197472654</v>
+        <v>2309594.642441093</v>
       </c>
       <c r="M40" s="7">
         <f t="shared" si="3"/>
-        <v>3823321.7613175856</v>
+        <v>2395391.3718266268</v>
       </c>
       <c r="N40" s="7">
         <f t="shared" si="3"/>
@@ -31660,83 +31661,83 @@
       </c>
       <c r="Z2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!Y2,'QTR P&amp;L'!V2)*(1+'IS DRIVERS'!AA2)</f>
-        <v>2181055.1690463959</v>
+        <v>2152363.5299999998</v>
       </c>
       <c r="AA2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!Z2,'QTR P&amp;L'!W2)*(1+'IS DRIVERS'!AB2)</f>
-        <v>2483340.3142511677</v>
+        <v>2173887.1653</v>
       </c>
       <c r="AB2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AA2,'QTR P&amp;L'!X2)*(1+'IS DRIVERS'!AC2)</f>
-        <v>2583949.1426628865</v>
+        <v>2195626.0369529999</v>
       </c>
       <c r="AC2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AB2,'QTR P&amp;L'!Y2)*(1+'IS DRIVERS'!AD2)</f>
-        <v>2506227.4467349248</v>
+        <v>2217582.2973225298</v>
       </c>
       <c r="AD2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AC2,'QTR P&amp;L'!Z2)*(1+'IS DRIVERS'!AE2)</f>
-        <v>2565032.5578515218</v>
+        <v>2239758.1202957551</v>
       </c>
       <c r="AE2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AD2,'QTR P&amp;L'!AA2)*(1+'IS DRIVERS'!AF2)</f>
-        <v>2920535.3668630533</v>
+        <v>2262155.7014987129</v>
       </c>
       <c r="AF2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AE2,'QTR P&amp;L'!AB2)*(1+'IS DRIVERS'!AG2)</f>
-        <v>3038856.5006637112</v>
+        <v>2284777.2585137002</v>
       </c>
       <c r="AG2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AF2,'QTR P&amp;L'!AC2)*(1+'IS DRIVERS'!AH2)</f>
-        <v>2947451.8065798739</v>
+        <v>2307625.031098837</v>
       </c>
       <c r="AH2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AG2,'QTR P&amp;L'!AD2)*(1+'IS DRIVERS'!AI2)</f>
-        <v>3016609.6283181002</v>
+        <v>2330701.2814098252</v>
       </c>
       <c r="AI2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AH2,'QTR P&amp;L'!AE2)*(1+'IS DRIVERS'!AJ2)</f>
-        <v>3434699.1349310586</v>
+        <v>2354008.2942239237</v>
       </c>
       <c r="AJ2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AI2,'QTR P&amp;L'!AF2)*(1+'IS DRIVERS'!AK2)</f>
-        <v>3573850.8468124638</v>
+        <v>2377548.3771661632</v>
       </c>
       <c r="AK2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AJ2,'QTR P&amp;L'!AG2)*(1+'IS DRIVERS'!AL2)</f>
-        <v>3466354.2462711716</v>
+        <v>2401323.8609378249</v>
       </c>
       <c r="AL2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AK2,'QTR P&amp;L'!AH2)*(1+'IS DRIVERS'!AM2)</f>
-        <v>3547687.385802072</v>
+        <v>2425337.0995472032</v>
       </c>
       <c r="AM2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AL2,'QTR P&amp;L'!AI2)*(1+'IS DRIVERS'!AN2)</f>
-        <v>4039382.0534922979</v>
+        <v>2449590.4705426753</v>
       </c>
       <c r="AN2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AM2,'QTR P&amp;L'!AJ2)*(1+'IS DRIVERS'!AO2)</f>
-        <v>4203031.5918084867</v>
+        <v>2474086.375248102</v>
       </c>
       <c r="AO2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AN2,'QTR P&amp;L'!AK2)*(1+'IS DRIVERS'!AP2)</f>
-        <v>4076610.0853010053</v>
+        <v>2498827.2390005831</v>
       </c>
       <c r="AP2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AO2,'QTR P&amp;L'!AL2)*(1+'IS DRIVERS'!AQ2)</f>
-        <v>4172262.0219827602</v>
+        <v>2523815.5113905887</v>
       </c>
       <c r="AQ2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AP2,'QTR P&amp;L'!AM2)*(1+'IS DRIVERS'!AR2)</f>
-        <v>4750520.1279887827</v>
+        <v>2549053.6665044948</v>
       </c>
       <c r="AR2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AQ2,'QTR P&amp;L'!AN2)*(1+'IS DRIVERS'!AS2)</f>
-        <v>4942980.364582397</v>
+        <v>2574544.20316954</v>
       </c>
       <c r="AS2" s="11">
         <f>IF('IS DRIVERS'!$B2="QoQ",'QTR P&amp;L'!AR2,'QTR P&amp;L'!AO2)*(1+'IS DRIVERS'!AT2)</f>
-        <v>4794302.199625154</v>
+        <v>2600289.6452012355</v>
       </c>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.25">
@@ -31841,83 +31842,83 @@
       </c>
       <c r="Z3" s="11">
         <f>'QTR P&amp;L'!Z2*'IS DRIVERS'!AA3</f>
-        <v>-969956.92026836041</v>
+        <v>-957197.2</v>
       </c>
       <c r="AA3" s="11">
         <f>'QTR P&amp;L'!AA2*'IS DRIVERS'!AB3</f>
-        <v>-1104388.9019288195</v>
+        <v>-966769.17200000002</v>
       </c>
       <c r="AB3" s="11">
         <f>'QTR P&amp;L'!AB2*'IS DRIVERS'!AC3</f>
-        <v>-1149131.5708640146</v>
+        <v>-976436.86371999991</v>
       </c>
       <c r="AC3" s="11">
         <f>'QTR P&amp;L'!AC2*'IS DRIVERS'!AD3</f>
-        <v>-1114567.2471870116</v>
+        <v>-986201.23235719989</v>
       </c>
       <c r="AD3" s="11">
         <f>'QTR P&amp;L'!AD2*'IS DRIVERS'!AE3</f>
-        <v>-1140719.0040449693</v>
+        <v>-996063.24468077195</v>
       </c>
       <c r="AE3" s="11">
         <f>'QTR P&amp;L'!AE2*'IS DRIVERS'!AF3</f>
-        <v>-1298817.8979516008</v>
+        <v>-1006023.8771275798</v>
       </c>
       <c r="AF3" s="11">
         <f>'QTR P&amp;L'!AF2*'IS DRIVERS'!AG3</f>
-        <v>-1351437.5676292484</v>
+        <v>-1016084.1158988556</v>
       </c>
       <c r="AG3" s="11">
         <f>'QTR P&amp;L'!AG2*'IS DRIVERS'!AH3</f>
-        <v>-1310788.1531486444</v>
+        <v>-1026244.9570578441</v>
       </c>
       <c r="AH3" s="11">
         <f>'QTR P&amp;L'!AH2*'IS DRIVERS'!AI3</f>
-        <v>-1341543.958291807</v>
+        <v>-1036507.4066284224</v>
       </c>
       <c r="AI3" s="11">
         <f>'QTR P&amp;L'!AI2*'IS DRIVERS'!AJ3</f>
-        <v>-1527476.3528438115</v>
+        <v>-1046872.4806947068</v>
       </c>
       <c r="AJ3" s="11">
         <f>'QTR P&amp;L'!AJ2*'IS DRIVERS'!AK3</f>
-        <v>-1589359.7787296271</v>
+        <v>-1057341.205501654</v>
       </c>
       <c r="AK3" s="11">
         <f>'QTR P&amp;L'!AK2*'IS DRIVERS'!AL3</f>
-        <v>-1541553.9858821507</v>
+        <v>-1067914.6175566704</v>
       </c>
       <c r="AL3" s="11">
         <f>'QTR P&amp;L'!AL2*'IS DRIVERS'!AM3</f>
-        <v>-1577724.3875550441</v>
+        <v>-1078593.7637322373</v>
       </c>
       <c r="AM3" s="11">
         <f>'QTR P&amp;L'!AM2*'IS DRIVERS'!AN3</f>
-        <v>-1796390.404056455</v>
+        <v>-1089379.7013695596</v>
       </c>
       <c r="AN3" s="11">
         <f>'QTR P&amp;L'!AN2*'IS DRIVERS'!AO3</f>
-        <v>-1869168.4815857415</v>
+        <v>-1100273.4983832552</v>
       </c>
       <c r="AO3" s="11">
         <f>'QTR P&amp;L'!AO2*'IS DRIVERS'!AP3</f>
-        <v>-1812946.4213426267</v>
+        <v>-1111276.2333670878</v>
       </c>
       <c r="AP3" s="11">
         <f>'QTR P&amp;L'!AP2*'IS DRIVERS'!AQ3</f>
-        <v>-1855484.6657842398</v>
+        <v>-1122388.9957007586</v>
       </c>
       <c r="AQ3" s="11">
         <f>'QTR P&amp;L'!AQ2*'IS DRIVERS'!AR3</f>
-        <v>-2112647.0977950944</v>
+        <v>-1133612.8856577664</v>
       </c>
       <c r="AR3" s="11">
         <f>'QTR P&amp;L'!AR2*'IS DRIVERS'!AS3</f>
-        <v>-2198237.8435083637</v>
+        <v>-1144949.014514344</v>
       </c>
       <c r="AS3" s="11">
         <f>'QTR P&amp;L'!AS2*'IS DRIVERS'!AT3</f>
-        <v>-2132117.8218602496</v>
+        <v>-1156398.5046594876</v>
       </c>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.25">
@@ -32022,83 +32023,83 @@
       </c>
       <c r="Z4" s="7">
         <f t="shared" ref="Z4:AS4" si="0">Z2+Z3</f>
-        <v>1211098.2487780354</v>
+        <v>1195166.3299999998</v>
       </c>
       <c r="AA4" s="7">
         <f t="shared" si="0"/>
-        <v>1378951.4123223482</v>
+        <v>1207117.9933</v>
       </c>
       <c r="AB4" s="7">
         <f t="shared" si="0"/>
-        <v>1434817.571798872</v>
+        <v>1219189.1732330001</v>
       </c>
       <c r="AC4" s="7">
         <f t="shared" si="0"/>
-        <v>1391660.1995479132</v>
+        <v>1231381.0649653301</v>
       </c>
       <c r="AD4" s="7">
         <f t="shared" si="0"/>
-        <v>1424313.5538065524</v>
+        <v>1243694.875614983</v>
       </c>
       <c r="AE4" s="7">
         <f t="shared" si="0"/>
-        <v>1621717.4689114525</v>
+        <v>1256131.824371133</v>
       </c>
       <c r="AF4" s="7">
         <f t="shared" si="0"/>
-        <v>1687418.9330344629</v>
+        <v>1268693.1426148447</v>
       </c>
       <c r="AG4" s="7">
         <f t="shared" si="0"/>
-        <v>1636663.6534312295</v>
+        <v>1281380.0740409929</v>
       </c>
       <c r="AH4" s="7">
         <f t="shared" si="0"/>
-        <v>1675065.6700262933</v>
+        <v>1294193.8747814028</v>
       </c>
       <c r="AI4" s="7">
         <f t="shared" si="0"/>
-        <v>1907222.7820872471</v>
+        <v>1307135.8135292169</v>
       </c>
       <c r="AJ4" s="7">
         <f t="shared" si="0"/>
-        <v>1984491.0680828367</v>
+        <v>1320207.1716645092</v>
       </c>
       <c r="AK4" s="7">
         <f t="shared" si="0"/>
-        <v>1924800.2603890209</v>
+        <v>1333409.2433811545</v>
       </c>
       <c r="AL4" s="7">
         <f t="shared" si="0"/>
-        <v>1969962.9982470279</v>
+        <v>1346743.3358149659</v>
       </c>
       <c r="AM4" s="7">
         <f t="shared" si="0"/>
-        <v>2242991.6494358429</v>
+        <v>1360210.7691731157</v>
       </c>
       <c r="AN4" s="7">
         <f t="shared" si="0"/>
-        <v>2333863.1102227452</v>
+        <v>1373812.8768648468</v>
       </c>
       <c r="AO4" s="7">
         <f t="shared" si="0"/>
-        <v>2263663.6639583786</v>
+        <v>1387551.0056334953</v>
       </c>
       <c r="AP4" s="7">
         <f t="shared" si="0"/>
-        <v>2316777.3561985204</v>
+        <v>1401426.5156898301</v>
       </c>
       <c r="AQ4" s="7">
         <f t="shared" si="0"/>
-        <v>2637873.0301936883</v>
+        <v>1415440.7808467285</v>
       </c>
       <c r="AR4" s="7">
         <f t="shared" si="0"/>
-        <v>2744742.5210740333</v>
+        <v>1429595.188655196</v>
       </c>
       <c r="AS4" s="7">
         <f t="shared" si="0"/>
-        <v>2662184.3777649044</v>
+        <v>1443891.1405417479</v>
       </c>
     </row>
     <row r="5" spans="1:45" x14ac:dyDescent="0.25">
@@ -32203,83 +32204,83 @@
       </c>
       <c r="Z5" s="11">
         <f>'QTR P&amp;L'!Z2*'IS DRIVERS'!AA4</f>
-        <v>-655732.10321510385</v>
+        <v>-647105.98999999987</v>
       </c>
       <c r="AA5" s="11">
         <f>'QTR P&amp;L'!AA2*'IS DRIVERS'!AB4</f>
-        <v>-746613.83644630562</v>
+        <v>-653577.04989999998</v>
       </c>
       <c r="AB5" s="11">
         <f>'QTR P&amp;L'!AB2*'IS DRIVERS'!AC4</f>
-        <v>-776861.78229962778</v>
+        <v>-660112.82039899996</v>
       </c>
       <c r="AC5" s="11">
         <f>'QTR P&amp;L'!AC2*'IS DRIVERS'!AD4</f>
-        <v>-753494.83044092264</v>
+        <v>-666713.9486029899</v>
       </c>
       <c r="AD5" s="11">
         <f>'QTR P&amp;L'!AD2*'IS DRIVERS'!AE4</f>
-        <v>-771174.52957899787</v>
+        <v>-673381.08808901988</v>
       </c>
       <c r="AE5" s="11">
         <f>'QTR P&amp;L'!AE2*'IS DRIVERS'!AF4</f>
-        <v>-878056.10137983027</v>
+        <v>-680114.89896991011</v>
       </c>
       <c r="AF5" s="11">
         <f>'QTR P&amp;L'!AF2*'IS DRIVERS'!AG4</f>
-        <v>-913629.23452337366</v>
+        <v>-686916.04795960931</v>
       </c>
       <c r="AG5" s="11">
         <f>'QTR P&amp;L'!AG2*'IS DRIVERS'!AH4</f>
-        <v>-886148.50265287561</v>
+        <v>-693785.20843920531</v>
       </c>
       <c r="AH5" s="11">
         <f>'QTR P&amp;L'!AH2*'IS DRIVERS'!AI4</f>
-        <v>-906940.73411303165</v>
+        <v>-700723.06052359729</v>
       </c>
       <c r="AI5" s="11">
         <f>'QTR P&amp;L'!AI2*'IS DRIVERS'!AJ4</f>
-        <v>-1032638.9353297146</v>
+        <v>-707730.29112883331</v>
       </c>
       <c r="AJ5" s="11">
         <f>'QTR P&amp;L'!AJ2*'IS DRIVERS'!AK4</f>
-        <v>-1074474.7613981909</v>
+        <v>-714807.59404012177</v>
       </c>
       <c r="AK5" s="11">
         <f>'QTR P&amp;L'!AK2*'IS DRIVERS'!AL4</f>
-        <v>-1042156.013591259</v>
+        <v>-721955.66998052294</v>
       </c>
       <c r="AL5" s="11">
         <f>'QTR P&amp;L'!AL2*'IS DRIVERS'!AM4</f>
-        <v>-1066608.742436721</v>
+        <v>-729175.22668032825</v>
       </c>
       <c r="AM5" s="11">
         <f>'QTR P&amp;L'!AM2*'IS DRIVERS'!AN4</f>
-        <v>-1214436.2633357602</v>
+        <v>-736466.97894713155</v>
       </c>
       <c r="AN5" s="11">
         <f>'QTR P&amp;L'!AN2*'IS DRIVERS'!AO4</f>
-        <v>-1263637.3369597592</v>
+        <v>-743831.64873660286</v>
       </c>
       <c r="AO5" s="11">
         <f>'QTR P&amp;L'!AO2*'IS DRIVERS'!AP4</f>
-        <v>-1225628.8346851387</v>
+        <v>-751269.96522396884</v>
       </c>
       <c r="AP5" s="11">
         <f>'QTR P&amp;L'!AP2*'IS DRIVERS'!AQ4</f>
-        <v>-1254386.4958883389</v>
+        <v>-758782.66487620852</v>
       </c>
       <c r="AQ5" s="11">
         <f>'QTR P&amp;L'!AQ2*'IS DRIVERS'!AR4</f>
-        <v>-1428239.2298465993</v>
+        <v>-766370.49152497062</v>
       </c>
       <c r="AR5" s="11">
         <f>'QTR P&amp;L'!AR2*'IS DRIVERS'!AS4</f>
-        <v>-1486102.2117270557</v>
+        <v>-774034.19644022046</v>
       </c>
       <c r="AS5" s="11">
         <f>'QTR P&amp;L'!AS2*'IS DRIVERS'!AT4</f>
-        <v>-1441402.2668594522</v>
+        <v>-781774.5384046227</v>
       </c>
     </row>
     <row r="6" spans="1:45" x14ac:dyDescent="0.25">
@@ -32384,83 +32385,83 @@
       </c>
       <c r="Z6" s="7">
         <f t="shared" ref="Z6:AS6" si="1">Z4+Z5</f>
-        <v>555366.14556293155</v>
+        <v>548060.34</v>
       </c>
       <c r="AA6" s="7">
         <f t="shared" si="1"/>
-        <v>632337.5758760426</v>
+        <v>553540.94339999999</v>
       </c>
       <c r="AB6" s="7">
         <f t="shared" si="1"/>
-        <v>657955.78949924419</v>
+        <v>559076.35283400014</v>
       </c>
       <c r="AC6" s="7">
         <f t="shared" si="1"/>
-        <v>638165.36910699052</v>
+        <v>564667.11636234017</v>
       </c>
       <c r="AD6" s="7">
         <f t="shared" si="1"/>
-        <v>653139.02422755456</v>
+        <v>570313.78752596315</v>
       </c>
       <c r="AE6" s="7">
         <f t="shared" si="1"/>
-        <v>743661.36753162218</v>
+        <v>576016.92540122289</v>
       </c>
       <c r="AF6" s="7">
         <f t="shared" si="1"/>
-        <v>773789.6985110892</v>
+        <v>581777.09465523541</v>
       </c>
       <c r="AG6" s="7">
         <f t="shared" si="1"/>
-        <v>750515.15077835391</v>
+        <v>587594.86560178758</v>
       </c>
       <c r="AH6" s="7">
         <f t="shared" si="1"/>
-        <v>768124.93591326161</v>
+        <v>593470.81425780547</v>
       </c>
       <c r="AI6" s="7">
         <f t="shared" si="1"/>
-        <v>874583.84675753256</v>
+        <v>599405.5224003836</v>
       </c>
       <c r="AJ6" s="7">
         <f t="shared" si="1"/>
-        <v>910016.30668464582</v>
+        <v>605399.57762438746</v>
       </c>
       <c r="AK6" s="7">
         <f t="shared" si="1"/>
-        <v>882644.24679776188</v>
+        <v>611453.57340063155</v>
       </c>
       <c r="AL6" s="7">
         <f t="shared" si="1"/>
-        <v>903354.25581030687</v>
+        <v>617568.10913463763</v>
       </c>
       <c r="AM6" s="7">
         <f t="shared" si="1"/>
-        <v>1028555.3861000827</v>
+        <v>623743.79022598418</v>
       </c>
       <c r="AN6" s="7">
         <f t="shared" si="1"/>
-        <v>1070225.773262986</v>
+        <v>629981.22812824394</v>
       </c>
       <c r="AO6" s="7">
         <f t="shared" si="1"/>
-        <v>1038034.8292732399</v>
+        <v>636281.04040952644</v>
       </c>
       <c r="AP6" s="7">
         <f t="shared" si="1"/>
-        <v>1062390.8603101815</v>
+        <v>642643.85081362154</v>
       </c>
       <c r="AQ6" s="7">
         <f t="shared" si="1"/>
-        <v>1209633.8003470891</v>
+        <v>649070.28932175785</v>
       </c>
       <c r="AR6" s="7">
         <f t="shared" si="1"/>
-        <v>1258640.3093469776</v>
+        <v>655560.99221497553</v>
       </c>
       <c r="AS6" s="7">
         <f t="shared" si="1"/>
-        <v>1220782.1109054522</v>
+        <v>662116.60213712521</v>
       </c>
     </row>
     <row r="7" spans="1:45" x14ac:dyDescent="0.25">
@@ -32927,83 +32928,83 @@
       </c>
       <c r="Z9" s="7">
         <f t="shared" ref="Z9:AS9" si="2">Z6+SUM(Z7:Z8)</f>
-        <v>581019.14556293155</v>
+        <v>573713.34</v>
       </c>
       <c r="AA9" s="7">
         <f t="shared" si="2"/>
-        <v>657990.5758760426</v>
+        <v>579193.94339999999</v>
       </c>
       <c r="AB9" s="7">
         <f t="shared" si="2"/>
-        <v>683608.78949924419</v>
+        <v>584729.35283400014</v>
       </c>
       <c r="AC9" s="7">
         <f t="shared" si="2"/>
-        <v>663818.36910699052</v>
+        <v>590320.11636234017</v>
       </c>
       <c r="AD9" s="7">
         <f t="shared" si="2"/>
-        <v>678792.02422755456</v>
+        <v>595966.78752596315</v>
       </c>
       <c r="AE9" s="7">
         <f t="shared" si="2"/>
-        <v>769314.36753162218</v>
+        <v>601669.92540122289</v>
       </c>
       <c r="AF9" s="7">
         <f t="shared" si="2"/>
-        <v>799442.6985110892</v>
+        <v>607430.09465523541</v>
       </c>
       <c r="AG9" s="7">
         <f t="shared" si="2"/>
-        <v>776168.15077835391</v>
+        <v>613247.86560178758</v>
       </c>
       <c r="AH9" s="7">
         <f t="shared" si="2"/>
-        <v>793777.93591326161</v>
+        <v>619123.81425780547</v>
       </c>
       <c r="AI9" s="7">
         <f t="shared" si="2"/>
-        <v>900236.84675753256</v>
+        <v>625058.5224003836</v>
       </c>
       <c r="AJ9" s="7">
         <f t="shared" si="2"/>
-        <v>935669.30668464582</v>
+        <v>631052.57762438746</v>
       </c>
       <c r="AK9" s="7">
         <f t="shared" si="2"/>
-        <v>908297.24679776188</v>
+        <v>637106.57340063155</v>
       </c>
       <c r="AL9" s="7">
         <f t="shared" si="2"/>
-        <v>929007.25581030687</v>
+        <v>643221.10913463763</v>
       </c>
       <c r="AM9" s="7">
         <f t="shared" si="2"/>
-        <v>1054208.3861000827</v>
+        <v>649396.79022598418</v>
       </c>
       <c r="AN9" s="7">
         <f t="shared" si="2"/>
-        <v>1095878.773262986</v>
+        <v>655634.22812824394</v>
       </c>
       <c r="AO9" s="7">
         <f t="shared" si="2"/>
-        <v>1063687.8292732399</v>
+        <v>661934.04040952644</v>
       </c>
       <c r="AP9" s="7">
         <f t="shared" si="2"/>
-        <v>1088043.8603101815</v>
+        <v>668296.85081362154</v>
       </c>
       <c r="AQ9" s="7">
         <f t="shared" si="2"/>
-        <v>1235286.8003470891</v>
+        <v>674723.28932175785</v>
       </c>
       <c r="AR9" s="7">
         <f t="shared" si="2"/>
-        <v>1284293.3093469776</v>
+        <v>681213.99221497553</v>
       </c>
       <c r="AS9" s="7">
         <f t="shared" si="2"/>
-        <v>1246435.1109054522</v>
+        <v>687769.60213712521</v>
       </c>
     </row>
     <row r="10" spans="1:45" x14ac:dyDescent="0.25">
@@ -33108,83 +33109,83 @@
       </c>
       <c r="Z10" s="11">
         <f>'QTR P&amp;L'!Z9*'IS DRIVERS'!AA7</f>
-        <v>-121765.30024284993</v>
+        <v>-120234.20851432462</v>
       </c>
       <c r="AA10" s="11">
         <f>'QTR P&amp;L'!AA9*'IS DRIVERS'!AB7</f>
-        <v>-137896.35099009663</v>
+        <v>-121382.7891137925</v>
       </c>
       <c r="AB10" s="11">
         <f>'QTR P&amp;L'!AB9*'IS DRIVERS'!AC7</f>
-        <v>-143265.20930971761</v>
+        <v>-122542.85551925508</v>
       </c>
       <c r="AC10" s="11">
         <f>'QTR P&amp;L'!AC9*'IS DRIVERS'!AD7</f>
-        <v>-139117.69283044527</v>
+        <v>-123714.52258877228</v>
       </c>
       <c r="AD10" s="11">
         <f>'QTR P&amp;L'!AD9*'IS DRIVERS'!AE7</f>
-        <v>-142255.75054405443</v>
+        <v>-124897.90632898454</v>
       </c>
       <c r="AE10" s="11">
         <f>'QTR P&amp;L'!AE9*'IS DRIVERS'!AF7</f>
-        <v>-161226.692199388</v>
+        <v>-126093.12390659904</v>
       </c>
       <c r="AF10" s="11">
         <f>'QTR P&amp;L'!AF9*'IS DRIVERS'!AG7</f>
-        <v>-167540.74449103215</v>
+        <v>-127300.29365998971</v>
       </c>
       <c r="AG10" s="11">
         <f>'QTR P&amp;L'!AG9*'IS DRIVERS'!AH7</f>
-        <v>-162663.05274139583</v>
+        <v>-128519.53511091419</v>
       </c>
       <c r="AH10" s="11">
         <f>'QTR P&amp;L'!AH9*'IS DRIVERS'!AI7</f>
-        <v>-166353.56929414489</v>
+        <v>-129750.96897634797</v>
       </c>
       <c r="AI10" s="11">
         <f>'QTR P&amp;L'!AI9*'IS DRIVERS'!AJ7</f>
-        <v>-188664.36807155865</v>
+        <v>-130994.7171804361</v>
       </c>
       <c r="AJ10" s="11">
         <f>'QTR P&amp;L'!AJ9*'IS DRIVERS'!AK7</f>
-        <v>-196090.01687214605</v>
+        <v>-132250.9028665651</v>
       </c>
       <c r="AK10" s="11">
         <f>'QTR P&amp;L'!AK9*'IS DRIVERS'!AL7</f>
-        <v>-190353.60161656531</v>
+        <v>-133519.65040955541</v>
       </c>
       <c r="AL10" s="11">
         <f>'QTR P&amp;L'!AL9*'IS DRIVERS'!AM7</f>
-        <v>-194693.83805232236</v>
+        <v>-134801.08542797554</v>
       </c>
       <c r="AM10" s="11">
         <f>'QTR P&amp;L'!AM9*'IS DRIVERS'!AN7</f>
-        <v>-220932.47981981208</v>
+        <v>-136095.33479657996</v>
       </c>
       <c r="AN10" s="11">
         <f>'QTR P&amp;L'!AN9*'IS DRIVERS'!AO7</f>
-        <v>-229665.42303325931</v>
+        <v>-137402.52665887037</v>
       </c>
       <c r="AO10" s="11">
         <f>'QTR P&amp;L'!AO9*'IS DRIVERS'!AP7</f>
-        <v>-222919.10496448987</v>
+        <v>-138722.79043978371</v>
       </c>
       <c r="AP10" s="11">
         <f>'QTR P&amp;L'!AP9*'IS DRIVERS'!AQ7</f>
-        <v>-228023.4452510117</v>
+        <v>-140056.25685850615</v>
       </c>
       <c r="AQ10" s="11">
         <f>'QTR P&amp;L'!AQ9*'IS DRIVERS'!AR7</f>
-        <v>-258881.43149665094</v>
+        <v>-141403.05794141587</v>
       </c>
       <c r="AR10" s="11">
         <f>'QTR P&amp;L'!AR9*'IS DRIVERS'!AS7</f>
-        <v>-269151.81987850682</v>
+        <v>-142763.32703515468</v>
       </c>
       <c r="AS10" s="11">
         <f>'QTR P&amp;L'!AS9*'IS DRIVERS'!AT7</f>
-        <v>-261217.80439022297</v>
+        <v>-144137.19881983084</v>
       </c>
     </row>
     <row r="11" spans="1:45" x14ac:dyDescent="0.25">
@@ -33289,83 +33290,83 @@
       </c>
       <c r="Z11" s="7">
         <f t="shared" ref="Z11:AS11" si="3">Z9+Z10</f>
-        <v>459253.84532008163</v>
+        <v>453479.13148567535</v>
       </c>
       <c r="AA11" s="7">
         <f t="shared" si="3"/>
-        <v>520094.22488594597</v>
+        <v>457811.15428620751</v>
       </c>
       <c r="AB11" s="7">
         <f t="shared" si="3"/>
-        <v>540343.58018952655</v>
+        <v>462186.49731474504</v>
       </c>
       <c r="AC11" s="7">
         <f t="shared" si="3"/>
-        <v>524700.67627654527</v>
+        <v>466605.59377356787</v>
       </c>
       <c r="AD11" s="7">
         <f t="shared" si="3"/>
-        <v>536536.27368350013</v>
+        <v>471068.88119697862</v>
       </c>
       <c r="AE11" s="7">
         <f t="shared" si="3"/>
-        <v>608087.67533223424</v>
+        <v>475576.80149462388</v>
       </c>
       <c r="AF11" s="7">
         <f t="shared" si="3"/>
-        <v>631901.95402005711</v>
+        <v>480129.80099524569</v>
       </c>
       <c r="AG11" s="7">
         <f t="shared" si="3"/>
-        <v>613505.09803695814</v>
+        <v>484728.33049087337</v>
       </c>
       <c r="AH11" s="7">
         <f t="shared" si="3"/>
-        <v>627424.36661911674</v>
+        <v>489372.84528145753</v>
       </c>
       <c r="AI11" s="7">
         <f t="shared" si="3"/>
-        <v>711572.47868597391</v>
+        <v>494063.80521994748</v>
       </c>
       <c r="AJ11" s="7">
         <f t="shared" si="3"/>
-        <v>739579.28981249977</v>
+        <v>498801.67475782236</v>
       </c>
       <c r="AK11" s="7">
         <f t="shared" si="3"/>
-        <v>717943.64518119651</v>
+        <v>503586.92299107614</v>
       </c>
       <c r="AL11" s="7">
         <f t="shared" si="3"/>
-        <v>734313.41775798448</v>
+        <v>508420.02370666212</v>
       </c>
       <c r="AM11" s="7">
         <f t="shared" si="3"/>
-        <v>833275.90628027054</v>
+        <v>513301.45542940422</v>
       </c>
       <c r="AN11" s="7">
         <f t="shared" si="3"/>
-        <v>866213.35022972664</v>
+        <v>518231.70146937354</v>
       </c>
       <c r="AO11" s="7">
         <f t="shared" si="3"/>
-        <v>840768.72430875013</v>
+        <v>523211.24996974273</v>
       </c>
       <c r="AP11" s="7">
         <f t="shared" si="3"/>
-        <v>860020.41505916975</v>
+        <v>528240.59395511542</v>
       </c>
       <c r="AQ11" s="7">
         <f t="shared" si="3"/>
-        <v>976405.36885043816</v>
+        <v>533320.23138034204</v>
       </c>
       <c r="AR11" s="7">
         <f t="shared" si="3"/>
-        <v>1015141.4894684708</v>
+        <v>538450.66517982085</v>
       </c>
       <c r="AS11" s="7">
         <f t="shared" si="3"/>
-        <v>985217.30651522917</v>
+        <v>543632.40331729432</v>
       </c>
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.25">
@@ -33819,83 +33820,83 @@
       </c>
       <c r="W2" s="11">
         <f>'BS DRIVERS'!W2</f>
-        <v>2585143.4922486003</v>
+        <v>2599086.7414856758</v>
       </c>
       <c r="X2" s="11">
         <f>'BS DRIVERS'!X2</f>
-        <v>2970647.3051565615</v>
+        <v>3114674.7218718827</v>
       </c>
       <c r="Y2" s="11">
         <f>'BS DRIVERS'!Y2</f>
-        <v>3521137.2784580542</v>
+        <v>3634927.1235476276</v>
       </c>
       <c r="Z2" s="11">
         <f>'BS DRIVERS'!Z2</f>
-        <v>4180582.3986528106</v>
+        <v>4159890.5907258056</v>
       </c>
       <c r="AA2" s="11">
         <f>'BS DRIVERS'!AA2</f>
-        <v>4756458.8170278277</v>
+        <v>4689612.2340614405</v>
       </c>
       <c r="AB2" s="11">
         <f>'BS DRIVERS'!AB2</f>
-        <v>5201178.8540754309</v>
+        <v>5224139.6353161074</v>
       </c>
       <c r="AC2" s="11">
         <f>'BS DRIVERS'!AC2</f>
-        <v>5839931.0637201872</v>
+        <v>5763520.8520689961</v>
       </c>
       <c r="AD2" s="11">
         <f>'BS DRIVERS'!AD2</f>
-        <v>6606820.1050659539</v>
+        <v>6307804.4224750893</v>
       </c>
       <c r="AE2" s="11">
         <f>'BS DRIVERS'!AE2</f>
-        <v>7275428.074008246</v>
+        <v>6857039.3700709185</v>
       </c>
       <c r="AF2" s="11">
         <f>'BS DRIVERS'!AF2</f>
-        <v>7789789.4227598654</v>
+        <v>7411275.2086283816</v>
       </c>
       <c r="AG2" s="11">
         <f>'BS DRIVERS'!AG2</f>
-        <v>8532342.5417361539</v>
+        <v>7970561.9470570944</v>
       </c>
       <c r="AH2" s="11">
         <f>'BS DRIVERS'!AH2</f>
-        <v>9425591.1359290257</v>
+        <v>8534950.0943557695</v>
       </c>
       <c r="AI2" s="11">
         <f>'BS DRIVERS'!AI2</f>
-        <v>10203256.15657768</v>
+        <v>9104490.6646131072</v>
       </c>
       <c r="AJ2" s="11">
         <f>'BS DRIVERS'!AJ2</f>
-        <v>10799519.253816657</v>
+        <v>9679235.1820586938</v>
       </c>
       <c r="AK2" s="11">
         <f>'BS DRIVERS'!AK2</f>
-        <v>11664147.557203062</v>
+        <v>10259235.686164411</v>
       </c>
       <c r="AL2" s="11">
         <f>'BS DRIVERS'!AL2</f>
-        <v>12706001.455676291</v>
+        <v>10844544.736796862</v>
       </c>
       <c r="AM2" s="11">
         <f>'BS DRIVERS'!AM2</f>
-        <v>13611923.153304106</v>
+        <v>11435215.419421311</v>
       </c>
       <c r="AN2" s="11">
         <f>'BS DRIVERS'!AN2</f>
-        <v>14304506.900472762</v>
+        <v>12031301.350357682</v>
       </c>
       <c r="AO2" s="11">
         <f>'BS DRIVERS'!AO2</f>
-        <v>15312701.871480227</v>
+        <v>12632856.68208909</v>
       </c>
       <c r="AP2" s="11">
         <f>'BS DRIVERS'!AP2</f>
-        <v>16529323.216993876</v>
+        <v>13239936.108623488</v>
       </c>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.25">
@@ -34157,83 +34158,83 @@
       </c>
       <c r="W4" s="11">
         <f>'QTR P&amp;L'!Z2*'BS DRIVERS'!W4/ASSUMPTIONS!$B$2</f>
-        <v>1656037.7895290451</v>
+        <v>1634252.7199999997</v>
       </c>
       <c r="X4" s="11">
         <f>'QTR P&amp;L'!AA2*'BS DRIVERS'!X4/ASSUMPTIONS!$B$2</f>
-        <v>1885557.7167536498</v>
+        <v>1650595.2472000001</v>
       </c>
       <c r="Y4" s="11">
         <f>'QTR P&amp;L'!AB2*'BS DRIVERS'!Y4/ASSUMPTIONS!$B$2</f>
-        <v>1961948.2749452135</v>
+        <v>1667101.199672</v>
       </c>
       <c r="Z4" s="11">
         <f>'QTR P&amp;L'!AC2*'BS DRIVERS'!Z4/ASSUMPTIONS!$B$2</f>
-        <v>1902935.5239842809</v>
+        <v>1683772.21166872</v>
       </c>
       <c r="AA4" s="11">
         <f>'QTR P&amp;L'!AD2*'BS DRIVERS'!AA4/ASSUMPTIONS!$B$2</f>
-        <v>1947585.2364760181</v>
+        <v>1700609.9337854071</v>
       </c>
       <c r="AB4" s="11">
         <f>'QTR P&amp;L'!AE2*'BS DRIVERS'!AB4/ASSUMPTIONS!$B$2</f>
-        <v>2217512.4232625067</v>
+        <v>1717616.0331232613</v>
       </c>
       <c r="AC4" s="11">
         <f>'QTR P&amp;L'!AF2*'BS DRIVERS'!AC4/ASSUMPTIONS!$B$2</f>
-        <v>2307351.6312085777</v>
+        <v>1734792.1934544942</v>
       </c>
       <c r="AD4" s="11">
         <f>'QTR P&amp;L'!AG2*'BS DRIVERS'!AD4/ASSUMPTIONS!$B$2</f>
-        <v>2237949.6143813925</v>
+        <v>1752140.1153890388</v>
       </c>
       <c r="AE4" s="11">
         <f>'QTR P&amp;L'!AH2*'BS DRIVERS'!AE4/ASSUMPTIONS!$B$2</f>
-        <v>2290459.9625217794</v>
+        <v>1769661.5165429292</v>
       </c>
       <c r="AF4" s="11">
         <f>'QTR P&amp;L'!AI2*'BS DRIVERS'!AF4/ASSUMPTIONS!$B$2</f>
-        <v>2607908.1555719958</v>
+        <v>1787358.1317083586</v>
       </c>
       <c r="AG4" s="11">
         <f>'QTR P&amp;L'!AJ2*'BS DRIVERS'!AG4/ASSUMPTIONS!$B$2</f>
-        <v>2713563.6642559045</v>
+        <v>1805231.7130254426</v>
       </c>
       <c r="AH4" s="11">
         <f>'QTR P&amp;L'!AK2*'BS DRIVERS'!AH4/ASSUMPTIONS!$B$2</f>
-        <v>2631943.3387965891</v>
+        <v>1823284.0301556971</v>
       </c>
       <c r="AI4" s="11">
         <f>'QTR P&amp;L'!AL2*'BS DRIVERS'!AI4/ASSUMPTIONS!$B$2</f>
-        <v>2693698.1969568711</v>
+        <v>1841516.8704572539</v>
       </c>
       <c r="AJ4" s="11">
         <f>'QTR P&amp;L'!AM2*'BS DRIVERS'!AJ4/ASSUMPTIONS!$B$2</f>
-        <v>3067033.5266454611</v>
+        <v>1859932.0391618265</v>
       </c>
       <c r="AK4" s="11">
         <f>'QTR P&amp;L'!AN2*'BS DRIVERS'!AK4/ASSUMPTIONS!$B$2</f>
-        <v>3191289.8148571351</v>
+        <v>1878531.3595534449</v>
       </c>
       <c r="AL4" s="11">
         <f>'QTR P&amp;L'!AO2*'BS DRIVERS'!AL4/ASSUMPTIONS!$B$2</f>
-        <v>3095300.1328184558</v>
+        <v>1897316.6731489792</v>
       </c>
       <c r="AM4" s="11">
         <f>'QTR P&amp;L'!AP2*'BS DRIVERS'!AM4/ASSUMPTIONS!$B$2</f>
-        <v>3167927.0081193144</v>
+        <v>1916289.8398804688</v>
       </c>
       <c r="AN4" s="11">
         <f>'QTR P&amp;L'!AQ2*'BS DRIVERS'!AN4/ASSUMPTIONS!$B$2</f>
-        <v>3606988.4721473684</v>
+        <v>1935452.738279274</v>
       </c>
       <c r="AO4" s="11">
         <f>'QTR P&amp;L'!AR2*'BS DRIVERS'!AO4/ASSUMPTIONS!$B$2</f>
-        <v>3753120.2295206026</v>
+        <v>1954807.2656620666</v>
       </c>
       <c r="AP4" s="11">
         <f>'QTR P&amp;L'!AS2*'BS DRIVERS'!AP4/ASSUMPTIONS!$B$2</f>
-        <v>3640231.4483740539</v>
+        <v>1974355.3383186876</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.25">
@@ -34326,83 +34327,83 @@
       </c>
       <c r="W5" s="11">
         <f>'QTR P&amp;L'!Z3*'BS DRIVERS'!W5/ASSUMPTIONS!$B$2</f>
-        <v>818385.0319247744</v>
+        <v>807619.22999999986</v>
       </c>
       <c r="X5" s="11">
         <f>'QTR P&amp;L'!AA3*'BS DRIVERS'!X5/ASSUMPTIONS!$B$2</f>
-        <v>931809.78234819195</v>
+        <v>815695.42230000009</v>
       </c>
       <c r="Y5" s="11">
         <f>'QTR P&amp;L'!AB3*'BS DRIVERS'!Y5/ASSUMPTIONS!$B$2</f>
-        <v>969560.66569133918</v>
+        <v>823852.37652300007</v>
       </c>
       <c r="Z5" s="11">
         <f>'QTR P&amp;L'!AC3*'BS DRIVERS'!Z5/ASSUMPTIONS!$B$2</f>
-        <v>940397.59200757591</v>
+        <v>832090.90028822992</v>
       </c>
       <c r="AA5" s="11">
         <f>'QTR P&amp;L'!AD3*'BS DRIVERS'!AA5/ASSUMPTIONS!$B$2</f>
-        <v>962462.70224480925</v>
+        <v>840411.80929111224</v>
       </c>
       <c r="AB5" s="11">
         <f>'QTR P&amp;L'!AE3*'BS DRIVERS'!AB5/ASSUMPTIONS!$B$2</f>
-        <v>1095856.0165594828</v>
+        <v>848815.92738402344</v>
       </c>
       <c r="AC5" s="11">
         <f>'QTR P&amp;L'!AF3*'BS DRIVERS'!AC5/ASSUMPTIONS!$B$2</f>
-        <v>1140252.9883725177</v>
+        <v>857304.08665786369</v>
       </c>
       <c r="AD5" s="11">
         <f>'QTR P&amp;L'!AG3*'BS DRIVERS'!AD5/ASSUMPTIONS!$B$2</f>
-        <v>1105955.7204503212</v>
+        <v>865877.12752444239</v>
       </c>
       <c r="AE5" s="11">
         <f>'QTR P&amp;L'!AH3*'BS DRIVERS'!AE5/ASSUMPTIONS!$B$2</f>
-        <v>1131905.4199142887</v>
+        <v>874535.89879968669</v>
       </c>
       <c r="AF5" s="11">
         <f>'QTR P&amp;L'!AI3*'BS DRIVERS'!AF5/ASSUMPTIONS!$B$2</f>
-        <v>1288782.7878382087</v>
+        <v>883281.25778768363</v>
       </c>
       <c r="AG5" s="11">
         <f>'QTR P&amp;L'!AJ3*'BS DRIVERS'!AG5/ASSUMPTIONS!$B$2</f>
-        <v>1340995.8999990723</v>
+        <v>892114.07036556059</v>
       </c>
       <c r="AH5" s="11">
         <f>'QTR P&amp;L'!AK3*'BS DRIVERS'!AH5/ASSUMPTIONS!$B$2</f>
-        <v>1300660.5567604809</v>
+        <v>901035.21106921614</v>
       </c>
       <c r="AI5" s="11">
         <f>'QTR P&amp;L'!AL3*'BS DRIVERS'!AI5/ASSUMPTIONS!$B$2</f>
-        <v>1331178.7320621356</v>
+        <v>910045.56317990844</v>
       </c>
       <c r="AJ5" s="11">
         <f>'QTR P&amp;L'!AM3*'BS DRIVERS'!AJ5/ASSUMPTIONS!$B$2</f>
-        <v>1515674.5495112846</v>
+        <v>919146.0188117075</v>
       </c>
       <c r="AK5" s="11">
         <f>'QTR P&amp;L'!AN3*'BS DRIVERS'!AK5/ASSUMPTIONS!$B$2</f>
-        <v>1577079.8429399352</v>
+        <v>928337.4789998245</v>
       </c>
       <c r="AL5" s="11">
         <f>'QTR P&amp;L'!AO3*'BS DRIVERS'!AL5/ASSUMPTIONS!$B$2</f>
-        <v>1529643.4139548128</v>
+        <v>937620.85378982278</v>
       </c>
       <c r="AM5" s="11">
         <f>'QTR P&amp;L'!AP3*'BS DRIVERS'!AM5/ASSUMPTIONS!$B$2</f>
-        <v>1565534.350766462</v>
+        <v>946997.06232772092</v>
       </c>
       <c r="AN5" s="11">
         <f>'QTR P&amp;L'!AQ3*'BS DRIVERS'!AN5/ASSUMPTIONS!$B$2</f>
-        <v>1782510.8790362205</v>
+        <v>956467.03295099828</v>
       </c>
       <c r="AO5" s="11">
         <f>'QTR P&amp;L'!AR3*'BS DRIVERS'!AO5/ASSUMPTIONS!$B$2</f>
-        <v>1854726.6483135191</v>
+        <v>966031.7032805084</v>
       </c>
       <c r="AP5" s="11">
         <f>'QTR P&amp;L'!AS3*'BS DRIVERS'!AP5/ASSUMPTIONS!$B$2</f>
-        <v>1798938.9788854921</v>
+        <v>975692.02031331358</v>
       </c>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.25">
@@ -34495,83 +34496,83 @@
       </c>
       <c r="W6" s="11">
         <f>'QTR P&amp;L'!Z2*'BS DRIVERS'!W6</f>
-        <v>105980.6789460062</v>
+        <v>104586.51</v>
       </c>
       <c r="X6" s="11">
         <f>'QTR P&amp;L'!AA2*'BS DRIVERS'!X6</f>
-        <v>120669.15880600936</v>
+        <v>105632.3751</v>
       </c>
       <c r="Y6" s="11">
         <f>'QTR P&amp;L'!AB2*'BS DRIVERS'!Y6</f>
-        <v>125557.88977180979</v>
+        <v>106688.69885099999</v>
       </c>
       <c r="Z6" s="11">
         <f>'QTR P&amp;L'!AC2*'BS DRIVERS'!Z6</f>
-        <v>121781.27823984115</v>
+        <v>107755.58583950999</v>
       </c>
       <c r="AA6" s="11">
         <f>'QTR P&amp;L'!AD2*'BS DRIVERS'!AA6</f>
-        <v>124638.70508996394</v>
+        <v>108833.1416979051</v>
       </c>
       <c r="AB6" s="11">
         <f>'QTR P&amp;L'!AE2*'BS DRIVERS'!AB6</f>
-        <v>141913.10951629831</v>
+        <v>109921.47311488415</v>
       </c>
       <c r="AC6" s="11">
         <f>'QTR P&amp;L'!AF2*'BS DRIVERS'!AC6</f>
-        <v>147662.50745534155</v>
+        <v>111020.687846033</v>
       </c>
       <c r="AD6" s="11">
         <f>'QTR P&amp;L'!AG2*'BS DRIVERS'!AD6</f>
-        <v>143221.018915603</v>
+        <v>112130.89472449332</v>
       </c>
       <c r="AE6" s="11">
         <f>'QTR P&amp;L'!AH2*'BS DRIVERS'!AE6</f>
-        <v>146581.49920343023</v>
+        <v>113252.20367173826</v>
       </c>
       <c r="AF6" s="11">
         <f>'QTR P&amp;L'!AI2*'BS DRIVERS'!AF6</f>
-        <v>166897.0833298121</v>
+        <v>114384.72570845565</v>
       </c>
       <c r="AG6" s="11">
         <f>'QTR P&amp;L'!AJ2*'BS DRIVERS'!AG6</f>
-        <v>173658.6696991006</v>
+        <v>115528.57296554021</v>
       </c>
       <c r="AH6" s="11">
         <f>'QTR P&amp;L'!AK2*'BS DRIVERS'!AH6</f>
-        <v>168435.25175376967</v>
+        <v>116683.85869519562</v>
       </c>
       <c r="AI6" s="11">
         <f>'QTR P&amp;L'!AL2*'BS DRIVERS'!AI6</f>
-        <v>172387.34864275565</v>
+        <v>117850.69728214758</v>
       </c>
       <c r="AJ6" s="11">
         <f>'QTR P&amp;L'!AM2*'BS DRIVERS'!AJ6</f>
-        <v>196279.51581738275</v>
+        <v>119029.20425496907</v>
       </c>
       <c r="AK6" s="11">
         <f>'QTR P&amp;L'!AN2*'BS DRIVERS'!AK6</f>
-        <v>204231.48760887721</v>
+        <v>120219.49629751875</v>
       </c>
       <c r="AL6" s="11">
         <f>'QTR P&amp;L'!AO2*'BS DRIVERS'!AL6</f>
-        <v>198088.48064454726</v>
+        <v>121421.69126049394</v>
       </c>
       <c r="AM6" s="11">
         <f>'QTR P&amp;L'!AP2*'BS DRIVERS'!AM6</f>
-        <v>202736.34894971491</v>
+        <v>122635.90817309887</v>
       </c>
       <c r="AN6" s="11">
         <f>'QTR P&amp;L'!AQ2*'BS DRIVERS'!AN6</f>
-        <v>230834.76092493546</v>
+        <v>123862.26725482987</v>
       </c>
       <c r="AO6" s="11">
         <f>'QTR P&amp;L'!AR2*'BS DRIVERS'!AO6</f>
-        <v>240186.68692560523</v>
+        <v>125100.88992737817</v>
       </c>
       <c r="AP6" s="11">
         <f>'QTR P&amp;L'!AS2*'BS DRIVERS'!AP6</f>
-        <v>232962.19618816816</v>
+        <v>126351.89882665196</v>
       </c>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.25">
@@ -34664,83 +34665,83 @@
       </c>
       <c r="W7" s="11">
         <f>'QTR P&amp;L'!Z2*'BS DRIVERS'!W7</f>
-        <v>76388.252498701739</v>
+        <v>75383.37</v>
       </c>
       <c r="X7" s="11">
         <f>'QTR P&amp;L'!AA2*'BS DRIVERS'!X7</f>
-        <v>86975.345537987276</v>
+        <v>76137.203699999998</v>
       </c>
       <c r="Y7" s="11">
         <f>'QTR P&amp;L'!AB2*'BS DRIVERS'!Y7</f>
-        <v>90499.02192058567</v>
+        <v>76898.575736999992</v>
       </c>
       <c r="Z7" s="11">
         <f>'QTR P&amp;L'!AC2*'BS DRIVERS'!Z7</f>
-        <v>87776.933723353941</v>
+        <v>77667.561494369991</v>
       </c>
       <c r="AA7" s="11">
         <f>'QTR P&amp;L'!AD2*'BS DRIVERS'!AA7</f>
-        <v>89836.496333204297</v>
+        <v>78444.23710931369</v>
       </c>
       <c r="AB7" s="11">
         <f>'QTR P&amp;L'!AE2*'BS DRIVERS'!AB7</f>
-        <v>102287.45985039213</v>
+        <v>79228.679480406834</v>
       </c>
       <c r="AC7" s="11">
         <f>'QTR P&amp;L'!AF2*'BS DRIVERS'!AC7</f>
-        <v>106431.48370314459</v>
+        <v>80020.966275210914</v>
       </c>
       <c r="AD7" s="11">
         <f>'QTR P&amp;L'!AG2*'BS DRIVERS'!AD7</f>
-        <v>103230.16860101651</v>
+        <v>80821.175937963009</v>
       </c>
       <c r="AE7" s="11">
         <f>'QTR P&amp;L'!AH2*'BS DRIVERS'!AE7</f>
-        <v>105652.31968833155</v>
+        <v>81629.387697342638</v>
       </c>
       <c r="AF7" s="11">
         <f>'QTR P&amp;L'!AI2*'BS DRIVERS'!AF7</f>
-        <v>120295.29032541631</v>
+        <v>82445.68157431607</v>
       </c>
       <c r="AG7" s="11">
         <f>'QTR P&amp;L'!AJ2*'BS DRIVERS'!AG7</f>
-        <v>125168.87456742833</v>
+        <v>83270.138390059234</v>
       </c>
       <c r="AH7" s="11">
         <f>'QTR P&amp;L'!AK2*'BS DRIVERS'!AH7</f>
-        <v>121403.96408674089</v>
+        <v>84102.839773959829</v>
       </c>
       <c r="AI7" s="11">
         <f>'QTR P&amp;L'!AL2*'BS DRIVERS'!AI7</f>
-        <v>124252.53778958536</v>
+        <v>84943.868171699432</v>
       </c>
       <c r="AJ7" s="11">
         <f>'QTR P&amp;L'!AM2*'BS DRIVERS'!AJ7</f>
-        <v>141473.42103950705</v>
+        <v>85793.306853416434</v>
       </c>
       <c r="AK7" s="11">
         <f>'QTR P&amp;L'!AN2*'BS DRIVERS'!AK7</f>
-        <v>147205.00565580023</v>
+        <v>86651.23992195059</v>
       </c>
       <c r="AL7" s="11">
         <f>'QTR P&amp;L'!AO2*'BS DRIVERS'!AL7</f>
-        <v>142777.2781515106</v>
+        <v>87517.752321170105</v>
       </c>
       <c r="AM7" s="11">
         <f>'QTR P&amp;L'!AP2*'BS DRIVERS'!AM7</f>
-        <v>146127.34668482072</v>
+        <v>88392.929844381797</v>
       </c>
       <c r="AN7" s="11">
         <f>'QTR P&amp;L'!AQ2*'BS DRIVERS'!AN7</f>
-        <v>166379.98716723552</v>
+        <v>89276.859142825619</v>
       </c>
       <c r="AO7" s="11">
         <f>'QTR P&amp;L'!AR2*'BS DRIVERS'!AO7</f>
-        <v>173120.62415685409</v>
+        <v>90169.627734253881</v>
       </c>
       <c r="AP7" s="11">
         <f>'QTR P&amp;L'!AS2*'BS DRIVERS'!AP7</f>
-        <v>167913.38989383305</v>
+        <v>91071.324011596429</v>
       </c>
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.25">
@@ -34833,83 +34834,83 @@
       </c>
       <c r="W8" s="7">
         <f t="shared" ref="W8:AP8" si="0">SUM(W2:W7)</f>
-        <v>5919019.2451471277</v>
+        <v>5898012.5714856749</v>
       </c>
       <c r="X8" s="7">
         <f t="shared" si="0"/>
-        <v>6672743.3086024001</v>
+        <v>6439818.9701718828</v>
       </c>
       <c r="Y8" s="7">
         <f t="shared" si="0"/>
-        <v>7345787.1307870029</v>
+        <v>6986551.9743306274</v>
       </c>
       <c r="Z8" s="7">
         <f t="shared" si="0"/>
-        <v>7910557.7266078629</v>
+        <v>7538260.8500166358</v>
       </c>
       <c r="AA8" s="7">
         <f t="shared" si="0"/>
-        <v>8558065.957171822</v>
+        <v>8094995.3559451783</v>
       </c>
       <c r="AB8" s="7">
         <f t="shared" si="0"/>
-        <v>9435831.8632641099</v>
+        <v>8656805.7484186832</v>
       </c>
       <c r="AC8" s="7">
         <f t="shared" si="0"/>
-        <v>10218713.674459768</v>
+        <v>9223742.7863025982</v>
       </c>
       <c r="AD8" s="7">
         <f t="shared" si="0"/>
-        <v>10874260.627414286</v>
+        <v>9795857.7360510286</v>
       </c>
       <c r="AE8" s="7">
         <f t="shared" si="0"/>
-        <v>11627111.275336076</v>
+        <v>10373202.376782615</v>
       </c>
       <c r="AF8" s="7">
         <f t="shared" si="0"/>
-        <v>12650756.739825297</v>
+        <v>10955829.005407196</v>
       </c>
       <c r="AG8" s="7">
         <f t="shared" si="0"/>
-        <v>13562813.65025766</v>
+        <v>11543790.441803697</v>
       </c>
       <c r="AH8" s="7">
         <f t="shared" si="0"/>
-        <v>14325118.247326607</v>
+        <v>12137140.034049841</v>
       </c>
       <c r="AI8" s="7">
         <f t="shared" si="0"/>
-        <v>15201856.972029027</v>
+        <v>12735931.663704116</v>
       </c>
       <c r="AJ8" s="7">
         <f t="shared" si="0"/>
-        <v>16397064.266830293</v>
+        <v>13340219.751140615</v>
       </c>
       <c r="AK8" s="7">
         <f t="shared" si="0"/>
-        <v>17461037.708264805</v>
+        <v>13950059.260937151</v>
       </c>
       <c r="AL8" s="7">
         <f t="shared" si="0"/>
-        <v>18348894.76124562</v>
+        <v>14565505.707317328</v>
       </c>
       <c r="AM8" s="7">
         <f t="shared" si="0"/>
-        <v>19371332.207824416</v>
+        <v>15186615.15964698</v>
       </c>
       <c r="AN8" s="7">
         <f t="shared" si="0"/>
-        <v>20768304.999748524</v>
+        <v>15813444.247985609</v>
       </c>
       <c r="AO8" s="7">
         <f t="shared" si="0"/>
-        <v>22010940.060396809</v>
+        <v>16446050.168693297</v>
       </c>
       <c r="AP8" s="7">
         <f t="shared" si="0"/>
-        <v>23046453.230335422</v>
+        <v>17084490.690093737</v>
       </c>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.25">
@@ -35002,83 +35003,83 @@
       </c>
       <c r="W9" s="11">
         <f>'QTR P&amp;L'!Z2*'BS DRIVERS'!W8</f>
-        <v>498763.49132387183</v>
+        <v>492202.28999999992</v>
       </c>
       <c r="X9" s="11">
         <f>'QTR P&amp;L'!AA2*'BS DRIVERS'!X8</f>
-        <v>567890.02995406836</v>
+        <v>497124.31289999996</v>
       </c>
       <c r="Y9" s="11">
         <f>'QTR P&amp;L'!AB2*'BS DRIVERS'!Y8</f>
-        <v>590897.24739120132</v>
+        <v>502095.55602899997</v>
       </c>
       <c r="Z9" s="11">
         <f>'QTR P&amp;L'!AC2*'BS DRIVERS'!Z8</f>
-        <v>573123.8572620597</v>
+        <v>507116.51158928993</v>
       </c>
       <c r="AA9" s="11">
         <f>'QTR P&amp;L'!AD2*'BS DRIVERS'!AA8</f>
-        <v>586571.40455222095</v>
+        <v>512187.67670518282</v>
       </c>
       <c r="AB9" s="11">
         <f>'QTR P&amp;L'!AE2*'BS DRIVERS'!AB8</f>
-        <v>667867.75354625378</v>
+        <v>517309.55347223475</v>
       </c>
       <c r="AC9" s="11">
         <f>'QTR P&amp;L'!AF2*'BS DRIVERS'!AC8</f>
-        <v>694925.41931709147</v>
+        <v>522482.64900695713</v>
       </c>
       <c r="AD9" s="11">
         <f>'QTR P&amp;L'!AG2*'BS DRIVERS'!AD8</f>
-        <v>674023.00245407468</v>
+        <v>527707.47549702669</v>
       </c>
       <c r="AE9" s="11">
         <f>'QTR P&amp;L'!AH2*'BS DRIVERS'!AE8</f>
-        <v>689838.0066373907</v>
+        <v>532984.55025199684</v>
       </c>
       <c r="AF9" s="11">
         <f>'QTR P&amp;L'!AI2*'BS DRIVERS'!AF8</f>
-        <v>785446.67576396163</v>
+        <v>538314.39575451694</v>
       </c>
       <c r="AG9" s="11">
         <f>'QTR P&amp;L'!AJ2*'BS DRIVERS'!AG8</f>
-        <v>817267.87617495726</v>
+        <v>543697.53971206211</v>
       </c>
       <c r="AH9" s="11">
         <f>'QTR P&amp;L'!AK2*'BS DRIVERS'!AH8</f>
-        <v>792685.56365378236</v>
+        <v>549134.5151091828</v>
       </c>
       <c r="AI9" s="11">
         <f>'QTR P&amp;L'!AL2*'BS DRIVERS'!AI8</f>
-        <v>811284.81836704107</v>
+        <v>554625.86026027461</v>
       </c>
       <c r="AJ9" s="11">
         <f>'QTR P&amp;L'!AM2*'BS DRIVERS'!AJ8</f>
-        <v>923725.50881951221</v>
+        <v>560172.11886287737</v>
       </c>
       <c r="AK9" s="11">
         <f>'QTR P&amp;L'!AN2*'BS DRIVERS'!AK8</f>
-        <v>961148.86988002551</v>
+        <v>565773.84005150618</v>
       </c>
       <c r="AL9" s="11">
         <f>'QTR P&amp;L'!AO2*'BS DRIVERS'!AL8</f>
-        <v>932238.81163896609</v>
+        <v>571431.57845202123</v>
       </c>
       <c r="AM9" s="11">
         <f>'QTR P&amp;L'!AP2*'BS DRIVERS'!AM8</f>
-        <v>954112.48754058976</v>
+        <v>577145.89423654135</v>
       </c>
       <c r="AN9" s="11">
         <f>'QTR P&amp;L'!AQ2*'BS DRIVERS'!AN8</f>
-        <v>1086348.4969414864</v>
+        <v>582917.35317890684</v>
       </c>
       <c r="AO9" s="11">
         <f>'QTR P&amp;L'!AR2*'BS DRIVERS'!AO8</f>
-        <v>1130360.2857796473</v>
+        <v>588746.52671069594</v>
       </c>
       <c r="AP9" s="11">
         <f>'QTR P&amp;L'!AS2*'BS DRIVERS'!AP8</f>
-        <v>1096360.5769735088</v>
+        <v>594633.99197780294</v>
       </c>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.25">
@@ -35171,83 +35172,83 @@
       </c>
       <c r="W10" s="11">
         <f>'BS DRIVERS'!W9</f>
-        <v>1077200.4204937969</v>
+        <v>1077257.56</v>
       </c>
       <c r="X10" s="11">
         <f>'BS DRIVERS'!X9</f>
-        <v>1072254.8389931577</v>
+        <v>1072928.2556</v>
       </c>
       <c r="Y10" s="11">
         <f>'BS DRIVERS'!Y9</f>
-        <v>1067108.8946353865</v>
+        <v>1068555.6581560001</v>
       </c>
       <c r="Z10" s="11">
         <f>'BS DRIVERS'!Z9</f>
-        <v>1062117.7333250188</v>
+        <v>1064139.33473756</v>
       </c>
       <c r="AA10" s="11">
         <f>'BS DRIVERS'!AA9</f>
-        <v>1057009.4614164731</v>
+        <v>1059678.8480849357</v>
       </c>
       <c r="AB10" s="11">
         <f>'BS DRIVERS'!AB9</f>
-        <v>1051193.2043374765</v>
+        <v>1055173.756565785</v>
       </c>
       <c r="AC10" s="11">
         <f>'BS DRIVERS'!AC9</f>
-        <v>1045141.3102790853</v>
+        <v>1050623.614131443</v>
       </c>
       <c r="AD10" s="11">
         <f>'BS DRIVERS'!AD9</f>
-        <v>1039271.4490099732</v>
+        <v>1046027.9702727575</v>
       </c>
       <c r="AE10" s="11">
         <f>'BS DRIVERS'!AE9</f>
-        <v>1033263.8596808566</v>
+        <v>1041386.369975485</v>
       </c>
       <c r="AF10" s="11">
         <f>'BS DRIVERS'!AF9</f>
-        <v>1026423.6435395184</v>
+        <v>1036698.3536752398</v>
       </c>
       <c r="AG10" s="11">
         <f>'BS DRIVERS'!AG9</f>
-        <v>1019306.3062448232</v>
+        <v>1031963.4572119924</v>
       </c>
       <c r="AH10" s="11">
         <f>'BS DRIVERS'!AH9</f>
-        <v>1012403.0488311527</v>
+        <v>1027181.2117841122</v>
       </c>
       <c r="AI10" s="11">
         <f>'BS DRIVERS'!AI9</f>
-        <v>1005337.8161666699</v>
+        <v>1022351.1439019534</v>
       </c>
       <c r="AJ10" s="11">
         <f>'BS DRIVERS'!AJ9</f>
-        <v>997293.37173707515</v>
+        <v>1017472.7753409729</v>
       </c>
       <c r="AK10" s="11">
         <f>'BS DRIVERS'!AK9</f>
-        <v>988923.01864138246</v>
+        <v>1012545.6230943826</v>
       </c>
       <c r="AL10" s="11">
         <f>'BS DRIVERS'!AL9</f>
-        <v>980804.43444755091</v>
+        <v>1007569.1993253264</v>
       </c>
       <c r="AM10" s="11">
         <f>'BS DRIVERS'!AM9</f>
-        <v>972495.35906496074</v>
+        <v>1002543.0113185795</v>
       </c>
       <c r="AN10" s="11">
         <f>'BS DRIVERS'!AN9</f>
-        <v>963034.68050690321</v>
+        <v>997466.56143176532</v>
       </c>
       <c r="AO10" s="11">
         <f>'BS DRIVERS'!AO9</f>
-        <v>953190.71666964167</v>
+        <v>992339.34704608307</v>
       </c>
       <c r="AP10" s="11">
         <f>'BS DRIVERS'!AP9</f>
-        <v>943642.84595257882</v>
+        <v>987160.86051654397</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.25">
@@ -35847,83 +35848,83 @@
       </c>
       <c r="W14" s="11">
         <f>'QTR P&amp;L'!Z2*'BS DRIVERS'!W13</f>
-        <v>163171.82475341341</v>
+        <v>161025.30999999997</v>
       </c>
       <c r="X14" s="11">
         <f>'QTR P&amp;L'!AA2*'BS DRIVERS'!X13</f>
-        <v>185786.75877201452</v>
+        <v>162635.5631</v>
       </c>
       <c r="Y14" s="11">
         <f>'QTR P&amp;L'!AB2*'BS DRIVERS'!Y13</f>
-        <v>193313.6321639521</v>
+        <v>164261.91873099998</v>
       </c>
       <c r="Z14" s="11">
         <f>'QTR P&amp;L'!AC2*'BS DRIVERS'!Z13</f>
-        <v>187499.01952715195</v>
+        <v>165904.53791830997</v>
       </c>
       <c r="AA14" s="11">
         <f>'QTR P&amp;L'!AD2*'BS DRIVERS'!AA13</f>
-        <v>191898.42098287839</v>
+        <v>167563.58329749308</v>
       </c>
       <c r="AB14" s="11">
         <f>'QTR P&amp;L'!AE2*'BS DRIVERS'!AB13</f>
-        <v>218494.74136698779</v>
+        <v>169239.21913046803</v>
       </c>
       <c r="AC14" s="11">
         <f>'QTR P&amp;L'!AF2*'BS DRIVERS'!AC13</f>
-        <v>227346.7298829809</v>
+        <v>170931.61132177271</v>
       </c>
       <c r="AD14" s="11">
         <f>'QTR P&amp;L'!AG2*'BS DRIVERS'!AD13</f>
-        <v>220508.44768986781</v>
+        <v>172640.92743499044</v>
       </c>
       <c r="AE14" s="11">
         <f>'QTR P&amp;L'!AH2*'BS DRIVERS'!AE13</f>
-        <v>225682.36906936759</v>
+        <v>174367.33670934031</v>
       </c>
       <c r="AF14" s="11">
         <f>'QTR P&amp;L'!AI2*'BS DRIVERS'!AF13</f>
-        <v>256961.00368277729</v>
+        <v>176111.01007643374</v>
       </c>
       <c r="AG14" s="11">
         <f>'QTR P&amp;L'!AJ2*'BS DRIVERS'!AG13</f>
-        <v>267371.39543603931</v>
+        <v>177872.12017719809</v>
       </c>
       <c r="AH14" s="11">
         <f>'QTR P&amp;L'!AK2*'BS DRIVERS'!AH13</f>
-        <v>259329.22542858348</v>
+        <v>179650.8413789701</v>
       </c>
       <c r="AI14" s="11">
         <f>'QTR P&amp;L'!AL2*'BS DRIVERS'!AI13</f>
-        <v>265414.02189706691</v>
+        <v>181447.34979275978</v>
       </c>
       <c r="AJ14" s="11">
         <f>'QTR P&amp;L'!AM2*'BS DRIVERS'!AJ13</f>
-        <v>302199.29779800429</v>
+        <v>183261.8232906874</v>
       </c>
       <c r="AK14" s="11">
         <f>'QTR P&amp;L'!AN2*'BS DRIVERS'!AK13</f>
-        <v>314442.45155499125</v>
+        <v>185094.44152359426</v>
       </c>
       <c r="AL14" s="11">
         <f>'QTR P&amp;L'!AO2*'BS DRIVERS'!AL13</f>
-        <v>304984.44783382886</v>
+        <v>186945.38593883021</v>
       </c>
       <c r="AM14" s="11">
         <f>'QTR P&amp;L'!AP2*'BS DRIVERS'!AM13</f>
-        <v>312140.48004753207</v>
+        <v>188814.83979821848</v>
       </c>
       <c r="AN14" s="11">
         <f>'QTR P&amp;L'!AQ2*'BS DRIVERS'!AN13</f>
-        <v>355401.84806543036</v>
+        <v>190702.98819620069</v>
       </c>
       <c r="AO14" s="11">
         <f>'QTR P&amp;L'!AR2*'BS DRIVERS'!AO13</f>
-        <v>369800.42378379893</v>
+        <v>192610.01807816271</v>
       </c>
       <c r="AP14" s="11">
         <f>'QTR P&amp;L'!AS2*'BS DRIVERS'!AP13</f>
-        <v>358677.3271187708</v>
+        <v>194536.11825894436</v>
       </c>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.25">
@@ -36016,83 +36017,83 @@
       </c>
       <c r="W15" s="7">
         <f t="shared" ref="W15:AP15" si="1">W8+SUM(W9:W14)</f>
-        <v>10553956.981718209</v>
+        <v>10524299.731485674</v>
       </c>
       <c r="X15" s="7">
         <f t="shared" si="1"/>
-        <v>11390721.936321642</v>
+        <v>11064554.101771884</v>
       </c>
       <c r="Y15" s="7">
         <f t="shared" si="1"/>
-        <v>12085398.904977543</v>
+        <v>11609757.107246626</v>
       </c>
       <c r="Z15" s="7">
         <f t="shared" si="1"/>
-        <v>12617835.336722095</v>
+        <v>12159958.234261796</v>
       </c>
       <c r="AA15" s="7">
         <f t="shared" si="1"/>
-        <v>13274327.244123396</v>
+        <v>12715207.46403279</v>
       </c>
       <c r="AB15" s="7">
         <f t="shared" si="1"/>
-        <v>14250414.562514829</v>
+        <v>13275555.277587172</v>
       </c>
       <c r="AC15" s="7">
         <f t="shared" si="1"/>
-        <v>15059399.133938927</v>
+        <v>13841052.660762772</v>
       </c>
       <c r="AD15" s="7">
         <f t="shared" si="1"/>
-        <v>15677580.5265682</v>
+        <v>14411751.109255802</v>
       </c>
       <c r="AE15" s="7">
         <f t="shared" si="1"/>
-        <v>16441657.510723691</v>
+        <v>14987702.633719437</v>
       </c>
       <c r="AF15" s="7">
         <f t="shared" si="1"/>
-        <v>17581595.062811553</v>
+        <v>15568959.764913386</v>
       </c>
       <c r="AG15" s="7">
         <f t="shared" si="1"/>
-        <v>18525011.22811348</v>
+        <v>16155575.55890495</v>
       </c>
       <c r="AH15" s="7">
         <f t="shared" si="1"/>
-        <v>19244033.085240126</v>
+        <v>16747603.602322105</v>
       </c>
       <c r="AI15" s="7">
         <f t="shared" si="1"/>
-        <v>20134635.628459804</v>
+        <v>17345098.017659105</v>
       </c>
       <c r="AJ15" s="7">
         <f t="shared" si="1"/>
-        <v>21467269.445184886</v>
+        <v>17948113.468635153</v>
       </c>
       <c r="AK15" s="7">
         <f t="shared" si="1"/>
-        <v>22568784.048341203</v>
+        <v>18556705.165606633</v>
       </c>
       <c r="AL15" s="7">
         <f t="shared" si="1"/>
-        <v>23406399.455165967</v>
+        <v>19170928.871033505</v>
       </c>
       <c r="AM15" s="7">
         <f t="shared" si="1"/>
-        <v>24445802.534477498</v>
+        <v>19790840.905000322</v>
       </c>
       <c r="AN15" s="7">
         <f t="shared" si="1"/>
-        <v>26005057.025262345</v>
+        <v>20416498.150792483</v>
       </c>
       <c r="AO15" s="7">
         <f t="shared" si="1"/>
-        <v>27292503.486629896</v>
+        <v>21047958.060528237</v>
       </c>
       <c r="AP15" s="7">
         <f t="shared" si="1"/>
-        <v>28269590.980380282</v>
+        <v>21685278.660847031</v>
       </c>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
@@ -36185,83 +36186,83 @@
       </c>
       <c r="W16" s="11">
         <f>'QTR P&amp;L'!Z3*'BS DRIVERS'!W14/ASSUMPTIONS!$B$2</f>
-        <v>579253.78591985512</v>
+        <v>571633.74</v>
       </c>
       <c r="X16" s="11">
         <f>'QTR P&amp;L'!AA3*'BS DRIVERS'!X14/ASSUMPTIONS!$B$2</f>
-        <v>659535.94350679708</v>
+        <v>577350.07740000007</v>
       </c>
       <c r="Y16" s="11">
         <f>'QTR P&amp;L'!AB3*'BS DRIVERS'!Y14/ASSUMPTIONS!$B$2</f>
-        <v>686256.05842251913</v>
+        <v>583123.57817400002</v>
       </c>
       <c r="Z16" s="11">
         <f>'QTR P&amp;L'!AC3*'BS DRIVERS'!Z14/ASSUMPTIONS!$B$2</f>
-        <v>665614.40421160439</v>
+        <v>588954.81395573996</v>
       </c>
       <c r="AA16" s="11">
         <f>'QTR P&amp;L'!AD3*'BS DRIVERS'!AA14/ASSUMPTIONS!$B$2</f>
-        <v>681232.1124333638</v>
+        <v>594844.36209529731</v>
       </c>
       <c r="AB16" s="11">
         <f>'QTR P&amp;L'!AE3*'BS DRIVERS'!AB14/ASSUMPTIONS!$B$2</f>
-        <v>775648.0405343977</v>
+        <v>600792.80571625044</v>
       </c>
       <c r="AC16" s="11">
         <f>'QTR P&amp;L'!AF3*'BS DRIVERS'!AC14/ASSUMPTIONS!$B$2</f>
-        <v>807072.26385577628</v>
+        <v>606800.733773413</v>
       </c>
       <c r="AD16" s="11">
         <f>'QTR P&amp;L'!AG3*'BS DRIVERS'!AD14/ASSUMPTIONS!$B$2</f>
-        <v>782796.62156560051</v>
+        <v>612868.7411111471</v>
       </c>
       <c r="AE16" s="11">
         <f>'QTR P&amp;L'!AH3*'BS DRIVERS'!AE14/ASSUMPTIONS!$B$2</f>
-        <v>801163.84612569865</v>
+        <v>618997.42852225841</v>
       </c>
       <c r="AF16" s="11">
         <f>'QTR P&amp;L'!AI3*'BS DRIVERS'!AF14/ASSUMPTIONS!$B$2</f>
-        <v>912201.81205886067</v>
+        <v>625187.40280748112</v>
       </c>
       <c r="AG16" s="11">
         <f>'QTR P&amp;L'!AJ3*'BS DRIVERS'!AG14/ASSUMPTIONS!$B$2</f>
-        <v>949158.30773511378</v>
+        <v>631439.27683555603</v>
       </c>
       <c r="AH16" s="11">
         <f>'QTR P&amp;L'!AK3*'BS DRIVERS'!AH14/ASSUMPTIONS!$B$2</f>
-        <v>920608.90938849479</v>
+        <v>637753.66960391146</v>
       </c>
       <c r="AI16" s="11">
         <f>'QTR P&amp;L'!AL3*'BS DRIVERS'!AI14/ASSUMPTIONS!$B$2</f>
-        <v>942209.70594909741</v>
+        <v>644131.20629995072</v>
       </c>
       <c r="AJ16" s="11">
         <f>'QTR P&amp;L'!AM3*'BS DRIVERS'!AJ14/ASSUMPTIONS!$B$2</f>
-        <v>1072796.0394899845</v>
+        <v>650572.5183629503</v>
       </c>
       <c r="AK16" s="11">
         <f>'QTR P&amp;L'!AN3*'BS DRIVERS'!AK14/ASSUMPTIONS!$B$2</f>
-        <v>1116258.7707308156</v>
+        <v>657078.24354657973</v>
       </c>
       <c r="AL16" s="11">
         <f>'QTR P&amp;L'!AO3*'BS DRIVERS'!AL14/ASSUMPTIONS!$B$2</f>
-        <v>1082683.2164278182</v>
+        <v>663649.02598204557</v>
       </c>
       <c r="AM16" s="11">
         <f>'QTR P&amp;L'!AP3*'BS DRIVERS'!AM14/ASSUMPTIONS!$B$2</f>
-        <v>1108086.8592332855</v>
+        <v>670285.51624186605</v>
       </c>
       <c r="AN16" s="11">
         <f>'QTR P&amp;L'!AQ3*'BS DRIVERS'!AN14/ASSUMPTIONS!$B$2</f>
-        <v>1261663.0740381978</v>
+        <v>676988.37140428473</v>
       </c>
       <c r="AO16" s="11">
         <f>'QTR P&amp;L'!AR3*'BS DRIVERS'!AO14/ASSUMPTIONS!$B$2</f>
-        <v>1312777.4714491651</v>
+        <v>683758.25511832756</v>
       </c>
       <c r="AP16" s="11">
         <f>'QTR P&amp;L'!AS3*'BS DRIVERS'!AP14/ASSUMPTIONS!$B$2</f>
-        <v>1273290.9003814766</v>
+        <v>690595.83766951098</v>
       </c>
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.25">
@@ -36354,83 +36355,83 @@
       </c>
       <c r="W17" s="11">
         <f>'QTR P&amp;L'!Z2*'BS DRIVERS'!W15</f>
-        <v>313266.85512634652</v>
+        <v>309145.84999999998</v>
       </c>
       <c r="X17" s="11">
         <f>'QTR P&amp;L'!AA2*'BS DRIVERS'!X15</f>
-        <v>356684.33402996958</v>
+        <v>312237.30850000004</v>
       </c>
       <c r="Y17" s="11">
         <f>'QTR P&amp;L'!AB2*'BS DRIVERS'!Y15</f>
-        <v>371134.86775409605</v>
+        <v>315359.68158500001</v>
       </c>
       <c r="Z17" s="11">
         <f>'QTR P&amp;L'!AC2*'BS DRIVERS'!Z15</f>
-        <v>359971.6328190146</v>
+        <v>318513.27840085002</v>
       </c>
       <c r="AA17" s="11">
         <f>'QTR P&amp;L'!AD2*'BS DRIVERS'!AA15</f>
-        <v>368417.86218830931</v>
+        <v>321698.41118485847</v>
       </c>
       <c r="AB17" s="11">
         <f>'QTR P&amp;L'!AE2*'BS DRIVERS'!AB15</f>
-        <v>419479.04053361306</v>
+        <v>324915.39529670711</v>
       </c>
       <c r="AC17" s="11">
         <f>'QTR P&amp;L'!AF2*'BS DRIVERS'!AC15</f>
-        <v>436473.60812032933</v>
+        <v>328164.54924967419</v>
       </c>
       <c r="AD17" s="11">
         <f>'QTR P&amp;L'!AG2*'BS DRIVERS'!AD15</f>
-        <v>423345.07223283552</v>
+        <v>331446.19474217092</v>
       </c>
       <c r="AE17" s="11">
         <f>'QTR P&amp;L'!AH2*'BS DRIVERS'!AE15</f>
-        <v>433278.27045303228</v>
+        <v>334760.65668959264</v>
       </c>
       <c r="AF17" s="11">
         <f>'QTR P&amp;L'!AI2*'BS DRIVERS'!AF15</f>
-        <v>493328.83073080453</v>
+        <v>338108.2632564886</v>
       </c>
       <c r="AG17" s="11">
         <f>'QTR P&amp;L'!AJ2*'BS DRIVERS'!AG15</f>
-        <v>513315.31240499089</v>
+        <v>341489.34588905348</v>
       </c>
       <c r="AH17" s="11">
         <f>'QTR P&amp;L'!AK2*'BS DRIVERS'!AH15</f>
-        <v>497875.48196591623</v>
+        <v>344904.23934794404</v>
       </c>
       <c r="AI17" s="11">
         <f>'QTR P&amp;L'!AL2*'BS DRIVERS'!AI15</f>
-        <v>509557.43169373419</v>
+        <v>348353.28174142347</v>
       </c>
       <c r="AJ17" s="11">
         <f>'QTR P&amp;L'!AM2*'BS DRIVERS'!AJ15</f>
-        <v>580179.96541765507</v>
+        <v>351836.81455883774</v>
       </c>
       <c r="AK17" s="11">
         <f>'QTR P&amp;L'!AN2*'BS DRIVERS'!AK15</f>
-        <v>603685.09125709254</v>
+        <v>355355.18270442612</v>
       </c>
       <c r="AL17" s="11">
         <f>'QTR P&amp;L'!AO2*'BS DRIVERS'!AL15</f>
-        <v>585527.06007751019</v>
+        <v>358908.7345314704</v>
       </c>
       <c r="AM17" s="11">
         <f>'QTR P&amp;L'!AP2*'BS DRIVERS'!AM15</f>
-        <v>599265.63112160668</v>
+        <v>362497.82187678502</v>
       </c>
       <c r="AN17" s="11">
         <f>'QTR P&amp;L'!AQ2*'BS DRIVERS'!AN15</f>
-        <v>682321.34694700071</v>
+        <v>366122.80009555293</v>
       </c>
       <c r="AO17" s="11">
         <f>'QTR P&amp;L'!AR2*'BS DRIVERS'!AO15</f>
-        <v>709964.57849391969</v>
+        <v>369784.02809650853</v>
       </c>
       <c r="AP17" s="11">
         <f>'QTR P&amp;L'!AS2*'BS DRIVERS'!AP15</f>
-        <v>688609.80406037078</v>
+        <v>373481.86837747361</v>
       </c>
     </row>
     <row r="18" spans="1:42" x14ac:dyDescent="0.25">
@@ -36523,83 +36524,83 @@
       </c>
       <c r="W18" s="11">
         <f>'QTR P&amp;L'!Z2*'BS DRIVERS'!W16</f>
-        <v>393081.66374822648</v>
+        <v>387910.69999999995</v>
       </c>
       <c r="X18" s="11">
         <f>'QTR P&amp;L'!AA2*'BS DRIVERS'!X16</f>
-        <v>447561.14207128866</v>
+        <v>391789.80699999997</v>
       </c>
       <c r="Y18" s="11">
         <f>'QTR P&amp;L'!AB2*'BS DRIVERS'!Y16</f>
-        <v>465693.41411149077</v>
+        <v>395707.70506999997</v>
       </c>
       <c r="Z18" s="11">
         <f>'QTR P&amp;L'!AC2*'BS DRIVERS'!Z16</f>
-        <v>451685.98597382725</v>
+        <v>399664.78212069994</v>
       </c>
       <c r="AA18" s="11">
         <f>'QTR P&amp;L'!AD2*'BS DRIVERS'!AA16</f>
-        <v>462284.16397622862</v>
+        <v>403661.42994190694</v>
       </c>
       <c r="AB18" s="11">
         <f>'QTR P&amp;L'!AE2*'BS DRIVERS'!AB16</f>
-        <v>526354.82005895337</v>
+        <v>407698.04424132605</v>
       </c>
       <c r="AC18" s="11">
         <f>'QTR P&amp;L'!AF2*'BS DRIVERS'!AC16</f>
-        <v>547679.30042561656</v>
+        <v>411775.02468373935</v>
       </c>
       <c r="AD18" s="11">
         <f>'QTR P&amp;L'!AG2*'BS DRIVERS'!AD16</f>
-        <v>531205.84769742098</v>
+        <v>415892.77493057674</v>
       </c>
       <c r="AE18" s="11">
         <f>'QTR P&amp;L'!AH2*'BS DRIVERS'!AE16</f>
-        <v>543669.84769882902</v>
+        <v>420051.70267988247</v>
       </c>
       <c r="AF18" s="11">
         <f>'QTR P&amp;L'!AI2*'BS DRIVERS'!AF16</f>
-        <v>619020.21993492031</v>
+        <v>424252.21970668132</v>
       </c>
       <c r="AG18" s="11">
         <f>'QTR P&amp;L'!AJ2*'BS DRIVERS'!AG16</f>
-        <v>644098.90074778197</v>
+        <v>428494.74190374819</v>
       </c>
       <c r="AH18" s="11">
         <f>'QTR P&amp;L'!AK2*'BS DRIVERS'!AH16</f>
-        <v>624725.27683045366</v>
+        <v>432779.68932278571</v>
       </c>
       <c r="AI18" s="11">
         <f>'QTR P&amp;L'!AL2*'BS DRIVERS'!AI16</f>
-        <v>639383.57904050336</v>
+        <v>437107.48621601355</v>
       </c>
       <c r="AJ18" s="11">
         <f>'QTR P&amp;L'!AM2*'BS DRIVERS'!AJ16</f>
-        <v>727999.47504111193</v>
+        <v>441478.56107817369</v>
       </c>
       <c r="AK18" s="11">
         <f>'QTR P&amp;L'!AN2*'BS DRIVERS'!AK16</f>
-        <v>757493.28780930617</v>
+        <v>445893.34668895544</v>
       </c>
       <c r="AL18" s="11">
         <f>'QTR P&amp;L'!AO2*'BS DRIVERS'!AL16</f>
-        <v>734708.91407278797</v>
+        <v>450352.28015584499</v>
       </c>
       <c r="AM18" s="11">
         <f>'QTR P&amp;L'!AP2*'BS DRIVERS'!AM16</f>
-        <v>751947.82803755638</v>
+        <v>454855.80295740342</v>
       </c>
       <c r="AN18" s="11">
         <f>'QTR P&amp;L'!AQ2*'BS DRIVERS'!AN16</f>
-        <v>856164.65923496592</v>
+        <v>459404.36098697747</v>
       </c>
       <c r="AO18" s="11">
         <f>'QTR P&amp;L'!AR2*'BS DRIVERS'!AO16</f>
-        <v>890850.89325566334</v>
+        <v>463998.40459684731</v>
       </c>
       <c r="AP18" s="11">
         <f>'QTR P&amp;L'!AS2*'BS DRIVERS'!AP16</f>
-        <v>864055.30308726849</v>
+        <v>468638.38864281576</v>
       </c>
     </row>
     <row r="19" spans="1:42" x14ac:dyDescent="0.25">
@@ -36692,83 +36693,83 @@
       </c>
       <c r="W19" s="11">
         <f>'QTR P&amp;L'!Z2*'BS DRIVERS'!W17</f>
-        <v>46386.440612546852</v>
+        <v>45776.229999999996</v>
       </c>
       <c r="X19" s="11">
         <f>'QTR P&amp;L'!AA2*'BS DRIVERS'!X17</f>
-        <v>52815.407717595801</v>
+        <v>46233.992300000005</v>
       </c>
       <c r="Y19" s="11">
         <f>'QTR P&amp;L'!AB2*'BS DRIVERS'!Y17</f>
-        <v>54955.145176074933</v>
+        <v>46696.332222999998</v>
       </c>
       <c r="Z19" s="11">
         <f>'QTR P&amp;L'!AC2*'BS DRIVERS'!Z17</f>
-        <v>53302.168725210962</v>
+        <v>47163.295545230001</v>
       </c>
       <c r="AA19" s="11">
         <f>'QTR P&amp;L'!AD2*'BS DRIVERS'!AA17</f>
-        <v>54552.829338127456</v>
+        <v>47634.928500682297</v>
       </c>
       <c r="AB19" s="11">
         <f>'QTR P&amp;L'!AE2*'BS DRIVERS'!AB17</f>
-        <v>62113.623843392998</v>
+        <v>48111.277785689126</v>
       </c>
       <c r="AC19" s="11">
         <f>'QTR P&amp;L'!AF2*'BS DRIVERS'!AC17</f>
-        <v>64630.064657979594</v>
+        <v>48592.390563546025</v>
       </c>
       <c r="AD19" s="11">
         <f>'QTR P&amp;L'!AG2*'BS DRIVERS'!AD17</f>
-        <v>62686.079712526924</v>
+        <v>49078.314469181481</v>
       </c>
       <c r="AE19" s="11">
         <f>'QTR P&amp;L'!AH2*'BS DRIVERS'!AE17</f>
-        <v>64156.920632317109</v>
+        <v>49569.097613873288</v>
       </c>
       <c r="AF19" s="11">
         <f>'QTR P&amp;L'!AI2*'BS DRIVERS'!AF17</f>
-        <v>73048.80211448537</v>
+        <v>50064.788590012031</v>
       </c>
       <c r="AG19" s="11">
         <f>'QTR P&amp;L'!AJ2*'BS DRIVERS'!AG17</f>
-        <v>76008.26536462552</v>
+        <v>50565.436475912153</v>
       </c>
       <c r="AH19" s="11">
         <f>'QTR P&amp;L'!AK2*'BS DRIVERS'!AH17</f>
-        <v>73722.039528697002</v>
+        <v>51071.090840671277</v>
       </c>
       <c r="AI19" s="11">
         <f>'QTR P&amp;L'!AL2*'BS DRIVERS'!AI17</f>
-        <v>75451.823763513778</v>
+        <v>51581.801749077989</v>
       </c>
       <c r="AJ19" s="11">
         <f>'QTR P&amp;L'!AM2*'BS DRIVERS'!AJ17</f>
-        <v>85909.131687682777</v>
+        <v>52097.619766568772</v>
       </c>
       <c r="AK19" s="11">
         <f>'QTR P&amp;L'!AN2*'BS DRIVERS'!AK17</f>
-        <v>89389.612006616473</v>
+        <v>52618.595964234461</v>
       </c>
       <c r="AL19" s="11">
         <f>'QTR P&amp;L'!AO2*'BS DRIVERS'!AL17</f>
-        <v>86700.893359338064</v>
+        <v>53144.781923876806</v>
       </c>
       <c r="AM19" s="11">
         <f>'QTR P&amp;L'!AP2*'BS DRIVERS'!AM17</f>
-        <v>88735.208191595724</v>
+        <v>53676.229743115568</v>
       </c>
       <c r="AN19" s="11">
         <f>'QTR P&amp;L'!AQ2*'BS DRIVERS'!AN17</f>
-        <v>101033.53776787138</v>
+        <v>54212.992040546727</v>
       </c>
       <c r="AO19" s="11">
         <f>'QTR P&amp;L'!AR2*'BS DRIVERS'!AO17</f>
-        <v>105126.76083793692</v>
+        <v>54755.121960952201</v>
       </c>
       <c r="AP19" s="11">
         <f>'QTR P&amp;L'!AS2*'BS DRIVERS'!AP17</f>
-        <v>101964.69003521305</v>
+        <v>55302.673180561724</v>
       </c>
     </row>
     <row r="20" spans="1:42" x14ac:dyDescent="0.25">
@@ -36861,83 +36862,83 @@
       </c>
       <c r="W20" s="11">
         <f>'QTR P&amp;L'!Z2*'BS DRIVERS'!W18</f>
-        <v>116698.38973511086</v>
+        <v>115163.23</v>
       </c>
       <c r="X20" s="11">
         <f>'QTR P&amp;L'!AA2*'BS DRIVERS'!X18</f>
-        <v>132872.29958704027</v>
+        <v>116314.86229999999</v>
       </c>
       <c r="Y20" s="11">
         <f>'QTR P&amp;L'!AB2*'BS DRIVERS'!Y18</f>
-        <v>138255.42259805379</v>
+        <v>117478.01092299999</v>
       </c>
       <c r="Z20" s="11">
         <f>'QTR P&amp;L'!AC2*'BS DRIVERS'!Z18</f>
-        <v>134096.88644958916</v>
+        <v>118652.79103222999</v>
       </c>
       <c r="AA20" s="11">
         <f>'QTR P&amp;L'!AD2*'BS DRIVERS'!AA18</f>
-        <v>137243.28176910855</v>
+        <v>119839.31894255229</v>
       </c>
       <c r="AB20" s="11">
         <f>'QTR P&amp;L'!AE2*'BS DRIVERS'!AB18</f>
-        <v>156264.62792611256</v>
+        <v>121037.71213197782</v>
       </c>
       <c r="AC20" s="11">
         <f>'QTR P&amp;L'!AF2*'BS DRIVERS'!AC18</f>
-        <v>162595.45622524561</v>
+        <v>122248.08925329761</v>
       </c>
       <c r="AD20" s="11">
         <f>'QTR P&amp;L'!AG2*'BS DRIVERS'!AD18</f>
-        <v>157704.80478038648</v>
+        <v>123470.57014583058</v>
       </c>
       <c r="AE20" s="11">
         <f>'QTR P&amp;L'!AH2*'BS DRIVERS'!AE18</f>
-        <v>161405.12678460591</v>
+        <v>124705.27584728888</v>
       </c>
       <c r="AF20" s="11">
         <f>'QTR P&amp;L'!AI2*'BS DRIVERS'!AF18</f>
-        <v>183775.20383690321</v>
+        <v>125952.32860576178</v>
       </c>
       <c r="AG20" s="11">
         <f>'QTR P&amp;L'!AJ2*'BS DRIVERS'!AG18</f>
-        <v>191220.58208129858</v>
+        <v>127211.8518918194</v>
       </c>
       <c r="AH20" s="11">
         <f>'QTR P&amp;L'!AK2*'BS DRIVERS'!AH18</f>
-        <v>185468.92556054579</v>
+        <v>128483.97041073762</v>
       </c>
       <c r="AI20" s="11">
         <f>'QTR P&amp;L'!AL2*'BS DRIVERS'!AI18</f>
-        <v>189820.69370931163</v>
+        <v>129768.81011484498</v>
       </c>
       <c r="AJ20" s="11">
         <f>'QTR P&amp;L'!AM2*'BS DRIVERS'!AJ18</f>
-        <v>216129.0497633575</v>
+        <v>131066.49821599344</v>
       </c>
       <c r="AK20" s="11">
         <f>'QTR P&amp;L'!AN2*'BS DRIVERS'!AK18</f>
-        <v>224885.19581295212</v>
+        <v>132377.16319815337</v>
       </c>
       <c r="AL20" s="11">
         <f>'QTR P&amp;L'!AO2*'BS DRIVERS'!AL18</f>
-        <v>218120.95323592445</v>
+        <v>133700.93483013491</v>
       </c>
       <c r="AM20" s="11">
         <f>'QTR P&amp;L'!AP2*'BS DRIVERS'!AM18</f>
-        <v>223238.85540741609</v>
+        <v>135037.94417843624</v>
       </c>
       <c r="AN20" s="11">
         <f>'QTR P&amp;L'!AQ2*'BS DRIVERS'!AN18</f>
-        <v>254178.82922370537</v>
+        <v>136388.32362022062</v>
       </c>
       <c r="AO20" s="11">
         <f>'QTR P&amp;L'!AR2*'BS DRIVERS'!AO18</f>
-        <v>264476.50532895175</v>
+        <v>137752.20685642285</v>
       </c>
       <c r="AP20" s="11">
         <f>'QTR P&amp;L'!AS2*'BS DRIVERS'!AP18</f>
-        <v>256521.40970114723</v>
+        <v>139129.72892498708</v>
       </c>
     </row>
     <row r="21" spans="1:42" x14ac:dyDescent="0.25">
@@ -37030,83 +37031,83 @@
       </c>
       <c r="W21" s="11">
         <f>'QTR P&amp;L'!Z2*'BS DRIVERS'!W19</f>
-        <v>33062.991505159102</v>
+        <v>32628.049999999996</v>
       </c>
       <c r="X21" s="11">
         <f>'QTR P&amp;L'!AA2*'BS DRIVERS'!X19</f>
-        <v>37645.384160733673</v>
+        <v>32954.330499999996</v>
       </c>
       <c r="Y21" s="11">
         <f>'QTR P&amp;L'!AB2*'BS DRIVERS'!Y19</f>
-        <v>39170.530744061522</v>
+        <v>33283.873804999996</v>
       </c>
       <c r="Z21" s="11">
         <f>'QTR P&amp;L'!AC2*'BS DRIVERS'!Z19</f>
-        <v>37992.334149723982</v>
+        <v>33616.712543049995</v>
       </c>
       <c r="AA21" s="11">
         <f>'QTR P&amp;L'!AD2*'BS DRIVERS'!AA19</f>
-        <v>38883.7709720938</v>
+        <v>33952.879668480498</v>
       </c>
       <c r="AB21" s="11">
         <f>'QTR P&amp;L'!AE2*'BS DRIVERS'!AB19</f>
-        <v>44272.899372521912</v>
+        <v>34292.408465165303</v>
       </c>
       <c r="AC21" s="11">
         <f>'QTR P&amp;L'!AF2*'BS DRIVERS'!AC19</f>
-        <v>46066.549848333751</v>
+        <v>34635.332549816958</v>
       </c>
       <c r="AD21" s="11">
         <f>'QTR P&amp;L'!AG2*'BS DRIVERS'!AD19</f>
-        <v>44680.930324850116</v>
+        <v>34981.685875315125</v>
       </c>
       <c r="AE21" s="11">
         <f>'QTR P&amp;L'!AH2*'BS DRIVERS'!AE19</f>
-        <v>45729.305673212359</v>
+        <v>35331.502734068272</v>
       </c>
       <c r="AF21" s="11">
         <f>'QTR P&amp;L'!AI2*'BS DRIVERS'!AF19</f>
-        <v>52067.196617797796</v>
+        <v>35684.817761408958</v>
       </c>
       <c r="AG21" s="11">
         <f>'QTR P&amp;L'!AJ2*'BS DRIVERS'!AG19</f>
-        <v>54176.621419681556</v>
+        <v>36041.665939023056</v>
       </c>
       <c r="AH21" s="11">
         <f>'QTR P&amp;L'!AK2*'BS DRIVERS'!AH19</f>
-        <v>52547.06191060954</v>
+        <v>36402.08259841329</v>
       </c>
       <c r="AI21" s="11">
         <f>'QTR P&amp;L'!AL2*'BS DRIVERS'!AI19</f>
-        <v>53780.005001441037</v>
+        <v>36766.103424397421</v>
       </c>
       <c r="AJ21" s="11">
         <f>'QTR P&amp;L'!AM2*'BS DRIVERS'!AJ19</f>
-        <v>61233.689278525067</v>
+        <v>37133.764458641395</v>
       </c>
       <c r="AK21" s="11">
         <f>'QTR P&amp;L'!AN2*'BS DRIVERS'!AK19</f>
-        <v>63714.480856822032</v>
+        <v>37505.102103227808</v>
       </c>
       <c r="AL21" s="11">
         <f>'QTR P&amp;L'!AO2*'BS DRIVERS'!AL19</f>
-        <v>61798.035433961035</v>
+        <v>37880.15312426009</v>
       </c>
       <c r="AM21" s="11">
         <f>'QTR P&amp;L'!AP2*'BS DRIVERS'!AM19</f>
-        <v>63248.039640568801</v>
+        <v>38258.954655502683</v>
       </c>
       <c r="AN21" s="11">
         <f>'QTR P&amp;L'!AQ2*'BS DRIVERS'!AN19</f>
-        <v>72013.954009908543</v>
+        <v>38641.544202057717</v>
       </c>
       <c r="AO21" s="11">
         <f>'QTR P&amp;L'!AR2*'BS DRIVERS'!AO19</f>
-        <v>74931.491932783625</v>
+        <v>39027.959644078299</v>
       </c>
       <c r="AP21" s="11">
         <f>'QTR P&amp;L'!AS2*'BS DRIVERS'!AP19</f>
-        <v>72677.653985560464</v>
+        <v>39418.239240519084</v>
       </c>
     </row>
     <row r="22" spans="1:42" x14ac:dyDescent="0.25">
@@ -37199,83 +37200,83 @@
       </c>
       <c r="W22" s="7">
         <f t="shared" ref="W22:AP22" si="2">SUM(W16:W21)</f>
-        <v>1481750.1266472447</v>
+        <v>1462257.8</v>
       </c>
       <c r="X22" s="7">
         <f t="shared" si="2"/>
-        <v>1687114.5110734249</v>
+        <v>1476880.378</v>
       </c>
       <c r="Y22" s="7">
         <f t="shared" si="2"/>
-        <v>1755465.4388062961</v>
+        <v>1491649.18178</v>
       </c>
       <c r="Z22" s="7">
         <f t="shared" si="2"/>
-        <v>1702663.4123289702</v>
+        <v>1506565.6735977998</v>
       </c>
       <c r="AA22" s="7">
         <f t="shared" si="2"/>
-        <v>1742614.0206772315</v>
+        <v>1521631.3303337779</v>
       </c>
       <c r="AB22" s="7">
         <f t="shared" si="2"/>
-        <v>1984133.0522689917</v>
+        <v>1536847.6436371161</v>
       </c>
       <c r="AC22" s="7">
         <f t="shared" si="2"/>
-        <v>2064517.2431332811</v>
+        <v>1552216.1200734871</v>
       </c>
       <c r="AD22" s="7">
         <f t="shared" si="2"/>
-        <v>2002419.3563136205</v>
+        <v>1567738.2812742221</v>
       </c>
       <c r="AE22" s="7">
         <f t="shared" si="2"/>
-        <v>2049403.3173676953</v>
+        <v>1583415.6640869637</v>
       </c>
       <c r="AF22" s="7">
         <f t="shared" si="2"/>
-        <v>2333442.0652937721</v>
+        <v>1599249.8207278338</v>
       </c>
       <c r="AG22" s="7">
         <f t="shared" si="2"/>
-        <v>2427977.9897534926</v>
+        <v>1615242.3189351121</v>
       </c>
       <c r="AH22" s="7">
         <f t="shared" si="2"/>
-        <v>2354947.695184717</v>
+        <v>1631394.7421244634</v>
       </c>
       <c r="AI22" s="7">
         <f t="shared" si="2"/>
-        <v>2410203.2391576013</v>
+        <v>1647708.6895457082</v>
       </c>
       <c r="AJ22" s="7">
         <f t="shared" si="2"/>
-        <v>2744247.3506783172</v>
+        <v>1664185.7764411652</v>
       </c>
       <c r="AK22" s="7">
         <f t="shared" si="2"/>
-        <v>2855426.4384736046</v>
+        <v>1680827.634205577</v>
       </c>
       <c r="AL22" s="7">
         <f t="shared" si="2"/>
-        <v>2769539.0726073394</v>
+        <v>1697635.9105476327</v>
       </c>
       <c r="AM22" s="7">
         <f t="shared" si="2"/>
-        <v>2834522.4216320287</v>
+        <v>1714612.2696531089</v>
       </c>
       <c r="AN22" s="7">
         <f t="shared" si="2"/>
-        <v>3227375.4012216502</v>
+        <v>1731758.3923496399</v>
       </c>
       <c r="AO22" s="7">
         <f t="shared" si="2"/>
-        <v>3358127.7012984203</v>
+        <v>1749075.9762731367</v>
       </c>
       <c r="AP22" s="7">
         <f t="shared" si="2"/>
-        <v>3257119.7612510365</v>
+        <v>1766566.7360358683</v>
       </c>
     </row>
     <row r="23" spans="1:42" x14ac:dyDescent="0.25">
@@ -37368,83 +37369,83 @@
       </c>
       <c r="W23" s="11">
         <f>'QTR P&amp;L'!Z2*'BS DRIVERS'!W20</f>
-        <v>163744.96436780406</v>
+        <v>161590.90999999997</v>
       </c>
       <c r="X23" s="11">
         <f>'QTR P&amp;L'!AA2*'BS DRIVERS'!X20</f>
-        <v>186439.33314533171</v>
+        <v>163206.81909999999</v>
       </c>
       <c r="Y23" s="11">
         <f>'QTR P&amp;L'!AB2*'BS DRIVERS'!Y20</f>
-        <v>193992.6446145534</v>
+        <v>164838.88729099999</v>
       </c>
       <c r="Z23" s="11">
         <f>'QTR P&amp;L'!AC2*'BS DRIVERS'!Z20</f>
-        <v>188157.60820147005</v>
+        <v>166487.27616390999</v>
       </c>
       <c r="AA23" s="11">
         <f>'QTR P&amp;L'!AD2*'BS DRIVERS'!AA20</f>
-        <v>192572.4625165225</v>
+        <v>168152.14892554909</v>
       </c>
       <c r="AB23" s="11">
         <f>'QTR P&amp;L'!AE2*'BS DRIVERS'!AB20</f>
-        <v>219262.20224451798</v>
+        <v>169833.6704148046</v>
       </c>
       <c r="AC23" s="11">
         <f>'QTR P&amp;L'!AF2*'BS DRIVERS'!AC20</f>
-        <v>228145.28329313622</v>
+        <v>171532.00711895266</v>
       </c>
       <c r="AD23" s="11">
         <f>'QTR P&amp;L'!AG2*'BS DRIVERS'!AD20</f>
-        <v>221282.98169333217</v>
+        <v>173247.32719014215</v>
       </c>
       <c r="AE23" s="11">
         <f>'QTR P&amp;L'!AH2*'BS DRIVERS'!AE20</f>
-        <v>226475.07642664973</v>
+        <v>174979.80046204358</v>
       </c>
       <c r="AF23" s="11">
         <f>'QTR P&amp;L'!AI2*'BS DRIVERS'!AF20</f>
-        <v>257863.57697192655</v>
+        <v>176729.59846666403</v>
       </c>
       <c r="AG23" s="11">
         <f>'QTR P&amp;L'!AJ2*'BS DRIVERS'!AG20</f>
-        <v>268310.53513562208</v>
+        <v>178496.89445133068</v>
       </c>
       <c r="AH23" s="11">
         <f>'QTR P&amp;L'!AK2*'BS DRIVERS'!AH20</f>
-        <v>260240.11707600468</v>
+        <v>180281.863395844</v>
       </c>
       <c r="AI23" s="11">
         <f>'QTR P&amp;L'!AL2*'BS DRIVERS'!AI20</f>
-        <v>266346.28633912874</v>
+        <v>182084.68202980244</v>
       </c>
       <c r="AJ23" s="11">
         <f>'QTR P&amp;L'!AM2*'BS DRIVERS'!AJ20</f>
-        <v>303260.7702015324</v>
+        <v>183905.52885010047</v>
       </c>
       <c r="AK23" s="11">
         <f>'QTR P&amp;L'!AN2*'BS DRIVERS'!AK20</f>
-        <v>315546.92792954075</v>
+        <v>185744.58413860147</v>
       </c>
       <c r="AL23" s="11">
         <f>'QTR P&amp;L'!AO2*'BS DRIVERS'!AL20</f>
-        <v>306055.70305261912</v>
+        <v>187602.02997998748</v>
       </c>
       <c r="AM23" s="11">
         <f>'QTR P&amp;L'!AP2*'BS DRIVERS'!AM20</f>
-        <v>313236.87076719524</v>
+        <v>189478.05027978733</v>
       </c>
       <c r="AN23" s="11">
         <f>'QTR P&amp;L'!AQ2*'BS DRIVERS'!AN20</f>
-        <v>356650.19396376034</v>
+        <v>191372.83078258525</v>
       </c>
       <c r="AO23" s="11">
         <f>'QTR P&amp;L'!AR2*'BS DRIVERS'!AO20</f>
-        <v>371099.34455403138</v>
+        <v>193286.55909041112</v>
       </c>
       <c r="AP23" s="11">
         <f>'QTR P&amp;L'!AS2*'BS DRIVERS'!AP20</f>
-        <v>359937.1781087697</v>
+        <v>195219.42468131523</v>
       </c>
     </row>
     <row r="24" spans="1:42" x14ac:dyDescent="0.25">
@@ -37682,83 +37683,83 @@
       </c>
       <c r="W25" s="11">
         <f>'QTR P&amp;L'!Z2*'BS DRIVERS'!W22</f>
-        <v>130047.42543242677</v>
+        <v>128336.65999999999</v>
       </c>
       <c r="X25" s="11">
         <f>'QTR P&amp;L'!AA2*'BS DRIVERS'!X22</f>
-        <v>148071.45592842548</v>
+        <v>129620.02660000001</v>
       </c>
       <c r="Y25" s="11">
         <f>'QTR P&amp;L'!AB2*'BS DRIVERS'!Y22</f>
-        <v>154070.3500858976</v>
+        <v>130916.226866</v>
       </c>
       <c r="Z25" s="11">
         <f>'QTR P&amp;L'!AC2*'BS DRIVERS'!Z22</f>
-        <v>149436.12230517963</v>
+        <v>132225.38913465998</v>
       </c>
       <c r="AA25" s="11">
         <f>'QTR P&amp;L'!AD2*'BS DRIVERS'!AA22</f>
-        <v>152942.43127503703</v>
+        <v>133547.64302600658</v>
       </c>
       <c r="AB25" s="11">
         <f>'QTR P&amp;L'!AE2*'BS DRIVERS'!AB22</f>
-        <v>174139.61404330196</v>
+        <v>134883.11945626666</v>
       </c>
       <c r="AC25" s="11">
         <f>'QTR P&amp;L'!AF2*'BS DRIVERS'!AC22</f>
-        <v>181194.62074070197</v>
+        <v>136231.95065082936</v>
       </c>
       <c r="AD25" s="11">
         <f>'QTR P&amp;L'!AG2*'BS DRIVERS'!AD22</f>
-        <v>175744.53157893225</v>
+        <v>137594.27015733763</v>
       </c>
       <c r="AE25" s="11">
         <f>'QTR P&amp;L'!AH2*'BS DRIVERS'!AE22</f>
-        <v>179868.13046501786</v>
+        <v>138970.21285891099</v>
       </c>
       <c r="AF25" s="11">
         <f>'QTR P&amp;L'!AI2*'BS DRIVERS'!AF22</f>
-        <v>204797.10278399923</v>
+        <v>140359.91498750012</v>
       </c>
       <c r="AG25" s="11">
         <f>'QTR P&amp;L'!AJ2*'BS DRIVERS'!AG22</f>
-        <v>213094.1519056882</v>
+        <v>141763.51413737514</v>
       </c>
       <c r="AH25" s="11">
         <f>'QTR P&amp;L'!AK2*'BS DRIVERS'!AH22</f>
-        <v>206684.56798432171</v>
+        <v>143181.1492787489</v>
       </c>
       <c r="AI25" s="11">
         <f>'QTR P&amp;L'!AL2*'BS DRIVERS'!AI22</f>
-        <v>211534.1314196907</v>
+        <v>144612.9607715364</v>
       </c>
       <c r="AJ25" s="11">
         <f>'QTR P&amp;L'!AM2*'BS DRIVERS'!AJ22</f>
-        <v>240851.87933338698</v>
+        <v>146059.09037925175</v>
       </c>
       <c r="AK25" s="11">
         <f>'QTR P&amp;L'!AN2*'BS DRIVERS'!AK22</f>
-        <v>250609.63394375326</v>
+        <v>147519.68128304428</v>
       </c>
       <c r="AL25" s="11">
         <f>'QTR P&amp;L'!AO2*'BS DRIVERS'!AL22</f>
-        <v>243071.63505499749</v>
+        <v>148994.87809587471</v>
       </c>
       <c r="AM25" s="11">
         <f>'QTR P&amp;L'!AP2*'BS DRIVERS'!AM22</f>
-        <v>248774.9699727137</v>
+        <v>150484.82687683345</v>
       </c>
       <c r="AN25" s="11">
         <f>'QTR P&amp;L'!AQ2*'BS DRIVERS'!AN22</f>
-        <v>283254.14270927222</v>
+        <v>151989.6751456018</v>
       </c>
       <c r="AO25" s="11">
         <f>'QTR P&amp;L'!AR2*'BS DRIVERS'!AO22</f>
-        <v>294729.76176849048</v>
+        <v>153509.57189705785</v>
       </c>
       <c r="AP25" s="11">
         <f>'QTR P&amp;L'!AS2*'BS DRIVERS'!AP22</f>
-        <v>285864.68909856764</v>
+        <v>155044.66761602843</v>
       </c>
     </row>
     <row r="26" spans="1:42" x14ac:dyDescent="0.25">
@@ -38020,83 +38021,83 @@
       </c>
       <c r="W27" s="7">
         <f t="shared" ref="W27:AP27" si="3">W22+SUM(W23:W26)</f>
-        <v>1775542.5164474756</v>
+        <v>1752185.37</v>
       </c>
       <c r="X27" s="7">
         <f t="shared" si="3"/>
-        <v>2021625.3001471821</v>
+        <v>1769707.2237</v>
       </c>
       <c r="Y27" s="7">
         <f t="shared" si="3"/>
-        <v>2103528.4335067472</v>
+        <v>1787404.2959369998</v>
       </c>
       <c r="Z27" s="7">
         <f t="shared" si="3"/>
-        <v>2040257.1428356199</v>
+        <v>1805278.3388963698</v>
       </c>
       <c r="AA27" s="7">
         <f t="shared" si="3"/>
-        <v>2088128.9144687909</v>
+        <v>1823331.1222853335</v>
       </c>
       <c r="AB27" s="7">
         <f t="shared" si="3"/>
-        <v>2377534.8685568115</v>
+        <v>1841564.4335081873</v>
       </c>
       <c r="AC27" s="7">
         <f t="shared" si="3"/>
-        <v>2473857.1471671192</v>
+        <v>1859980.0778432691</v>
       </c>
       <c r="AD27" s="7">
         <f t="shared" si="3"/>
-        <v>2399446.8695858847</v>
+        <v>1878579.8786217018</v>
       </c>
       <c r="AE27" s="7">
         <f t="shared" si="3"/>
-        <v>2455746.5242593628</v>
+        <v>1897365.6774079183</v>
       </c>
       <c r="AF27" s="7">
         <f t="shared" si="3"/>
-        <v>2796102.7450496978</v>
+        <v>1916339.3341819979</v>
       </c>
       <c r="AG27" s="7">
         <f t="shared" si="3"/>
-        <v>2909382.6767948028</v>
+        <v>1935502.7275238179</v>
       </c>
       <c r="AH27" s="7">
         <f t="shared" si="3"/>
-        <v>2821872.3802450434</v>
+        <v>1954857.7547990563</v>
       </c>
       <c r="AI27" s="7">
         <f t="shared" si="3"/>
-        <v>2888083.6569164209</v>
+        <v>1974406.332347047</v>
       </c>
       <c r="AJ27" s="7">
         <f t="shared" si="3"/>
-        <v>3288360.0002132365</v>
+        <v>1994150.3956705173</v>
       </c>
       <c r="AK27" s="7">
         <f t="shared" si="3"/>
-        <v>3421583.0003468986</v>
+        <v>2014091.8996272227</v>
       </c>
       <c r="AL27" s="7">
         <f t="shared" si="3"/>
-        <v>3318666.410714956</v>
+        <v>2034232.8186234948</v>
       </c>
       <c r="AM27" s="7">
         <f t="shared" si="3"/>
-        <v>3396534.2623719377</v>
+        <v>2054575.1468097297</v>
       </c>
       <c r="AN27" s="7">
         <f t="shared" si="3"/>
-        <v>3867279.7378946827</v>
+        <v>2075120.8982778271</v>
       </c>
       <c r="AO27" s="7">
         <f t="shared" si="3"/>
-        <v>4023956.8076209421</v>
+        <v>2095872.1072606058</v>
       </c>
       <c r="AP27" s="7">
         <f t="shared" si="3"/>
-        <v>3902921.6284583742</v>
+        <v>2116830.8283332121</v>
       </c>
     </row>
     <row r="28" spans="1:42" x14ac:dyDescent="0.25">
@@ -38358,83 +38359,83 @@
       </c>
       <c r="W29" s="11">
         <f>'BS DRIVERS'!W25</f>
-        <v>5470785.6199506521</v>
+        <v>5470260.2300000004</v>
       </c>
       <c r="X29" s="11">
         <f>'BS DRIVERS'!X25</f>
-        <v>5516259.5659684297</v>
+        <v>5510067.5923000006</v>
       </c>
       <c r="Y29" s="11">
         <f>'BS DRIVERS'!Y25</f>
-        <v>5563575.8210752402</v>
+        <v>5550273.0282230005</v>
       </c>
       <c r="Z29" s="11">
         <f>'BS DRIVERS'!Z25</f>
-        <v>5609468.8672143724</v>
+        <v>5590880.5185052305</v>
       </c>
       <c r="AA29" s="11">
         <f>'BS DRIVERS'!AA25</f>
-        <v>5656438.7292990042</v>
+        <v>5631894.0836902829</v>
       </c>
       <c r="AB29" s="11">
         <f>'BS DRIVERS'!AB25</f>
-        <v>5709918.4182701828</v>
+        <v>5673317.7845271854</v>
       </c>
       <c r="AC29" s="11">
         <f>'BS DRIVERS'!AC25</f>
-        <v>5765564.757063915</v>
+        <v>5715155.7223724574</v>
       </c>
       <c r="AD29" s="11">
         <f>'BS DRIVERS'!AD25</f>
-        <v>5819537.3292374676</v>
+        <v>5757412.0395961823</v>
       </c>
       <c r="AE29" s="11">
         <f>'BS DRIVERS'!AE25</f>
-        <v>5874776.2921003606</v>
+        <v>5800090.9199921442</v>
       </c>
       <c r="AF29" s="11">
         <f>'BS DRIVERS'!AF25</f>
-        <v>5937671.1447119173</v>
+        <v>5843196.5891920654</v>
       </c>
       <c r="AG29" s="11">
         <f>'BS DRIVERS'!AG25</f>
-        <v>6003114.0884562368</v>
+        <v>5886733.3150839861</v>
       </c>
       <c r="AH29" s="11">
         <f>'BS DRIVERS'!AH25</f>
-        <v>6066588.5969514456</v>
+        <v>5930705.4082348263</v>
       </c>
       <c r="AI29" s="11">
         <f>'BS DRIVERS'!AI25</f>
-        <v>6131552.4457417643</v>
+        <v>5975117.222317175</v>
       </c>
       <c r="AJ29" s="11">
         <f>'BS DRIVERS'!AJ25</f>
-        <v>6205520.0128897559</v>
+        <v>6019973.1545403469</v>
       </c>
       <c r="AK29" s="11">
         <f>'BS DRIVERS'!AK25</f>
-        <v>6282484.2656826908</v>
+        <v>6065277.6460857503</v>
       </c>
       <c r="AL29" s="11">
         <f>'BS DRIVERS'!AL25</f>
-        <v>6357133.5378306387</v>
+        <v>6111035.1825466082</v>
       </c>
       <c r="AM29" s="11">
         <f>'BS DRIVERS'!AM25</f>
-        <v>6433534.3504260238</v>
+        <v>6157250.2943720743</v>
       </c>
       <c r="AN29" s="11">
         <f>'BS DRIVERS'!AN25</f>
-        <v>6520523.996837683</v>
+        <v>6203927.5573157948</v>
       </c>
       <c r="AO29" s="11">
         <f>'BS DRIVERS'!AO25</f>
-        <v>6611037.8990105046</v>
+        <v>6251071.5928889532</v>
       </c>
       <c r="AP29" s="11">
         <f>'BS DRIVERS'!AP25</f>
-        <v>6698829.26540823</v>
+        <v>6298687.0688178428</v>
       </c>
     </row>
     <row r="30" spans="1:42" x14ac:dyDescent="0.25">
@@ -38527,83 +38528,83 @@
       </c>
       <c r="W30" s="11">
         <f>'BS DRIVERS'!W26</f>
-        <v>9813469.8453200813</v>
+        <v>9807695.1314856745</v>
       </c>
       <c r="X30" s="11">
         <f>'BS DRIVERS'!X26</f>
-        <v>10333564.070206027</v>
+        <v>10265506.285771882</v>
       </c>
       <c r="Y30" s="11">
         <f>'BS DRIVERS'!Y26</f>
-        <v>10873907.650395554</v>
+        <v>10727692.783086628</v>
       </c>
       <c r="Z30" s="11">
         <f>'BS DRIVERS'!Z26</f>
-        <v>11398608.3266721</v>
+        <v>11194298.376860196</v>
       </c>
       <c r="AA30" s="11">
         <f>'BS DRIVERS'!AA26</f>
-        <v>11935144.600355599</v>
+        <v>11665367.258057175</v>
       </c>
       <c r="AB30" s="11">
         <f>'BS DRIVERS'!AB26</f>
-        <v>12543232.275687832</v>
+        <v>12140944.0595518</v>
       </c>
       <c r="AC30" s="11">
         <f>'BS DRIVERS'!AC26</f>
-        <v>13175134.229707889</v>
+        <v>12621073.860547045</v>
       </c>
       <c r="AD30" s="11">
         <f>'BS DRIVERS'!AD26</f>
-        <v>13788639.327744847</v>
+        <v>13105802.191037919</v>
       </c>
       <c r="AE30" s="11">
         <f>'BS DRIVERS'!AE26</f>
-        <v>14416063.694363965</v>
+        <v>13595175.036319377</v>
       </c>
       <c r="AF30" s="11">
         <f>'BS DRIVERS'!AF26</f>
-        <v>15127636.173049938</v>
+        <v>14089238.841539325</v>
       </c>
       <c r="AG30" s="11">
         <f>'BS DRIVERS'!AG26</f>
-        <v>15867215.462862438</v>
+        <v>14588040.516297147</v>
       </c>
       <c r="AH30" s="11">
         <f>'BS DRIVERS'!AH26</f>
-        <v>16585159.108043633</v>
+        <v>15091627.439288223</v>
       </c>
       <c r="AI30" s="11">
         <f>'BS DRIVERS'!AI26</f>
-        <v>17319472.525801618</v>
+        <v>15600047.462994885</v>
       </c>
       <c r="AJ30" s="11">
         <f>'BS DRIVERS'!AJ26</f>
-        <v>18152748.432081889</v>
+        <v>16113348.91842429</v>
       </c>
       <c r="AK30" s="11">
         <f>'BS DRIVERS'!AK26</f>
-        <v>19018961.782311615</v>
+        <v>16631580.619893663</v>
       </c>
       <c r="AL30" s="11">
         <f>'BS DRIVERS'!AL26</f>
-        <v>19859730.506620366</v>
+        <v>17154791.869863406</v>
       </c>
       <c r="AM30" s="11">
         <f>'BS DRIVERS'!AM26</f>
-        <v>20719750.921679534</v>
+        <v>17683032.46381852</v>
       </c>
       <c r="AN30" s="11">
         <f>'BS DRIVERS'!AN26</f>
-        <v>21696156.290529974</v>
+        <v>18216352.695198864</v>
       </c>
       <c r="AO30" s="11">
         <f>'BS DRIVERS'!AO26</f>
-        <v>22711297.779998444</v>
+        <v>18754803.360378686</v>
       </c>
       <c r="AP30" s="11">
         <f>'BS DRIVERS'!AP26</f>
-        <v>23696515.086513672</v>
+        <v>19298435.763695981</v>
       </c>
     </row>
     <row r="31" spans="1:42" x14ac:dyDescent="0.25">
@@ -39034,83 +39035,83 @@
       </c>
       <c r="W33" s="7">
         <f t="shared" ref="W33:AP33" si="4">SUM(W28:W32)</f>
-        <v>8778414.4652707335</v>
+        <v>8772114.361485675</v>
       </c>
       <c r="X33" s="7">
         <f t="shared" si="4"/>
-        <v>9369096.6361744571</v>
+        <v>9294846.8780718818</v>
       </c>
       <c r="Y33" s="7">
         <f t="shared" si="4"/>
-        <v>9981870.4714707937</v>
+        <v>9822352.8113096282</v>
       </c>
       <c r="Z33" s="7">
         <f t="shared" si="4"/>
-        <v>10577578.193886474</v>
+        <v>10354679.895365424</v>
       </c>
       <c r="AA33" s="7">
         <f t="shared" si="4"/>
-        <v>11186198.329654604</v>
+        <v>10891876.341747459</v>
       </c>
       <c r="AB33" s="7">
         <f t="shared" si="4"/>
-        <v>11872879.693958014</v>
+        <v>11433990.844078984</v>
       </c>
       <c r="AC33" s="7">
         <f t="shared" si="4"/>
-        <v>12585541.986771803</v>
+        <v>11981072.582919501</v>
       </c>
       <c r="AD33" s="7">
         <f t="shared" si="4"/>
-        <v>13278133.656982314</v>
+        <v>12533171.230634101</v>
       </c>
       <c r="AE33" s="7">
         <f t="shared" si="4"/>
-        <v>13985910.986464325</v>
+        <v>13090336.95631152</v>
       </c>
       <c r="AF33" s="7">
         <f t="shared" si="4"/>
-        <v>14785492.317761853</v>
+        <v>13652620.43073139</v>
       </c>
       <c r="AG33" s="7">
         <f t="shared" si="4"/>
-        <v>15615628.551318675</v>
+        <v>14220072.831381135</v>
       </c>
       <c r="AH33" s="7">
         <f t="shared" si="4"/>
-        <v>16422160.704995081</v>
+        <v>14792745.847523049</v>
       </c>
       <c r="AI33" s="7">
         <f t="shared" si="4"/>
-        <v>17246551.971543383</v>
+        <v>15370691.685312059</v>
       </c>
       <c r="AJ33" s="7">
         <f t="shared" si="4"/>
-        <v>18178909.444971643</v>
+        <v>15953963.072964638</v>
       </c>
       <c r="AK33" s="7">
         <f t="shared" si="4"/>
-        <v>19147201.047994304</v>
+        <v>16542613.265979413</v>
       </c>
       <c r="AL33" s="7">
         <f t="shared" si="4"/>
-        <v>20087733.044451006</v>
+        <v>17136696.052410014</v>
       </c>
       <c r="AM33" s="7">
         <f t="shared" si="4"/>
-        <v>21049268.27210556</v>
+        <v>17736265.758190595</v>
       </c>
       <c r="AN33" s="7">
         <f t="shared" si="4"/>
-        <v>22137777.287367657</v>
+        <v>18341377.25251466</v>
       </c>
       <c r="AO33" s="7">
         <f t="shared" si="4"/>
-        <v>23268546.67900895</v>
+        <v>18952085.953267641</v>
       </c>
       <c r="AP33" s="7">
         <f t="shared" si="4"/>
-        <v>24366669.351921901</v>
+        <v>19568447.832513824</v>
       </c>
     </row>
     <row r="34" spans="1:42" x14ac:dyDescent="0.25">
@@ -39203,83 +39204,83 @@
       </c>
       <c r="W34" s="7">
         <f t="shared" ref="W34:AP34" si="5">W27+W33</f>
-        <v>10553956.981718209</v>
+        <v>10524299.731485676</v>
       </c>
       <c r="X34" s="7">
         <f t="shared" si="5"/>
-        <v>11390721.936321639</v>
+        <v>11064554.101771882</v>
       </c>
       <c r="Y34" s="7">
         <f t="shared" si="5"/>
-        <v>12085398.904977541</v>
+        <v>11609757.107246628</v>
       </c>
       <c r="Z34" s="7">
         <f t="shared" si="5"/>
-        <v>12617835.336722095</v>
+        <v>12159958.234261794</v>
       </c>
       <c r="AA34" s="7">
         <f t="shared" si="5"/>
-        <v>13274327.244123396</v>
+        <v>12715207.464032792</v>
       </c>
       <c r="AB34" s="7">
         <f t="shared" si="5"/>
-        <v>14250414.562514827</v>
+        <v>13275555.277587172</v>
       </c>
       <c r="AC34" s="7">
         <f t="shared" si="5"/>
-        <v>15059399.133938923</v>
+        <v>13841052.66076277</v>
       </c>
       <c r="AD34" s="7">
         <f t="shared" si="5"/>
-        <v>15677580.526568199</v>
+        <v>14411751.109255802</v>
       </c>
       <c r="AE34" s="7">
         <f t="shared" si="5"/>
-        <v>16441657.510723688</v>
+        <v>14987702.633719439</v>
       </c>
       <c r="AF34" s="7">
         <f t="shared" si="5"/>
-        <v>17581595.06281155</v>
+        <v>15568959.764913388</v>
       </c>
       <c r="AG34" s="7">
         <f t="shared" si="5"/>
-        <v>18525011.22811348</v>
+        <v>16155575.558904953</v>
       </c>
       <c r="AH34" s="7">
         <f t="shared" si="5"/>
-        <v>19244033.085240126</v>
+        <v>16747603.602322105</v>
       </c>
       <c r="AI34" s="7">
         <f t="shared" si="5"/>
-        <v>20134635.628459804</v>
+        <v>17345098.017659105</v>
       </c>
       <c r="AJ34" s="7">
         <f t="shared" si="5"/>
-        <v>21467269.445184879</v>
+        <v>17948113.468635157</v>
       </c>
       <c r="AK34" s="7">
         <f t="shared" si="5"/>
-        <v>22568784.048341203</v>
+        <v>18556705.165606637</v>
       </c>
       <c r="AL34" s="7">
         <f t="shared" si="5"/>
-        <v>23406399.45516596</v>
+        <v>19170928.871033508</v>
       </c>
       <c r="AM34" s="7">
         <f t="shared" si="5"/>
-        <v>24445802.534477498</v>
+        <v>19790840.905000325</v>
       </c>
       <c r="AN34" s="7">
         <f t="shared" si="5"/>
-        <v>26005057.025262341</v>
+        <v>20416498.150792487</v>
       </c>
       <c r="AO34" s="7">
         <f t="shared" si="5"/>
-        <v>27292503.486629892</v>
+        <v>21047958.060528249</v>
       </c>
       <c r="AP34" s="7">
         <f t="shared" si="5"/>
-        <v>28269590.980380274</v>
+        <v>21685278.660847038</v>
       </c>
     </row>
   </sheetData>
